--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6507285861344934</v>
+        <v>0.6507185199474106</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514749943297899</v>
+        <v>0.6514698916445938</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525806380241281</v>
+        <v>0.6525717005696026</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497716531981911</v>
+        <v>0.6497682440778303</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464748704057454</v>
+        <v>0.6464711542190449</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431895283144505</v>
+        <v>0.643185385706021</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408756747511436</v>
+        <v>0.6408712579731557</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398604654474215</v>
+        <v>0.6398560269169357</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642653943043196</v>
+        <v>0.6426310151515504</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6434261100152229</v>
+        <v>0.6434120742290093</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6415178609259462</v>
+        <v>0.641503942914484</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6386428006487677</v>
+        <v>0.6386287279698382</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6408353307611966</v>
+        <v>0.6407942593895866</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6408889754648854</v>
+        <v>0.6408502021684547</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6401494546642179</v>
+        <v>0.6401298932123969</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424858616755921</v>
+        <v>0.6424686899349309</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6454118615258277</v>
+        <v>0.645379743451557</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6474174938496128</v>
+        <v>0.6473770484968863</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6469795572733819</v>
+        <v>0.6469459790756278</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6470257466517234</v>
+        <v>0.6470061512616139</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6459753429630415</v>
+        <v>0.6459420351171408</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6457454645240396</v>
+        <v>0.6456863712798924</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.647046569308633</v>
+        <v>0.6469474846005487</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6451878664788162</v>
+        <v>0.6450593159152099</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6447706757821856</v>
+        <v>0.6446072519363151</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.646202583451899</v>
+        <v>0.6460167969774993</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6469046796839537</v>
+        <v>0.646710111744159</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6491008055268204</v>
+        <v>0.648873660899875</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.655402601709089</v>
+        <v>0.6552050193028565</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6682879290217325</v>
+        <v>0.6680129021169798</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6759748236734053</v>
+        <v>0.6756660968899515</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6914378135194361</v>
+        <v>0.6911716671189063</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.69973143239214</v>
+        <v>0.699533335351625</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7021861744449246</v>
+        <v>0.7019836083402915</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7024618375768374</v>
+        <v>0.7022635418345071</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708698836114684</v>
+        <v>0.7086536783024621</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7085382295560261</v>
+        <v>0.7085098864697146</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7103660458410836</v>
+        <v>0.7104200967226579</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7148733040169202</v>
+        <v>0.7150760554330419</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7149387763127857</v>
+        <v>0.7151482223252652</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.721128765294873</v>
+        <v>0.7214081835442895</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7184380302604968</v>
+        <v>0.7185579052562495</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7216063933769179</v>
+        <v>0.7217409852019792</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7214007630578103</v>
+        <v>0.72150972580251</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.719254820438356</v>
+        <v>0.7189337547636725</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7149928845689819</v>
+        <v>0.7147355770808005</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165525256402152</v>
+        <v>0.7160832991857088</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7173784711340883</v>
+        <v>0.717028417775726</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7167384872409278</v>
+        <v>0.7167695317376283</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7146363725283122</v>
+        <v>0.7152879509571595</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7134897841176326</v>
+        <v>0.7146370412500995</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.713755595162106</v>
+        <v>0.7153047566733772</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7132963453087501</v>
+        <v>0.7157066917747108</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7166335051435684</v>
+        <v>0.7192572473807032</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7184365734185012</v>
+        <v>0.7217841818400345</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.718597147278755</v>
+        <v>0.7228632022634055</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7197320602401914</v>
+        <v>0.7250598444576172</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7194703018485114</v>
+        <v>0.7275616133628034</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,15 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7148</v>
+        <v>0.7309418545532345</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>0.7362963661149134</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6507185199474106</v>
+        <v>0.650713864091615</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514698916445938</v>
+        <v>0.6514675253099385</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525717005696026</v>
+        <v>0.6525675625606164</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497682440778303</v>
+        <v>0.6497666548991465</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464711542190449</v>
+        <v>0.6464694235042964</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643185385706021</v>
+        <v>0.643183457949141</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408712579731557</v>
+        <v>0.6408692035854174</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398560269169357</v>
+        <v>0.6398539629068287</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6426310151515504</v>
+        <v>0.6426204191015291</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6434120742290093</v>
+        <v>0.6434055974726132</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.641503942914484</v>
+        <v>0.6414975196775513</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6386287279698382</v>
+        <v>0.6386222326876578</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6407942593895866</v>
+        <v>0.6407752930412673</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6408502021684547</v>
+        <v>0.6408322692651482</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6401298932123969</v>
+        <v>0.6401208319790177</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424686899349309</v>
+        <v>0.6424607772457004</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645379743451557</v>
+        <v>0.6453649122350529</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6473770484968863</v>
+        <v>0.6473583121218814</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6469459790756278</v>
+        <v>0.6469304051934128</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6470061512616139</v>
+        <v>0.6469970699774246</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6459420351171408</v>
+        <v>0.6459266097416924</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6456863712798924</v>
+        <v>0.6456590436019578</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6469474846005487</v>
+        <v>0.6469015997595871</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6450593159152099</v>
+        <v>0.644999751119318</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6446072519363151</v>
+        <v>0.6445315178593645</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6460167969774993</v>
+        <v>0.6459306342359625</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.646710111744159</v>
+        <v>0.6466198079809629</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.648873660899875</v>
+        <v>0.6487682414287752</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6552050193028565</v>
+        <v>0.6551135393200145</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6680129021169798</v>
+        <v>0.6678854030071413</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6756660968899515</v>
+        <v>0.6755229953715065</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6911716671189063</v>
+        <v>0.6910478866854326</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.699533335351625</v>
+        <v>0.6994411237058659</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7019836083402915</v>
+        <v>0.701889155302974</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7022635418345071</v>
+        <v>0.702170808818206</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7086536783024621</v>
+        <v>0.7086321521815903</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7085098864697146</v>
+        <v>0.7084961044337501</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7104200967226579</v>
+        <v>0.7104445403441921</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7150760554330419</v>
+        <v>0.7151700063861924</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7151482223252652</v>
+        <v>0.715245472962321</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7214081835442895</v>
+        <v>0.7215381898735157</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7185579052562495</v>
+        <v>0.718613656138136</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7217409852019792</v>
+        <v>0.7218036605389588</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.72150972580251</v>
+        <v>0.7215606580998188</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7189337547636725</v>
+        <v>0.7189730820840421</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147355770808005</v>
+        <v>0.7147352862353931</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7160832991857088</v>
+        <v>0.7162972444328743</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.717028417775726</v>
+        <v>0.7171754490368399</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7167695317376283</v>
+        <v>0.7170186159285344</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7152879509571595</v>
+        <v>0.7158724200991863</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7146370412500995</v>
+        <v>0.7154739949287631</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7153047566733772</v>
+        <v>0.7163324204605481</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7157066917747108</v>
+        <v>0.7169717810453352</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7192572473807032</v>
+        <v>0.7204676060260744</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7217841818400345</v>
+        <v>0.7231920995660159</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7228632022634055</v>
+        <v>0.7251325430774712</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7250598444576172</v>
+        <v>0.727484754825826</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7275616133628034</v>
+        <v>0.7299606344912326</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7309418545532345</v>
+        <v>0.7335254044842929</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,15 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7362963661149134</v>
+        <v>0.7397693752681768</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>0.7456552823207711</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7171754490368399</v>
+        <v>0.7171763208968076</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7170186159285344</v>
+        <v>0.7170207558771033</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7158724200991863</v>
+        <v>0.7158844771933623</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7154739949287631</v>
+        <v>0.7155038537106879</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7163324204605481</v>
+        <v>0.7163678524956069</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7169717810453352</v>
+        <v>0.7170102337033186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7204676060260744</v>
+        <v>0.7205071716706701</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7231920995660159</v>
+        <v>0.7232441190827048</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7251325430774712</v>
+        <v>0.7252180902883667</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.727484754825826</v>
+        <v>0.7275768688743488</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7299606344912326</v>
+        <v>0.7300027526788347</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7335254044842929</v>
+        <v>0.7338004381074452</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7397693752681768</v>
+        <v>0.7401166042634602</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7456552823207711</v>
+        <v>0.7461399615646985</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7171763208968076</v>
+        <v>0.7171765460042003</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7170207558771033</v>
+        <v>0.7170212979862514</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7158844771933623</v>
+        <v>0.7158854579054477</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7155038537106879</v>
+        <v>0.7155049229666012</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7163678524956069</v>
+        <v>0.7163696509948988</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7170102337033186</v>
+        <v>0.7170134736518317</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7205071716706701</v>
+        <v>0.7205124539418408</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7232441190827048</v>
+        <v>0.7232521068397924</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7252180902883667</v>
+        <v>0.7252310741375556</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7275768688743488</v>
+        <v>0.7275935009115245</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7300027526788347</v>
+        <v>0.7300235881960933</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7338004381074452</v>
+        <v>0.7338291017064265</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7401166042634602</v>
+        <v>0.7401748061986761</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,15 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7461399615646985</v>
+        <v>0.7462583007729743</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>0.7475818770185665</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650713864091615</v>
+        <v>0.6507094352122202</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514675253099385</v>
+        <v>0.6514652706876332</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525675625606164</v>
+        <v>0.6525636238090575</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497666548991465</v>
+        <v>0.6497651359300362</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464694235042964</v>
+        <v>0.6464677701872972</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643183457949141</v>
+        <v>0.6431816173072668</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408692035854174</v>
+        <v>0.6408672425920986</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398539629068287</v>
+        <v>0.6398519930187283</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6426204191015291</v>
+        <v>0.6426103447394877</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6434055974726132</v>
+        <v>0.6433994453718721</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414975196775513</v>
+        <v>0.6414914179271038</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6386222326876578</v>
+        <v>0.63861606210644</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6407752930412673</v>
+        <v>0.6407572691464223</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6408322692651482</v>
+        <v>0.6408152112311486</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6401208319790177</v>
+        <v>0.6401122045547347</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424607772457004</v>
+        <v>0.6424532677619236</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6453649122350529</v>
+        <v>0.6453508184466639</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6473583121218814</v>
+        <v>0.6473404722743692</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6469304051934128</v>
+        <v>0.6469155654520269</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469970699774246</v>
+        <v>0.6469884210442052</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6459266097416924</v>
+        <v>0.6459119250812115</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6456590436019578</v>
+        <v>0.6456330512375035</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6469015997595871</v>
+        <v>0.6468579197295992</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.644999751119318</v>
+        <v>0.644943028535487</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6445315178593645</v>
+        <v>0.6444593917172077</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6459306342359625</v>
+        <v>0.6458485383369819</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6466198079809629</v>
+        <v>0.6465337268120994</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6487682414287752</v>
+        <v>0.6486677542285695</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6551135393200145</v>
+        <v>0.6550264675218165</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6678854030071413</v>
+        <v>0.6677639529573811</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6755229953715065</v>
+        <v>0.6753866952948434</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6910478866854326</v>
+        <v>0.6909297445517903</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6994411237058659</v>
+        <v>0.6993530660462802</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.701889155302974</v>
+        <v>0.7017988632041738</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.702170808818206</v>
+        <v>0.7020820028403217</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7086321521815903</v>
+        <v>0.7086112990167626</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084961044337501</v>
+        <v>0.7084825972412747</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7104445403441921</v>
+        <v>0.7104674616985416</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7151700063861924</v>
+        <v>0.7152594752185863</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.715245472962321</v>
+        <v>0.7153381991687409</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7215381898735157</v>
+        <v>0.7216623069248804</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.718613656138136</v>
+        <v>0.7186668663501684</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7218036605389588</v>
+        <v>0.721863526102368</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7215606580998188</v>
+        <v>0.7216094194217465</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7189730820840421</v>
+        <v>0.7190108089826077</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147352862353931</v>
+        <v>0.7147350422887455</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7162972444328743</v>
+        <v>0.7164797877608322</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7171765460042003</v>
+        <v>0.7172877145567123</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7170212979862514</v>
+        <v>0.717192188766658</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7158854579054477</v>
+        <v>0.7162761584950894</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7155049229666012</v>
+        <v>0.7160613267402842</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7163696509948988</v>
+        <v>0.7170125134330514</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7170134736518317</v>
+        <v>0.7177743294936534</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7205124539418408</v>
+        <v>0.7211735176214802</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7232521068397924</v>
+        <v>0.7240349144914466</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7252310741375556</v>
+        <v>0.7265995496814383</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7275935009115245</v>
+        <v>0.7290590562288106</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7300235881960933</v>
+        <v>0.7314058443661463</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7338291017064265</v>
+        <v>0.735384642255416</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7401748061986761</v>
+        <v>0.7414024980826029</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7462583007729743</v>
+        <v>0.7464414874584442</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,15 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7475818770185665</v>
+        <v>0.7479519485053475</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>0.7347144485053475</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6507094352122202</v>
+        <v>0.6507052171093453</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514652706876332</v>
+        <v>0.6514631200602321</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525636238090575</v>
+        <v>0.652559870267875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497651359300362</v>
+        <v>0.6497636826669255</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464677701872972</v>
+        <v>0.6464661892318568</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431816173072668</v>
+        <v>0.6431798580434029</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408672425920986</v>
+        <v>0.6408653688011786</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398519930187283</v>
+        <v>0.6398501109912801</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6426103447394877</v>
+        <v>0.6426007545002435</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433994453718721</v>
+        <v>0.643393594149704</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414914179271038</v>
+        <v>0.6414856141513374</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.63861606210644</v>
+        <v>0.6386101925058979</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6407572691464223</v>
+        <v>0.6407401192769607</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6408152112311486</v>
+        <v>0.6407989657219929</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6401122045547347</v>
+        <v>0.6401039805577726</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424532677619236</v>
+        <v>0.6424461315182903</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6453508184466639</v>
+        <v>0.645337408580331</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6473404722743692</v>
+        <v>0.6473234663862324</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6469155654520269</v>
+        <v>0.6469014093503188</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469884210442052</v>
+        <v>0.6469801744296022</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6459119250812115</v>
+        <v>0.6458979292288922</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6456330512375035</v>
+        <v>0.6456082989819818</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6468579197295992</v>
+        <v>0.6468162897788798</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.644943028535487</v>
+        <v>0.6448889503730463</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6444593917172077</v>
+        <v>0.6443906230638132</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6458485383369819</v>
+        <v>0.6457702299384283</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6465337268120994</v>
+        <v>0.6464515812984606</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6486677542285695</v>
+        <v>0.6485718642870858</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6550264675218165</v>
+        <v>0.6549434949338448</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6677639529573811</v>
+        <v>0.6676481350673535</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6753866952948434</v>
+        <v>0.67525672713508</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6909297445517903</v>
+        <v>0.6908168683549183</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6993530660462802</v>
+        <v>0.6992688917095758</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7017988632041738</v>
+        <v>0.7017124680481964</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7020820028403217</v>
+        <v>0.7019968869026638</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7086112990167626</v>
+        <v>0.7085910963916431</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084825972412747</v>
+        <v>0.7084693716156735</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7104674616985416</v>
+        <v>0.7104889899064051</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7152594752185863</v>
+        <v>0.7153447725889603</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7153381991687409</v>
+        <v>0.7154267058590096</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7216623069248804</v>
+        <v>0.7217809221147455</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7186668663501684</v>
+        <v>0.7187177034219067</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.721863526102368</v>
+        <v>0.7219207635021438</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7216094194217465</v>
+        <v>0.7216561418763706</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7190108089826077</v>
+        <v>0.7190470276260805</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147350422887455</v>
+        <v>0.7147348398166541</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7164797877608322</v>
+        <v>0.7164848110675592</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7172877145567123</v>
+        <v>0.716223692785982</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.717192188766658</v>
+        <v>0.7158435293613508</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7162761584950894</v>
+        <v>0.7148912062904405</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7160613267402842</v>
+        <v>0.7143223214124327</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7170125134330514</v>
+        <v>0.7150873813758952</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7177743294936534</v>
+        <v>0.7157011675250564</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7211735176214802</v>
+        <v>0.7186747214595217</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7240349144914466</v>
+        <v>0.7210005614018347</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7265995496814383</v>
+        <v>0.7229134905268551</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7290590562288106</v>
+        <v>0.7255555907941547</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7314058443661463</v>
+        <v>0.7270963991199362</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.735384642255416</v>
+        <v>0.7295232785429555</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7414024980826029</v>
+        <v>0.727338927437558</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7464414874584442</v>
+        <v>0.7260446105420256</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7479519485053475</v>
+        <v>0.7265780171630868</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7347144485053475</v>
+        <v>0.7126655171630867</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6507052171093453</v>
+        <v>0.6507011950886468</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514631200602321</v>
+        <v>0.6514610664041571</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652559870267875</v>
+        <v>0.6525562891794642</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497636826669255</v>
+        <v>0.6497622909786271</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464661892318568</v>
+        <v>0.6464646760254001</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431798580434029</v>
+        <v>0.6431781749099146</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408653688011786</v>
+        <v>0.640863576552858</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398501109912801</v>
+        <v>0.6398483111033193</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6426007545002435</v>
+        <v>0.642591614337449</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643393594149704</v>
+        <v>0.643388022292346</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414856141513374</v>
+        <v>0.6414800870735631</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6386101925058979</v>
+        <v>0.6386046024183194</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6407401192769607</v>
+        <v>0.6407237814625326</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6407989657219929</v>
+        <v>0.640783476165906</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6401039805577726</v>
+        <v>0.6400961323749341</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424461315182903</v>
+        <v>0.6424393414393276</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645337408580331</v>
+        <v>0.6453246341702029</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6473234663862324</v>
+        <v>0.6473072375542048</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6469014093503188</v>
+        <v>0.6468878908956712</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469801744296022</v>
+        <v>0.6469723028084229</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458979292288922</v>
+        <v>0.6458845750000077</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6456082989819818</v>
+        <v>0.6455847004423887</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6468162897788798</v>
+        <v>0.6467765692829145</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6448889503730463</v>
+        <v>0.6448373366970503</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6443906230638132</v>
+        <v>0.6443249839855756</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6457702299384283</v>
+        <v>0.6456954545337699</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6464515812984606</v>
+        <v>0.6463731097010044</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6485718642870858</v>
+        <v>0.6484802659705038</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6549434949338448</v>
+        <v>0.6548643406071667</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6676481350673535</v>
+        <v>0.6675375695638566</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.67525672713508</v>
+        <v>0.675132663244405</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6908168683549183</v>
+        <v>0.6907089174193889</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6992688917095758</v>
+        <v>0.6991883526881791</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7017124680481964</v>
+        <v>0.7016297272339415</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7019968869026638</v>
+        <v>0.7019152419878582</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7085910963916431</v>
+        <v>0.7085715217249038</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084693716156735</v>
+        <v>0.7084564314071744</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7104889899064051</v>
+        <v>0.7105092404716049</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7153447725889603</v>
+        <v>0.715426181324762</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7154267058590096</v>
+        <v>0.7155112714796921</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7217809221147455</v>
+        <v>0.7218943899637851</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7187177034219067</v>
+        <v>0.7187663206824827</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7219207635021438</v>
+        <v>0.72197553932818</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7216561418763706</v>
+        <v>0.7217009474406493</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7190470276260805</v>
+        <v>0.7190818235913141</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147348398166541</v>
+        <v>0.7147346740654648</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7164848110675592</v>
+        <v>0.716489693471198</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716223692785982</v>
+        <v>0.7162391730703694</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7158435293613508</v>
+        <v>0.7148945242008344</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7148912062904405</v>
+        <v>0.7138198138038978</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7143223214124327</v>
+        <v>0.713188219024341</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7150873813758952</v>
+        <v>0.7136704317369171</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7157011675250564</v>
+        <v>0.7141466221784469</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7186747214595217</v>
+        <v>0.7168968616645348</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7210005614018347</v>
+        <v>0.7191249761031029</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7229134905268551</v>
+        <v>0.7208931550116159</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7255555907941547</v>
+        <v>0.7231957914355751</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7270963991199362</v>
+        <v>0.724855610904936</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7295232785429555</v>
+        <v>0.7276030738115663</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.727338927437558</v>
+        <v>0.72562501073332</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7260446105420256</v>
+        <v>0.7201499637481441</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7265780171630868</v>
+        <v>0.720616537127571</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7126655171630867</v>
+        <v>0.7065080623881428</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45142</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45170</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45205</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45233</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45261</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45296</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45324</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45352</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45387</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45415</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45443</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45478</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45506</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45541</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45569</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45597</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45632</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45660</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45688</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45716</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45751</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45779</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45814</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45821</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45828</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45835</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45842</v>
       </c>
       <c r="B41">
@@ -692,507 +718,515 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6507011950886468</v>
+        <v>0.650697355790425</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514610664041571</v>
+        <v>0.6514591033135422</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525562891794642</v>
+        <v>0.6525528689310963</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497622909786271</v>
+        <v>0.6497609570691959</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464646760254001</v>
+        <v>0.6464632263358238</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431781749099146</v>
+        <v>0.6431765630978556</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640863576552858</v>
+        <v>0.6408618606639637</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398483111033193</v>
+        <v>0.6398465881172091</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642591614337449</v>
+        <v>0.6425828933213488</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643388022292346</v>
+        <v>0.6433827102866516</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414800870735631</v>
+        <v>0.6414748173930983</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6386046024183194</v>
+        <v>0.6385992723676889</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6407237814625326</v>
+        <v>0.6407081994473822</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640783476165906</v>
+        <v>0.6407686911122471</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400961323749341</v>
+        <v>0.6400886348536611</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424393414393276</v>
+        <v>0.6424328730000509</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6453246341702029</v>
+        <v>0.6453124512123097</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6473072375542048</v>
+        <v>0.6472917339157086</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468878908956712</v>
+        <v>0.6468749681140529</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469723028084229</v>
+        <v>0.6469647812655973</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458845750000077</v>
+        <v>0.6458718194087294</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6455847004423887</v>
+        <v>0.6455621770439526</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6467765692829145</v>
+        <v>0.6467386301568816</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6448373366970503</v>
+        <v>0.6447880234666972</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6443249839855756</v>
+        <v>0.6442622666365334</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6456954545337699</v>
+        <v>0.6456239797712777</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6463731097010044</v>
+        <v>0.6462980727983068</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6484802659705038</v>
+        <v>0.6483926799041148</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6548643406071667</v>
+        <v>0.6547887485318848</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6675375695638566</v>
+        <v>0.6674319097933984</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.675132663244405</v>
+        <v>0.6750141133255999</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6907089174193889</v>
+        <v>0.6906055795015973</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6991883526881791</v>
+        <v>0.6991112213497017</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7016297272339415</v>
+        <v>0.7015504174864717</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7019152419878582</v>
+        <v>0.7018368654737119</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7085715217249038</v>
+        <v>0.7085525525277743</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084564314071744</v>
+        <v>0.7084437781504691</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7105092404716049</v>
+        <v>0.7105283169787855</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.715426181324762</v>
+        <v>0.7155039594457004</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7155112714796921</v>
+        <v>0.7155921507837055</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7218943899637851</v>
+        <v>0.7220030354758797</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7187663206824827</v>
+        <v>0.7188128587095947</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.72197553932818</v>
+        <v>0.7220280066364297</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7217009474406493</v>
+        <v>0.7217439488670458</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7190818235913141</v>
+        <v>0.7191152763996869</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147346740654648</v>
+        <v>0.7147345408602801</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716489693471198</v>
+        <v>0.716494438801582</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7162391730703694</v>
+        <v>0.7162540209932083</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7148945242008344</v>
+        <v>0.7149120597824469</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7138198138038978</v>
+        <v>0.7127756743605178</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.713188219024341</v>
+        <v>0.7119943581497682</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7136704317369171</v>
+        <v>0.7123435749431436</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7141466221784469</v>
+        <v>0.7125016115053904</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7168968616645348</v>
+        <v>0.7148785199903257</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7191249761031029</v>
+        <v>0.7167238372314166</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7208931550116159</v>
+        <v>0.7182530789280553</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7231957914355751</v>
+        <v>0.7202337310955438</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.724855610904936</v>
+        <v>0.7215549986277876</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7276030738115663</v>
+        <v>0.7238214476102893</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.72562501073332</v>
+        <v>0.7214356949252634</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7201499637481441</v>
+        <v>0.7172063031481856</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.720616537127571</v>
+        <v>0.7178301216278633</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7065080623881428</v>
+        <v>0.7065289904708</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>0.7040803820995383</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650697355790425</v>
+        <v>0.6506936870414841</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514591033135422</v>
+        <v>0.6514572249338763</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525528689310963</v>
+        <v>0.6525495989293637</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497609570691959</v>
+        <v>0.6497596774450648</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464632263358238</v>
+        <v>0.6464618362734504</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431765630978556</v>
+        <v>0.6431750181924085</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408618606639637</v>
+        <v>0.6408602163791272</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398465881172091</v>
+        <v>0.6398449372291126</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425828933213488</v>
+        <v>0.6425745632904312</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433827102866516</v>
+        <v>0.6433776403931011</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414748173930983</v>
+        <v>0.6414697875613448</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385992723676889</v>
+        <v>0.6385941846442058</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6407081994473822</v>
+        <v>0.6406933220473794</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6407686911122471</v>
+        <v>0.6407545636660689</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400886348536611</v>
+        <v>0.6400814650342508</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424328730000509</v>
+        <v>0.6424267039332323</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6453124512123097</v>
+        <v>0.6453008196638926</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472917339157086</v>
+        <v>0.6472769081050771</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468749681140529</v>
+        <v>0.6468626026223137</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469647812655973</v>
+        <v>0.6469575870372426</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458718194087294</v>
+        <v>0.64585962321276</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6455621770439526</v>
+        <v>0.6455406571678477</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6467386301568816</v>
+        <v>0.6467023554920559</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6447880234666972</v>
+        <v>0.64474086082563</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6442622666365334</v>
+        <v>0.6442022810884583</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6456239797712777</v>
+        <v>0.6455555931106322</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6462980727983068</v>
+        <v>0.6462262515364058</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6483926799041148</v>
+        <v>0.6483088502380538</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6547887485318848</v>
+        <v>0.6547164849471512</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6674319097933984</v>
+        <v>0.6673308387182431</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6750141133255999</v>
+        <v>0.6749007204749893</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6906055795015973</v>
+        <v>0.6905065679212972</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6991112213497017</v>
+        <v>0.6990372884207693</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7015504174864717</v>
+        <v>0.7014743330161524</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7018368654737119</v>
+        <v>0.7017615696993043</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7085525525277743</v>
+        <v>0.7085341665978069</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084437781504691</v>
+        <v>0.7084314115204946</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7105283169787855</v>
+        <v>0.7105463125488277</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7155039594457004</v>
+        <v>0.7155783428046911</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7155921507837055</v>
+        <v>0.7156695772676559</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7220030354758797</v>
+        <v>0.7221071571142404</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7188128587095947</v>
+        <v>0.7188574466079646</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7220280066364297</v>
+        <v>0.7220783062669184</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7217439488670458</v>
+        <v>0.7217852505014495</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7191152763996869</v>
+        <v>0.7191474600071255</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147345408602801</v>
+        <v>0.7147344365270357</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716494438801582</v>
+        <v>0.716499051010969</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7162540209932083</v>
+        <v>0.7162682743235063</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7149120597824469</v>
+        <v>0.7149288423189784</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7127756743605178</v>
+        <v>0.7127886916880457</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7119943581497682</v>
+        <v>0.7101747988889746</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7123435749431436</v>
+        <v>0.7101423146128194</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7125016115053904</v>
+        <v>0.710130179759056</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7148785199903257</v>
+        <v>0.7117792563678702</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7167238372314166</v>
+        <v>0.7128778071842978</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7182530789280553</v>
+        <v>0.7137404315892931</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7202337310955438</v>
+        <v>0.7147956664168289</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7215549986277876</v>
+        <v>0.7153563040204662</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7238214476102893</v>
+        <v>0.7165410710138556</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7214356949252634</v>
+        <v>0.7121798381909046</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7172063031481856</v>
+        <v>0.706710923083577</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7178301216278633</v>
+        <v>0.7064296403440813</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7065289904708</v>
+        <v>0.6957688759208173</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,15 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7040803820995383</v>
+        <v>0.6818563759208172</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>0.6679438759208171</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506936870414841</v>
+        <v>0.650690177726295</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514572249338763</v>
+        <v>0.6514554259040106</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525495989293637</v>
+        <v>0.6525464694907857</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497596774450648</v>
+        <v>0.6497584488859055</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464618362734504</v>
+        <v>0.6464605022574064</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431750181924085</v>
+        <v>0.6431735361335994</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408602163791272</v>
+        <v>0.6408586393278013</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398449372291126</v>
+        <v>0.6398433540252397</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425745632904312</v>
+        <v>0.6425665985487494</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433776403931011</v>
+        <v>0.6433727964490024</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414697875613448</v>
+        <v>0.6414649815876101</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385941846442058</v>
+        <v>0.6385893231087262</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406933220473794</v>
+        <v>0.6406791025918404</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6407545636660689</v>
+        <v>0.6407410509958229</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400814650342508</v>
+        <v>0.6400746019162602</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424267039332323</v>
+        <v>0.6424208139759988</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6453008196638926</v>
+        <v>0.6452897030085163</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472769081050771</v>
+        <v>0.6472627167783934</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468626026223137</v>
+        <v>0.6468507592537303</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469575870372426</v>
+        <v>0.6469506992842722</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.64585962321276</v>
+        <v>0.64584795051578</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6455406571678477</v>
+        <v>0.6455200754002555</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6467023554920559</v>
+        <v>0.6466676383659012</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.64474086082563</v>
+        <v>0.6446957116073488</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6442022810884583</v>
+        <v>0.6441448534501204</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6455555931106322</v>
+        <v>0.6454900997687757</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6462262515364058</v>
+        <v>0.6461574449643601</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6483088502380538</v>
+        <v>0.6482285422443186</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6547164849471512</v>
+        <v>0.6546473359898535</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6673308387182431</v>
+        <v>0.667234065844342</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6749007204749893</v>
+        <v>0.6747921577137534</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6905065679212972</v>
+        <v>0.6904116190286933</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6990372884207693</v>
+        <v>0.6989663612010387</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7014743330161524</v>
+        <v>0.7014012838779696</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7017615696993043</v>
+        <v>0.7016891806685018</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7085341665978069</v>
+        <v>0.70851634216267</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084314115204946</v>
+        <v>0.7084193297055446</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7105463125488277</v>
+        <v>0.7105633110906779</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7155783428046911</v>
+        <v>0.7156495474010431</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7156695772676559</v>
+        <v>0.7157437653182896</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7221071571142404</v>
+        <v>0.7222070294288665</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7188574466079646</v>
+        <v>0.7189002031396956</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7220783062669184</v>
+        <v>0.7221265680146274</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7217852505014495</v>
+        <v>0.7218249490211052</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7191474600071255</v>
+        <v>0.7191784432527109</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147344365270357</v>
+        <v>0.7147343578261525</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716499051010969</v>
+        <v>0.7165035341160519</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7162682743235063</v>
+        <v>0.7162819678935024</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7149288423189784</v>
+        <v>0.7149449194487487</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7127886916880457</v>
+        <v>0.7128010880820141</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7101747988889746</v>
+        <v>0.7101947870000864</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7101423146128194</v>
+        <v>0.710164646929353</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.710130179759056</v>
+        <v>0.7088653149543758</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7117792563678702</v>
+        <v>0.7101962506023594</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7128778071842978</v>
+        <v>0.7110707620316487</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7137404315892931</v>
+        <v>0.711485758119172</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7147956664168289</v>
+        <v>0.7120546457784362</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7153563040204662</v>
+        <v>0.7121339694263789</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7165410710138556</v>
+        <v>0.7127008726858701</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7121798381909046</v>
+        <v>0.7079170287872099</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.706710923083577</v>
+        <v>0.7024186592920468</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7064296403440813</v>
+        <v>0.7013579996942576</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6957688759208173</v>
+        <v>0.6914113203072458</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6818563759208172</v>
+        <v>0.6757831180298713</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,15 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6679438759208171</v>
+        <v>0.6618706180298712</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>0.6712188480333341</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7101962506023594</v>
+        <v>0.7101866917692341</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7110707620316487</v>
+        <v>0.7110198747253952</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.711485758119172</v>
+        <v>0.7112845658244616</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7120546457784362</v>
+        <v>0.7117070242585828</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7121339694263789</v>
+        <v>0.7116081257441393</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7127008726858701</v>
+        <v>0.7120074091277739</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7079170287872099</v>
+        <v>0.7070471118255734</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7024186592920468</v>
+        <v>0.7014747929324174</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7013579996942576</v>
+        <v>0.7002477840744328</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6914113203072458</v>
+        <v>0.690108139336275</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6757831180298713</v>
+        <v>0.6732227143040269</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6618706180298712</v>
+        <v>0.6593102143040268</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6712188480333341</v>
+        <v>0.663208102265287</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650690177726295</v>
+        <v>0.650686817674584</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514554259040106</v>
+        <v>0.6514537013053245</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525464694907857</v>
+        <v>0.6525434717462029</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497584488859055</v>
+        <v>0.6497572684187469</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464605022574064</v>
+        <v>0.6464592209858424</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431735361335994</v>
+        <v>0.6431721131815864</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408586393278013</v>
+        <v>0.6408571254863233</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398433540252397</v>
+        <v>0.6398418344432538</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425665985487494</v>
+        <v>0.6425589756020728</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433727964490024</v>
+        <v>0.6433681636972917</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414649815876101</v>
+        <v>0.6414603848701649</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385893231087262</v>
+        <v>0.6385846730225957</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406791025918404</v>
+        <v>0.6406654984373893</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6407410509958229</v>
+        <v>0.6407281139034285</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400746019162602</v>
+        <v>0.6400680262541117</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424208139759988</v>
+        <v>0.6424151846497431</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452897030085163</v>
+        <v>0.6452790678771171</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472627167783934</v>
+        <v>0.6472491201970942</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468507592537303</v>
+        <v>0.6468394057292619</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469506992842722</v>
+        <v>0.6469440988938961</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.64584795051578</v>
+        <v>0.6458367684193458</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6455200754002555</v>
+        <v>0.6455003718763965</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6466676383659012</v>
+        <v>0.6466343808006468</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6446957116073488</v>
+        <v>0.6446524500249428</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6441448534501204</v>
+        <v>0.6440898242174213</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6454900997687757</v>
+        <v>0.6454273209144994</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6461574449643601</v>
+        <v>0.6460914684161926</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6482285422443186</v>
+        <v>0.6481515401996711</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6546473359898535</v>
+        <v>0.654581105633568</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.667234065844342</v>
+        <v>0.6671413245208421</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6747921577137534</v>
+        <v>0.674688124939326</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6904116190286933</v>
+        <v>0.6903204899629067</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6989663612010387</v>
+        <v>0.6988982619780255</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7014012838779696</v>
+        <v>0.7013310945070915</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7016891806685018</v>
+        <v>0.7016195368775955</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.70851634216267</v>
+        <v>0.7084990579847852</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084193297055446</v>
+        <v>0.7084075297130799</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7105633110906779</v>
+        <v>0.7105793883814824</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7156495474010431</v>
+        <v>0.7157177714120158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7157437653182896</v>
+        <v>0.7158149121071891</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7222070294288665</v>
+        <v>0.7223029053814354</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7189002031396956</v>
+        <v>0.7189412377257486</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7221265680146274</v>
+        <v>0.7221729116714369</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7218249490211052</v>
+        <v>0.7218631341005777</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7191784432527109</v>
+        <v>0.7192082902689136</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147343578261525</v>
+        <v>0.7147343018958876</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165035341160519</v>
+        <v>0.7165078921523564</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7162819678935024</v>
+        <v>0.7162951338779159</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7149449194487487</v>
+        <v>0.714960334861801</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128010880820141</v>
+        <v>0.7128129065959079</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7101947870000864</v>
+        <v>0.7102138069188587</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710164646929353</v>
+        <v>0.7101859018425324</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7088653149543758</v>
+        <v>0.707767622755197</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7101866917692341</v>
+        <v>0.7088144393421566</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7110198747253952</v>
+        <v>0.7094325662382654</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7112845658244616</v>
+        <v>0.709208004584751</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7117070242585828</v>
+        <v>0.7091266035650623</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7116081257441393</v>
+        <v>0.7085212717507963</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7120074091277739</v>
+        <v>0.7083380174164281</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7070471118255734</v>
+        <v>0.7030895237202983</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7014747929324174</v>
+        <v>0.6975774573414544</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7002477840744328</v>
+        <v>0.6956468368389752</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.690108139336275</v>
+        <v>0.6860919791087737</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6732227143040269</v>
+        <v>0.670505578087904</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6593102143040268</v>
+        <v>0.659456597665004</v>
       </c>
     </row>
     <row r="107" spans="1:2">

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650686817674584</v>
+        <v>0.65068359756296</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514537013053245</v>
+        <v>0.6514520466170417</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525434717462029</v>
+        <v>0.6525405975569716</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497572684187469</v>
+        <v>0.6497561332949342</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464592209858424</v>
+        <v>0.6464579894094982</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431721131815864</v>
+        <v>0.6431707458859111</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408571254863233</v>
+        <v>0.6408556711443514</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398418344432538</v>
+        <v>0.6398403747381438</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425589756020728</v>
+        <v>0.6425516729271901</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433681636972917</v>
+        <v>0.6433637286371487</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414603848701649</v>
+        <v>0.6414559840487981</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385846730225957</v>
+        <v>0.6385802208991187</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406654984373893</v>
+        <v>0.6406524705432536</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6407281139034285</v>
+        <v>0.6407157164476945</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400680262541117</v>
+        <v>0.6400617203777379</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424151846497431</v>
+        <v>0.6424097990683563</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452790678771171</v>
+        <v>0.6452688837167906</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472491201970942</v>
+        <v>0.6472360818620645</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468394057292619</v>
+        <v>0.6468285123681652</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469440988938961</v>
+        <v>0.6469377683051025</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458367684193458</v>
+        <v>0.6458260467172348</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6455003718763965</v>
+        <v>0.6454814917058469</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6466343808006468</v>
+        <v>0.6466024928492238</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6446524500249428</v>
+        <v>0.6446109605192605</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6440898242174213</v>
+        <v>0.6440370468221606</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6454273209144994</v>
+        <v>0.6453670920775548</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6460914684161926</v>
+        <v>0.6460281519058835</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6481515401996711</v>
+        <v>0.6480776455159141</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.654581105633568</v>
+        <v>0.6545176138770581</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6671413245208421</v>
+        <v>0.667052369560213</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.674688124939326</v>
+        <v>0.6745883462391935</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6903204899629067</v>
+        <v>0.6902329566640271</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6988982619780255</v>
+        <v>0.6988328266174448</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7013310945070915</v>
+        <v>0.7012636024097649</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7016195368775955</v>
+        <v>0.7015524882548292</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7084990579847852</v>
+        <v>0.7084822934353255</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7084075297130799</v>
+        <v>0.708396007620601</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7105793883814824</v>
+        <v>0.7105946130014196</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7157177714120158</v>
+        <v>0.7157831969816466</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7158149121071891</v>
+        <v>0.7158831992670348</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7223029053814354</v>
+        <v>0.7223950184069972</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7189412377257486</v>
+        <v>0.7189806513350327</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7221729116714369</v>
+        <v>0.7222174479548954</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7218631341005777</v>
+        <v>0.7218998890130576</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7192082902689136</v>
+        <v>0.7192370608564679</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147343018958876</v>
+        <v>0.7147342662038343</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165078921523564</v>
+        <v>0.7165121291385947</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7162951338779159</v>
+        <v>0.7163078020419498</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.714960334861801</v>
+        <v>0.7149751287019911</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128129065959079</v>
+        <v>0.7128241864223264</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7102138069188587</v>
+        <v>0.710231925888539</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7101859018425324</v>
+        <v>0.7102061539211195</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.707767622755197</v>
+        <v>0.7077976089667306</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7088144393421566</v>
+        <v>0.7074699100811277</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7094325662382654</v>
+        <v>0.7078518216417187</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.709208004584751</v>
+        <v>0.707455463009252</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7091266035650623</v>
+        <v>0.7069187186519708</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7085212717507963</v>
+        <v>0.7058967671752779</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7083380174164281</v>
+        <v>0.7052176510359865</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7030895237202983</v>
+        <v>0.6997638517124538</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6975774573414544</v>
+        <v>0.6943294814273067</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6956468368389752</v>
+        <v>0.6922864767076817</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6860919791087737</v>
+        <v>0.6827568344013465</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.670505578087904</v>
+        <v>0.6678853353894629</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.659456597665004</v>
+        <v>0.658426679467828</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,15 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.663208102265287</v>
+        <v>0.6606324499206604</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>0.6567332298350506</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.65068359756296</v>
+        <v>0.6506805088285736</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514520466170417</v>
+        <v>0.6514504576768465</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525405975569716</v>
+        <v>0.6525378394412961</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497561332949342</v>
+        <v>0.6497550409695863</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464579894094982</v>
+        <v>0.6464568047081896</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431707458859111</v>
+        <v>0.6431694310582041</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408556711443514</v>
+        <v>0.6408542728751004</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398403747381438</v>
+        <v>0.6398389714519763</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425516729271901</v>
+        <v>0.6425446707696019</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433637286371487</v>
+        <v>0.6433594788932425</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414559840487981</v>
+        <v>0.6414517668757443</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385802208991187</v>
+        <v>0.6385759543735167</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406524705432536</v>
+        <v>0.6406399830991334</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6407157164476945</v>
+        <v>0.640703825613542</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400617203777379</v>
+        <v>0.6400556680347594</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424097990683563</v>
+        <v>0.6424046417706251</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452688837167906</v>
+        <v>0.6452591225004563</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472360818620645</v>
+        <v>0.6472235681912488</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468285123681652</v>
+        <v>0.6468180518325941</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469377683051025</v>
+        <v>0.6469316913548124</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458260467172348</v>
+        <v>0.6458157576263301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6454814917058469</v>
+        <v>0.6454633844676507</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6466024928492238</v>
+        <v>0.646571891790792</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6446109605192605</v>
+        <v>0.6445711367437019</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6440370468221606</v>
+        <v>0.6439863863522122</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6453670920775548</v>
+        <v>0.6453092617433196</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6460281519058835</v>
+        <v>0.6459673387070877</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6480776455159141</v>
+        <v>0.6480066750847799</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6545176138770581</v>
+        <v>0.6544566951479667</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.667052369560213</v>
+        <v>0.6669669751357925</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6745883462391935</v>
+        <v>0.6744925675182172</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6902329566640271</v>
+        <v>0.6901488121063659</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6988328266174448</v>
+        <v>0.6987699033072514</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7012636024097649</v>
+        <v>0.7011986569912907</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7015524882548292</v>
+        <v>0.7014878952006643</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7084822934353255</v>
+        <v>0.7084660285442701</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708396007620601</v>
+        <v>0.708384758781563</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7105946130014196</v>
+        <v>0.7106090471451485</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7157831969816466</v>
+        <v>0.7158459917997958</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7158831992670348</v>
+        <v>0.7159487943778867</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7223950184069972</v>
+        <v>0.7224835842461765</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7189806513350327</v>
+        <v>0.7190185372752942</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7222174479548954</v>
+        <v>0.7222602793375112</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7218998890130576</v>
+        <v>0.7219352911736412</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7192370608564679</v>
+        <v>0.7192648108267998</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147342662038343</v>
+        <v>0.7147342485052877</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165121291385947</v>
+        <v>0.7165162490490269</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163078020419498</v>
+        <v>0.7163199999620615</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7149751287019911</v>
+        <v>0.7149893379207601</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128241864223264</v>
+        <v>0.7128349633132198</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710231925888539</v>
+        <v>0.710249205168068</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7102061539211195</v>
+        <v>0.7102254711170872</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7077976089667306</v>
+        <v>0.7078262655304137</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7074699100811277</v>
+        <v>0.706780655008253</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7078518216417187</v>
+        <v>0.707061375515057</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.707455463009252</v>
+        <v>0.7065623102475878</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7069187186519708</v>
+        <v>0.7057850610339138</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7058967671752779</v>
+        <v>0.7045289186462709</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7052176510359865</v>
+        <v>0.7035882238792777</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6997638517124538</v>
+        <v>0.6982526102135538</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6943294814273067</v>
+        <v>0.6930978889512294</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6922864767076817</v>
+        <v>0.6910396924411855</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6827568344013465</v>
+        <v>0.6818390141101295</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6678853353894629</v>
+        <v>0.669213883745598</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.658426679467828</v>
+        <v>0.6619004850749882</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6606324499206604</v>
+        <v>0.6640909191234761</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6567332298350506</v>
+        <v>0.6661526033611456</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506805088285736</v>
+        <v>0.6506775435931267</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514504576768465</v>
+        <v>0.6514489306460853</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525378394412961</v>
+        <v>0.6525351905092964</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497550409695863</v>
+        <v>0.6497539890832396</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464568047081896</v>
+        <v>0.6464556642698508</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431694310582041</v>
+        <v>0.6431681657479028</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408542728751004</v>
+        <v>0.6408529275088909</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398389714519763</v>
+        <v>0.6398376213870265</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425446707696019</v>
+        <v>0.6425379509656143</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433594788932425</v>
+        <v>0.6433554031009621</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414517668757443</v>
+        <v>0.641447722102371</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385759543735167</v>
+        <v>0.6385718620887537</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406399830991334</v>
+        <v>0.6406280031982136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640703825613542</v>
+        <v>0.6406924110206677</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400556680347594</v>
+        <v>0.6400498542512425</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6424046417706251</v>
+        <v>0.6423996985733247</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452591225004563</v>
+        <v>0.6452497584716461</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472235681912488</v>
+        <v>0.6472115482348824</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468180518325941</v>
+        <v>0.6468079989016426</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469316913548124</v>
+        <v>0.646925853141926</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458157576263301</v>
+        <v>0.6458058755490705</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6454633844676507</v>
+        <v>0.6454460037655602</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646571891790792</v>
+        <v>0.6465425014208681</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6445711367437019</v>
+        <v>0.6445328806671555</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6439863863522122</v>
+        <v>0.6439377184200572</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6453092617433196</v>
+        <v>0.6452536901084023</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6459673387070877</v>
+        <v>0.6459088840934405</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6480066750847799</v>
+        <v>0.6479384598094938</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6544566951479667</v>
+        <v>0.6543981968926176</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6669669751357925</v>
+        <v>0.6668849329200259</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6744925675182172</v>
+        <v>0.6744005543979161</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6901488121063659</v>
+        <v>0.6900678647250931</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6987699033072514</v>
+        <v>0.6987093514365323</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7011986569912907</v>
+        <v>0.7011361185051186</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7014878952006643</v>
+        <v>0.7014256277186611</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7084660285442701</v>
+        <v>0.7084502440318055</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708384758781563</v>
+        <v>0.7083737779944225</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7106090471451485</v>
+        <v>0.7106227473281526</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7158459917997958</v>
+        <v>0.7159063104993566</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7159487943778867</v>
+        <v>0.7160118522878415</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7224835842461765</v>
+        <v>0.7225688025768162</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7190185372752942</v>
+        <v>0.7190549818980141</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7222602793375112</v>
+        <v>0.7223015007884681</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7219352911736412</v>
+        <v>0.7219694126305489</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7192648108267998</v>
+        <v>0.7192915923147752</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147342485052877</v>
+        <v>0.7147342468074114</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165162490490269</v>
+        <v>0.7165202557922701</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163199999620615</v>
+        <v>0.7163317532229296</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7149893379207601</v>
+        <v>0.7150029965892535</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128349633132198</v>
+        <v>0.7128452699467768</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710249205168068</v>
+        <v>0.7102657006743121</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7102254711170872</v>
+        <v>0.710243915474017</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7078262655304137</v>
+        <v>0.7078536774222057</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.706780655008253</v>
+        <v>0.7063327295108394</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.707061375515057</v>
+        <v>0.7065519799784346</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7065623102475878</v>
+        <v>0.7059729066890796</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7057850610339138</v>
+        <v>0.7050235615795305</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7045289186462709</v>
+        <v>0.7036036177361903</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7035882238792777</v>
+        <v>0.7024890642163149</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6982526102135538</v>
+        <v>0.6973487139762042</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6930978889512294</v>
+        <v>0.6924966582993128</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6910396924411855</v>
+        <v>0.6904665508930418</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6818390141101295</v>
+        <v>0.6816335926592486</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.669213883745598</v>
+        <v>0.6708989084831002</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6619004850749882</v>
+        <v>0.6650947850508195</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6640909191234761</v>
+        <v>0.6672550872301027</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6661526033611456</v>
+        <v>0.6712444831098811</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506775435931267</v>
+        <v>0.650671955133999</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514489306460853</v>
+        <v>0.6514460483950363</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525351905092964</v>
+        <v>0.6525301952586418</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497539890832396</v>
+        <v>0.6497519980199111</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464556642698508</v>
+        <v>0.6464535066640726</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431681657479028</v>
+        <v>0.6431657729387112</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408529275088909</v>
+        <v>0.6408503839535686</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398376213870265</v>
+        <v>0.6398350692899697</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425379509656143</v>
+        <v>0.642525292794671</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433554031009621</v>
+        <v>0.6433477323721836</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.641447722102371</v>
+        <v>0.6414401091690021</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385718620887537</v>
+        <v>0.6385641592609661</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406280031982136</v>
+        <v>0.6406054472211338</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406924110206677</v>
+        <v>0.6406709006973498</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400498542512425</v>
+        <v>0.6400388881340671</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423996985733247</v>
+        <v>0.6423904033775873</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452497584716461</v>
+        <v>0.6452321289803369</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6472115482348824</v>
+        <v>0.6471888773432954</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6468079989016426</v>
+        <v>0.6467890243746098</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646925853141926</v>
+        <v>0.646914838924696</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6458058755490705</v>
+        <v>0.645787239735464</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6454460037655602</v>
+        <v>0.6454132541964369</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6465425014208681</v>
+        <v>0.646487076813635</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6445328806671555</v>
+        <v>0.6444607163856555</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6439377184200572</v>
+        <v>0.6438459093378677</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6452536901084023</v>
+        <v>0.6451488157745613</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6459088840934405</v>
+        <v>0.6457985251198516</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6479384598094938</v>
+        <v>0.6478096807050866</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6543981968926176</v>
+        <v>0.6542879093294586</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6668849329200259</v>
+        <v>0.6667301495680475</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6744005543979161</v>
+        <v>0.6742269750498762</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6900678647250931</v>
+        <v>0.6899148642618493</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6987093514365323</v>
+        <v>0.6985948496645518</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7011361185051186</v>
+        <v>0.7010177520167262</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7014256277186611</v>
+        <v>0.7013075928483208</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7084502440318055</v>
+        <v>0.7084200425648151</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083737779944225</v>
+        <v>0.7083525978021479</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7106227473281526</v>
+        <v>0.7106481471001711</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7159063104993566</v>
+        <v>0.7160200800869384</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7160118522878415</v>
+        <v>0.7161309191664585</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7225688025768162</v>
+        <v>0.7227299236915401</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7190549818980141</v>
+        <v>0.7191238615258697</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7223015007884681</v>
+        <v>0.7223794601742436</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7219694126305489</v>
+        <v>0.7220340774171192</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7192915923147752</v>
+        <v>0.7193424416895839</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147342468074114</v>
+        <v>0.7147342845203745</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165202557922701</v>
+        <v>0.7165279449915596</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163317532229296</v>
+        <v>0.716354019185053</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150029965892535</v>
+        <v>0.7150287857838052</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128452699467768</v>
+        <v>0.712864589673959</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7102657006743121</v>
+        <v>0.7102965406285682</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710243915474017</v>
+        <v>0.7102784079492404</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7078536774222057</v>
+        <v>0.7079050728677903</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7063327295108394</v>
+        <v>0.70550500899738</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7065519799784346</v>
+        <v>0.7056075999910612</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7059729066890796</v>
+        <v>0.7048793759101692</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7050235615795305</v>
+        <v>0.7036164910094885</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7036036177361903</v>
+        <v>0.7019090499991693</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7024890642163149</v>
+        <v>0.7005186281310468</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6973487139762042</v>
+        <v>0.6956810098139022</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6924966582993128</v>
+        <v>0.6912380576721308</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6904665508930418</v>
+        <v>0.6891834236205764</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6816335926592486</v>
+        <v>0.6811245844978864</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6708989084831002</v>
+        <v>0.6725889730942043</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6650947850508195</v>
+        <v>0.6681828856772351</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6672550872301027</v>
+        <v>0.6701036586375013</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6712444831098811</v>
+        <v>0.6735758154328415</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650671955133999</v>
+        <v>0.6506693190105861</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514460483950363</v>
+        <v>0.6514446868551191</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525301952586418</v>
+        <v>0.652527837635248</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497519980199111</v>
+        <v>0.6497510549115214</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464535066640726</v>
+        <v>0.6464524851542418</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431657729387112</v>
+        <v>0.6431646405441513</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408503839535686</v>
+        <v>0.6408491805109231</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398350692899697</v>
+        <v>0.6398338619607379</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642525292794671</v>
+        <v>0.6425193247310785</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433477323721836</v>
+        <v>0.6433441189086299</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414401091690021</v>
+        <v>0.6414365226666074</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385641592609661</v>
+        <v>0.6385605301952344</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6406054472211338</v>
+        <v>0.6405948174193867</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406709006973498</v>
+        <v>0.6406607552085165</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400388881340671</v>
+        <v>0.6400337112042769</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423904033775873</v>
+        <v>0.6423860283149849</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452321289803369</v>
+        <v>0.6452238214609046</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471888773432954</v>
+        <v>0.6471781755386968</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467890243746098</v>
+        <v>0.6467800612264288</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646914838924696</v>
+        <v>0.6469096384098079</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645787239735464</v>
+        <v>0.6457784439554866</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6454132541964369</v>
+        <v>0.6453978093444253</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646487076813635</v>
+        <v>0.6464609174436688</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6444607163856555</v>
+        <v>0.6444266469787532</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6438459093378677</v>
+        <v>0.6438025635573982</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6451488157745613</v>
+        <v>0.6450992826799442</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6457985251198516</v>
+        <v>0.6457463818255715</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6478096807050866</v>
+        <v>0.6477488376825917</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6542879093294586</v>
+        <v>0.6542358694524066</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6667301495680475</v>
+        <v>0.6666570652907992</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6742269750498762</v>
+        <v>0.6741450228761261</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6899148642618493</v>
+        <v>0.6898424934450595</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6985948496645518</v>
+        <v>0.6985406660337999</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7010177520167262</v>
+        <v>0.7009616907325389</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7013075928483208</v>
+        <v>0.7012516067527784</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7084200425648151</v>
+        <v>0.7084055906007993</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083525978021479</v>
+        <v>0.7083423863471905</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7106481471001711</v>
+        <v>0.7106599364988242</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7160200800869384</v>
+        <v>0.71607378543767</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7161309191664585</v>
+        <v>0.716187184136609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7227299236915401</v>
+        <v>0.7228061578686122</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7191238615258697</v>
+        <v>0.7191564397940661</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7223794601742436</v>
+        <v>0.7224163561780481</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7220340774171192</v>
+        <v>0.7220647418044677</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7193424416895839</v>
+        <v>0.7193665979130807</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147342845203745</v>
+        <v>0.7147343209469448</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165279449915596</v>
+        <v>0.716531634812571</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716354019185053</v>
+        <v>0.7163645745922593</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150287857838052</v>
+        <v>0.7150409723832951</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.712864589673959</v>
+        <v>0.7128736554555685</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7102965406285682</v>
+        <v>0.710310974925657</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7102784079492404</v>
+        <v>0.7102945558274343</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7079050728677903</v>
+        <v>0.7079291941490597</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.70550500899738</v>
+        <v>0.7049629987146079</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7056075999910612</v>
+        <v>0.704990095180669</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7048793759101692</v>
+        <v>0.7041832439751036</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7036164910094885</v>
+        <v>0.702740170550648</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7019090499991693</v>
+        <v>0.7008787406632986</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7005186281310468</v>
+        <v>0.6993397727304084</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6956810098139022</v>
+        <v>0.6945704185189121</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6912380576721308</v>
+        <v>0.6902295915609999</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6891834236205764</v>
+        <v>0.6883679462820527</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6811245844978864</v>
+        <v>0.6806335790619007</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6725889730942043</v>
+        <v>0.672594615178943</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6681828856772351</v>
+        <v>0.6686479141255051</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6701036586375013</v>
+        <v>0.6700249114731559</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6735758154328415</v>
+        <v>0.6724981601391599</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506693190105861</v>
+        <v>0.6506667804872555</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514446868551191</v>
+        <v>0.6514433745392839</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652527837635248</v>
+        <v>0.6525255665007264</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497510549115214</v>
+        <v>0.649750144354179</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464524851542418</v>
+        <v>0.6464514991940953</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431646405441513</v>
+        <v>0.6431635478428205</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408491805109231</v>
+        <v>0.640848019428591</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398338619607379</v>
+        <v>0.6398326972223024</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425193247310785</v>
+        <v>0.6425135793957421</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433441189086299</v>
+        <v>0.6433406421937542</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414365226666074</v>
+        <v>0.6414330717320794</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385605301952344</v>
+        <v>0.6385570381767341</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405948174193867</v>
+        <v>0.6405845872842199</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406607552085165</v>
+        <v>0.6406509860623294</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400337112042769</v>
+        <v>0.6400287234581669</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423860283149849</v>
+        <v>0.6423818210348334</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452238214609046</v>
+        <v>0.6452158266827189</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471781755386968</v>
+        <v>0.6471678653331996</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467800612264288</v>
+        <v>0.6467714222783294</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469096384098079</v>
+        <v>0.6469046274311623</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457784439554866</v>
+        <v>0.6457699707883733</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453978093444253</v>
+        <v>0.6453829384753531</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6464609174436688</v>
+        <v>0.6464357175609968</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6444266469787532</v>
+        <v>0.6443938216793509</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6438025635573982</v>
+        <v>0.6437607995535828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6450992826799442</v>
+        <v>0.6450515458352734</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6457463818255715</v>
+        <v>0.6456961175609754</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6477488376825917</v>
+        <v>0.6476901894611466</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6542358694524066</v>
+        <v>0.6541857470454919</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6666570652907992</v>
+        <v>0.6665866444597035</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6741450228761261</v>
+        <v>0.6740660616136882</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6898424934450595</v>
+        <v>0.6897726822018639</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6985406660337999</v>
+        <v>0.6984883848529121</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7009616907325389</v>
+        <v>0.7009075683625098</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7012516067527784</v>
+        <v>0.7011975075772262</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7084055906007993</v>
+        <v>0.7083915489843184</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083423863471905</v>
+        <v>0.7083324190138873</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7106599364988242</v>
+        <v>0.7106711724456856</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.71607378543767</v>
+        <v>0.716125525452425</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.716187184136609</v>
+        <v>0.7162414256868307</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7228061578686122</v>
+        <v>0.7228797095357147</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7191564397940661</v>
+        <v>0.7191878642287127</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7224163561780481</v>
+        <v>0.7224519594065899</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7220647418044677</v>
+        <v>0.7220943682998907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7193665979130807</v>
+        <v>0.7193899627841496</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147343209469448</v>
+        <v>0.7147343673623416</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716531634812571</v>
+        <v>0.7165352261820188</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163645745922593</v>
+        <v>0.7163747710211489</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150409723832951</v>
+        <v>0.7150527209909491</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128736554555685</v>
+        <v>0.7128823568231335</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710310974925657</v>
+        <v>0.710324805964927</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7102945558274343</v>
+        <v>0.7103100312887536</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7079291941490597</v>
+        <v>0.7079523473712329</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7049629987146079</v>
+        <v>0.7050017887781148</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.704990095180669</v>
+        <v>0.7047009199967056</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7041832439751036</v>
+        <v>0.7040013302771836</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.702740170550648</v>
+        <v>0.7026251067899925</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7008787406632986</v>
+        <v>0.7008210429429487</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6993397727304084</v>
+        <v>0.6993259249040045</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6945704185189121</v>
+        <v>0.6947432933382145</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6902295915609999</v>
+        <v>0.6907414113733626</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6883679462820527</v>
+        <v>0.6888972009510055</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6806335790619007</v>
+        <v>0.6818716629487296</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.672594615178943</v>
+        <v>0.6748575044284377</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6686479141255051</v>
+        <v>0.671390823096816</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6700249114731559</v>
+        <v>0.6725257461653649</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,15 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6724981601391599</v>
+        <v>0.6767280976750557</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>0.6885405976750558</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506667804872555</v>
+        <v>0.6506643342427796</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514433745392839</v>
+        <v>0.6514421088275718</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525255665007264</v>
+        <v>0.6525233771828848</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649750144354179</v>
+        <v>0.6497492647001994</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464514991940953</v>
+        <v>0.6464505469674202</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431635478428205</v>
+        <v>0.643162492790649</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640848019428591</v>
+        <v>0.6408468985152359</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398326972223024</v>
+        <v>0.6398315728662383</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425135793957421</v>
+        <v>0.6425080445556943</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433406421937542</v>
+        <v>0.6433372946160931</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414330717320794</v>
+        <v>0.6414297488281266</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385570381767341</v>
+        <v>0.638553675592726</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405845872842199</v>
+        <v>0.6405747347134605</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406509860623294</v>
+        <v>0.6406415727290147</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400287234581669</v>
+        <v>0.640023914720111</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423818210348334</v>
+        <v>0.6423777720839868</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452158266827189</v>
+        <v>0.6452081273425838</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471678653331996</v>
+        <v>0.6471579256716223</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467714222783294</v>
+        <v>0.6467630902935917</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6469046274311623</v>
+        <v>0.6468997958363495</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457699707883733</v>
+        <v>0.6457618028426284</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453829384753531</v>
+        <v>0.6453686102415269</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6464357175609968</v>
+        <v>0.6464114254151295</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6443938216793509</v>
+        <v>0.6443621737355959</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6437607995535828</v>
+        <v>0.6437205325599193</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6450515458352734</v>
+        <v>0.6450055096497085</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6456961175609754</v>
+        <v>0.6456476330333343</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6476901894611466</v>
+        <v>0.6476336200116777</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6541857470454919</v>
+        <v>0.6541374384691366</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6665866444597035</v>
+        <v>0.6665187447832329</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6740660616136882</v>
+        <v>0.6739899312614511</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6897726822018639</v>
+        <v>0.6897052979338612</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6984883848529121</v>
+        <v>0.6984379083914215</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7009075683625098</v>
+        <v>0.7008552869909682</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7011975075772262</v>
+        <v>0.7011452028850564</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083915489843184</v>
+        <v>0.708377901953181</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083324190138873</v>
+        <v>0.7083226894686871</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7106711724456856</v>
+        <v>0.710681890920747</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.716125525452425</v>
+        <v>0.7161754055604341</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7162414256868307</v>
+        <v>0.7162937503294835</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7228797095357147</v>
+        <v>0.7229507170757945</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7191878642287127</v>
+        <v>0.7192181946278273</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7224519594065899</v>
+        <v>0.7224863360278322</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7220943682998907</v>
+        <v>0.7221230080092635</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7193899627841496</v>
+        <v>0.7194125738782922</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147343673623416</v>
+        <v>0.7147344226442569</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165352261820188</v>
+        <v>0.7165387225121356</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163747710211489</v>
+        <v>0.7163846264036043</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150527209909491</v>
+        <v>0.7150640548502243</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128823568231335</v>
+        <v>0.7128907151969222</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710324805964927</v>
+        <v>0.7103380701454134</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103100312887536</v>
+        <v>0.7103248747729778</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7079523473712329</v>
+        <v>0.7079745887788196</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7050017887781148</v>
+        <v>0.7050392294947658</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7047009199967056</v>
+        <v>0.7044292362247271</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7040013302771836</v>
+        <v>0.7038250133003771</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026251067899925</v>
+        <v>0.7025089266693134</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7008210429429487</v>
+        <v>0.7007572035162795</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6993259249040045</v>
+        <v>0.6993022803766915</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6947432933382145</v>
+        <v>0.6948859042930919</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6907414113733626</v>
+        <v>0.6911773681790094</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6888972009510055</v>
+        <v>0.6893510815937485</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6818716629487296</v>
+        <v>0.6829341271139017</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6748575044284377</v>
+        <v>0.6767332088110315</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.671390823096816</v>
+        <v>0.6736325985299124</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6725257461653649</v>
+        <v>0.6745385187319594</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6767280976750557</v>
+        <v>0.6798823710533333</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6885405976750558</v>
+        <v>0.6916948710533334</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7038250133003771</v>
+        <v>0.7038238762023268</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025089266693134</v>
+        <v>0.7025008622130591</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7007572035162795</v>
+        <v>0.7007344724855968</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6993022803766915</v>
+        <v>0.6992654287617571</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6948859042930919</v>
+        <v>0.6948497254763399</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6911773681790094</v>
+        <v>0.6911255377968706</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6893510815937485</v>
+        <v>0.6893015506252496</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6829341271139017</v>
+        <v>0.682695638022067</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6767332088110315</v>
+        <v>0.6763335105954126</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6736325985299124</v>
+        <v>0.6732201867850639</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6745385187319594</v>
+        <v>0.6755435637497953</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6798823710533333</v>
+        <v>0.6798261543797178</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6916948710533334</v>
+        <v>0.6916386543797179</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7038238762023268</v>
+        <v>0.7038243917140572</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025008622130591</v>
+        <v>0.7025109071581062</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7007344724855968</v>
+        <v>0.7007600847297411</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6992654287617571</v>
+        <v>0.6993022881228277</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6948497254763399</v>
+        <v>0.694894475459614</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6911255377968706</v>
+        <v>0.6911684958830284</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6893015506252496</v>
+        <v>0.6895097248230856</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.682695638022067</v>
+        <v>0.682852433603174</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6763335105954126</v>
+        <v>0.6767195879055642</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6732201867850639</v>
+        <v>0.6731947955373442</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6755435637497953</v>
+        <v>0.6756542358981773</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6798261543797178</v>
+        <v>0.6798679665811773</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6916386543797179</v>
+        <v>0.6916804665811774</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506643342427796</v>
+        <v>0.6506619753358089</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514421088275718</v>
+        <v>0.6514408872825679</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525233771828848</v>
+        <v>0.6525212653400151</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497492647001994</v>
+        <v>0.6497484144105998</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464505469674202</v>
+        <v>0.6464496267790828</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643162492790649</v>
+        <v>0.6431614734810429</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408468985152359</v>
+        <v>0.6408458157276322</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398315728662383</v>
+        <v>0.6398304868337619</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425080445556943</v>
+        <v>0.6425027088572154</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433372946160931</v>
+        <v>0.6433340691182874</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414297488281266</v>
+        <v>0.6414265469655803</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.638553675592726</v>
+        <v>0.6385504353836107</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405747347134605</v>
+        <v>0.640565239203629</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406415727290147</v>
+        <v>0.6406324961433332</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.640023914720111</v>
+        <v>0.6400192755308093</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423777720839868</v>
+        <v>0.6423738727052052</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452081273425838</v>
+        <v>0.6452007073885637</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471579256716223</v>
+        <v>0.6471483369779761</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467630902935917</v>
+        <v>0.6467550492332664</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468997958363495</v>
+        <v>0.6468951341836517</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457618028426284</v>
+        <v>0.6457539239521422</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453686102415269</v>
+        <v>0.6453547955327308</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6464114254151295</v>
+        <v>0.6463879929053851</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6443621737355959</v>
+        <v>0.644331641075118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6437205325599193</v>
+        <v>0.6436816837419981</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6450055096497085</v>
+        <v>0.6449610851707379</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6456476330333343</v>
+        <v>0.6456008357913772</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6476336200116777</v>
+        <v>0.6475790212984832</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6541374384691366</v>
+        <v>0.6540908473917444</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6665187447832329</v>
+        <v>0.6664532338797271</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6739899312614511</v>
+        <v>0.6739164829756688</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6897052979338612</v>
+        <v>0.6896402169876237</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6984379083914215</v>
+        <v>0.698389145447685</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7008552869909682</v>
+        <v>0.7008047551169342</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7011452028850564</v>
+        <v>0.7010946060791159</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708377901953181</v>
+        <v>0.7083646344142219</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083226894686871</v>
+        <v>0.7083131913575968</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710681890920747</v>
+        <v>0.7106921249617808</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7161754055604341</v>
+        <v>0.7162235238175978</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7162937503294835</v>
+        <v>0.7163442572794905</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7229507170757945</v>
+        <v>0.7230193095675448</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7192181946278273</v>
+        <v>0.7192474867583666</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7224863360278322</v>
+        <v>0.7225195478134786</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7221230080092635</v>
+        <v>0.7221507087899089</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7194125738782922</v>
+        <v>0.7194344664798611</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147344226442569</v>
+        <v>0.7147344857884781</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165387225121356</v>
+        <v>0.7165421271017287</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163846264036043</v>
+        <v>0.7163941575010302</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150640548502243</v>
+        <v>0.7150749955849438</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128907151969222</v>
+        <v>0.7128987503596662</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103380701454134</v>
+        <v>0.7103508010360067</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103248747729778</v>
+        <v>0.7103391235845635</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7079745887788196</v>
+        <v>0.7079959703977423</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7050392294947658</v>
+        <v>0.7050753889022877</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7044292362247271</v>
+        <v>0.7041359190880487</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7038243917140572</v>
+        <v>0.7036090892653124</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025109071581062</v>
+        <v>0.7023550187251695</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7007600847297411</v>
+        <v>0.7006535652141973</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6993022881228277</v>
+        <v>0.6992298218012324</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.694894475459614</v>
+        <v>0.6949587755003834</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6911684958830284</v>
+        <v>0.6914722306422973</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6895097248230856</v>
+        <v>0.6899612268347968</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.682852433603174</v>
+        <v>0.6837865323808388</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6767195879055642</v>
+        <v>0.6784440442625088</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6731947955373442</v>
+        <v>0.6748415584987273</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6756542358981773</v>
+        <v>0.6770049391941317</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6798679665811773</v>
+        <v>0.6820549747742437</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6916804665811774</v>
+        <v>0.6987202224363565</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506619753358089</v>
+        <v>0.6506596991715712</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514408872825679</v>
+        <v>0.6514397076337883</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525212653400151</v>
+        <v>0.6525192269321872</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497484144105998</v>
+        <v>0.6497475920463393</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464496267790828</v>
+        <v>0.6464487370451549</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431614734810429</v>
+        <v>0.6431604881335624</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408458157276322</v>
+        <v>0.6408447691584035</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398304868337619</v>
+        <v>0.6398294372033065</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6425027088572154</v>
+        <v>0.6424975617482727</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433340691182874</v>
+        <v>0.6433309591476007</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414265469655803</v>
+        <v>0.6414234596544952</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385504353836107</v>
+        <v>0.6385473109936227</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640565239203629</v>
+        <v>0.6405560817080881</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406324961433332</v>
+        <v>0.6406237385764451</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400192755308093</v>
+        <v>0.6400147970853926</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423738727052052</v>
+        <v>0.6423701147743701</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6452007073885637</v>
+        <v>0.6451935519090612</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471483369779761</v>
+        <v>0.6471390810281241</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467550492332664</v>
+        <v>0.6467472841541573</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468951341836517</v>
+        <v>0.6468906336810686</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457539239521422</v>
+        <v>0.6457463190703564</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453547955327308</v>
+        <v>0.6453414672804665</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6463879929053851</v>
+        <v>0.6463653752652159</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.644331641075118</v>
+        <v>0.6443021659030606</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6436816837419981</v>
+        <v>0.6436441796890728</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6449610851707379</v>
+        <v>0.6449181895200014</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6456008357913772</v>
+        <v>0.6455556396488882</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6475790212984832</v>
+        <v>0.6475262926062806</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6540908473917444</v>
+        <v>0.6540458841591548</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6664532338797271</v>
+        <v>0.6663899884335772</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6739164829756688</v>
+        <v>0.6738455781187858</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6896402169876237</v>
+        <v>0.6895773239180263</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.698389145447685</v>
+        <v>0.6983420108172664</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7008047551169342</v>
+        <v>0.7007558871434418</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7010946060791159</v>
+        <v>0.7010456359570328</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083646344142219</v>
+        <v>0.7083517319231145</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083131913575968</v>
+        <v>0.7083039183470243</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7106921249617808</v>
+        <v>0.7107019049514658</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7162235238175978</v>
+        <v>0.7162699715370304</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7163442572794905</v>
+        <v>0.7163930390645299</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7230193095675448</v>
+        <v>0.7230856075498333</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7192474867583666</v>
+        <v>0.7192757926875586</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7225195478134786</v>
+        <v>0.7225516524942561</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7221507087899089</v>
+        <v>0.7221775154998513</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7194344664798611</v>
+        <v>0.7194556737493822</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147344857884781</v>
+        <v>0.7147345558955203</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165421271017287</v>
+        <v>0.7165454431355689</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7163941575010302</v>
+        <v>0.7164033799980342</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150749955849438</v>
+        <v>0.7150855633382712</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7128987503596662</v>
+        <v>0.7129064806092946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103508010360067</v>
+        <v>0.7103630296421078</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103391235845635</v>
+        <v>0.7103528121873228</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7079959703977423</v>
+        <v>0.7080165404191873</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7050753889022877</v>
+        <v>0.7051103306205531</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041359190880487</v>
+        <v>0.7037396626963036</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7036090892653124</v>
+        <v>0.703262325414026</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023550187251695</v>
+        <v>0.702060967152439</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7006535652141973</v>
+        <v>0.7003965103868864</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6992298218012324</v>
+        <v>0.6989827386189444</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6949587755003834</v>
+        <v>0.6948036342998012</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6914722306422973</v>
+        <v>0.6916410646927591</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6899612268347968</v>
+        <v>0.6900353742133918</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6837865323808388</v>
+        <v>0.6844220225544356</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6784440442625088</v>
+        <v>0.6791678425934214</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6748415584987273</v>
+        <v>0.6761059262502426</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6770049391941317</v>
+        <v>0.6766602767048702</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6820549747742437</v>
+        <v>0.6831585208889511</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6987202224363565</v>
+        <v>0.6968002073947058</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.703262325414026</v>
+        <v>0.703261782875759</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.702060967152439</v>
+        <v>0.702062677161398</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7003965103868864</v>
+        <v>0.7003989768893573</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6989827386189444</v>
+        <v>0.6989827047687348</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6948036342998012</v>
+        <v>0.6948109053283299</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6916410646927591</v>
+        <v>0.6916334853995509</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6900353742133918</v>
+        <v>0.6901698406630465</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6844220225544356</v>
+        <v>0.6843529544194205</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6791678425934214</v>
+        <v>0.6791562540916938</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6761059262502426</v>
+        <v>0.6757508085647074</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6766602767048702</v>
+        <v>0.67755219539926</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6831585208889511</v>
+        <v>0.6831474068680056</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6968002073947058</v>
+        <v>0.6967826255997415</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506596991715712</v>
+        <v>0.6506575014720115</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514397076337883</v>
+        <v>0.6514385677636403</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525192269321872</v>
+        <v>0.6525172581954842</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497475920463393</v>
+        <v>0.6497467962603872</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464487370451549</v>
+        <v>0.6464478762839864</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431604881335624</v>
+        <v>0.6431595350836974</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408447691584035</v>
+        <v>0.6408437570249518</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398294372033065</v>
+        <v>0.6398284221793126</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424975617482727</v>
+        <v>0.642492593409024</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433309591476007</v>
+        <v>0.6433279586116436</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414234596544952</v>
+        <v>0.6414204808603909</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385473109936227</v>
+        <v>0.6385442963267033</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405560817080881</v>
+        <v>0.6405472445100197</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406237385764451</v>
+        <v>0.6406152835209794</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400147970853926</v>
+        <v>0.6400104711778315</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423701147743701</v>
+        <v>0.6423664907443662</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451935519090612</v>
+        <v>0.6451866470334728</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471390810281241</v>
+        <v>0.6471301408353397</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467472841541573</v>
+        <v>0.6467397811170315</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468906336810686</v>
+        <v>0.6468862861315005</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457463190703564</v>
+        <v>0.6457389741751876</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453414672804665</v>
+        <v>0.6453286002823547</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6463653752652159</v>
+        <v>0.6463435307786891</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6443021659030606</v>
+        <v>0.6442736943407457</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6436441796890728</v>
+        <v>0.6436079519568845</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6449181895200014</v>
+        <v>0.6448767453854629</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6455556396488882</v>
+        <v>0.6455119641653232</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6475262926062806</v>
+        <v>0.6474753399337344</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6540458841591548</v>
+        <v>0.6540024652280315</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6663899884335772</v>
+        <v>0.6663288934357714</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6738455781187858</v>
+        <v>0.6737770874034652</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6895773239180263</v>
+        <v>0.6895165108226735</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6983420108172664</v>
+        <v>0.6982964248119512</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7007558871434418</v>
+        <v>0.7007086029142318</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7010456359570328</v>
+        <v>0.700998216305552</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083517319231145</v>
+        <v>0.7083391806624656</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7083039183470243</v>
+        <v>0.7082948641566189</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107019049514658</v>
+        <v>0.710711258872176</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7162699715370304</v>
+        <v>0.7163148338562815</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7163930390645299</v>
+        <v>0.7164401820754398</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7230856075498333</v>
+        <v>0.7231497237124586</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7192757926875586</v>
+        <v>0.7193031610823652</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7225516524942561</v>
+        <v>0.7225827040816968</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7221775154998513</v>
+        <v>0.7222034702249974</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7194556737493822</v>
+        <v>0.7194762268769452</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147345558955203</v>
+        <v>0.7147346321589179</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165454431355689</v>
+        <v>0.7165486736848439</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164033799980342</v>
+        <v>0.7164123085872766</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150855633382712</v>
+        <v>0.7150957768975879</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129064806092946</v>
+        <v>0.7129139228949717</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103630296421078</v>
+        <v>0.7103747846429895</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103528121873228</v>
+        <v>0.7103659724667956</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080165404191873</v>
+        <v>0.7080363435427048</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7051103306205531</v>
+        <v>0.7051441141974494</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037396626963036</v>
+        <v>0.7033785953553702</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.703261782875759</v>
+        <v>0.7029483884179257</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.702062677161398</v>
+        <v>0.7018109883202001</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7003989768893573</v>
+        <v>0.7002030124914381</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6989827047687348</v>
+        <v>0.6988005491407572</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6948109053283299</v>
+        <v>0.6948328671437793</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6916334853995509</v>
+        <v>0.6919025081357071</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6901698406630465</v>
+        <v>0.6904804690650899</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6843529544194205</v>
+        <v>0.6850002132863007</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6791562540916938</v>
+        <v>0.6800222470378564</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6757508085647074</v>
+        <v>0.6768456398541574</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.67755219539926</v>
+        <v>0.6784138863672351</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6831474068680056</v>
+        <v>0.68342336139132</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6967826255997415</v>
+        <v>0.6943447343481702</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506575014720115</v>
+        <v>0.650653325780034</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514385677636403</v>
+        <v>0.6514363995786774</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525172581954842</v>
+        <v>0.6525135159231248</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497467962603872</v>
+        <v>0.6497452794528347</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464478762839864</v>
+        <v>0.6464462362169465</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431595350836974</v>
+        <v>0.6431577197437766</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408437570249518</v>
+        <v>0.6408418294997753</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398284221793126</v>
+        <v>0.6398264893386677</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642492593409024</v>
+        <v>0.6424831570531035</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433279586116436</v>
+        <v>0.6433222635419464</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414204808603909</v>
+        <v>0.6414148267310882</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385442963267033</v>
+        <v>0.6385385738429495</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405472445100197</v>
+        <v>0.6405304661158091</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406152835209794</v>
+        <v>0.640599220412754</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400104711778315</v>
+        <v>0.6400022468511462</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423664907443662</v>
+        <v>0.6423596167870058</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451866470334728</v>
+        <v>0.645173538290685</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471301408353397</v>
+        <v>0.6471131453530204</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467397811170315</v>
+        <v>0.6467255099432281</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468862861315005</v>
+        <v>0.6468780197861077</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457389741751876</v>
+        <v>0.6457250128737582</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453286002823547</v>
+        <v>0.6453041576385257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6463435307786891</v>
+        <v>0.6463020081503545</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6442736943407457</v>
+        <v>0.6442195641909325</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6436079519568845</v>
+        <v>0.6435390740793056</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6448767453854629</v>
+        <v>0.6447979275453017</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6455119641653232</v>
+        <v>0.6454288793732748</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6474753399337344</v>
+        <v>0.647378416979543</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6540024652280315</v>
+        <v>0.6539199536405215</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6663288934357714</v>
+        <v>0.6662127322400924</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6737770874034652</v>
+        <v>0.673646873444155</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6895165108226735</v>
+        <v>0.6894007271014345</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6982964248119512</v>
+        <v>0.6982096049301865</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7007086029142318</v>
+        <v>0.7006184897797183</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.700998216305552</v>
+        <v>0.7009077463159799</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083391806624656</v>
+        <v>0.7083150795591137</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082948641566189</v>
+        <v>0.7082773875328472</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710711258872176</v>
+        <v>0.7107287897692828</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7163148338562815</v>
+        <v>0.7164001149838445</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7164401820754398</v>
+        <v>0.7165298695904965</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7231497237124586</v>
+        <v>0.7232718257851722</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7193031610823652</v>
+        <v>0.7193552645364905</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7225827040816968</v>
+        <v>0.7226418471511407</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7222034702249974</v>
+        <v>0.7222529794297221</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7194762268769452</v>
+        <v>0.7195154864471991</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147346321589179</v>
+        <v>0.7147348003335967</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165486736848439</v>
+        <v>0.7165548900548635</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164123085872766</v>
+        <v>0.7164293383081364</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150957768975879</v>
+        <v>0.7151152104682759</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129139228949717</v>
+        <v>0.7129280053430258</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103747846429895</v>
+        <v>0.7103969781633719</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103659724667956</v>
+        <v>0.7103908240864141</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080363435427048</v>
+        <v>0.7080738122479879</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7051441141974494</v>
+        <v>0.7052084266182437</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7033785953553702</v>
+        <v>0.7032690413308473</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029483884179257</v>
+        <v>0.7026629786824388</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7018109883202001</v>
+        <v>0.7017027609062341</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7002030124914381</v>
+        <v>0.7002810899218872</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6988005491407572</v>
+        <v>0.6991086218378579</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6948328671437793</v>
+        <v>0.6954849575913815</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6919025081357071</v>
+        <v>0.6928808227410557</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6904804690650899</v>
+        <v>0.6915002351127101</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6850002132863007</v>
+        <v>0.6866048350035869</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6800222470378564</v>
+        <v>0.6821924862351789</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6768456398541574</v>
+        <v>0.6792632113059652</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6784138863672351</v>
+        <v>0.6804465283849818</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.68342336139132</v>
+        <v>0.6846173155630952</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6943447343481702</v>
+        <v>0.6930005183188307</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>0.6867539875929403</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650653325780034</v>
+        <v>0.6506575014720115</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514363995786774</v>
+        <v>0.6514385677636403</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525135159231248</v>
+        <v>0.6525172581954842</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497452794528347</v>
+        <v>0.6497467962603872</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464462362169465</v>
+        <v>0.6464478762839864</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431577197437766</v>
+        <v>0.6431595350836974</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408418294997753</v>
+        <v>0.6408437570249518</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398264893386677</v>
+        <v>0.6398284221793126</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424831570531035</v>
+        <v>0.642492593409024</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433222635419464</v>
+        <v>0.6433279586116436</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414148267310882</v>
+        <v>0.6414204808603909</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385385738429495</v>
+        <v>0.6385442963267033</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405304661158091</v>
+        <v>0.6405472445100197</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640599220412754</v>
+        <v>0.6406152835209794</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400022468511462</v>
+        <v>0.6400104711778315</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423596167870058</v>
+        <v>0.6423664907443662</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645173538290685</v>
+        <v>0.6451866470334728</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471131453530204</v>
+        <v>0.6471301408353397</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467255099432281</v>
+        <v>0.6467397811170315</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468780197861077</v>
+        <v>0.6468862861315005</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457250128737582</v>
+        <v>0.6457389741751876</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453041576385257</v>
+        <v>0.6453286002823547</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6463020081503545</v>
+        <v>0.6463435307786891</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6442195641909325</v>
+        <v>0.6442736943407457</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6435390740793056</v>
+        <v>0.6436079519568845</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6447979275453017</v>
+        <v>0.6448767453854629</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6454288793732748</v>
+        <v>0.6455119641653232</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.647378416979543</v>
+        <v>0.6474753399337344</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6539199536405215</v>
+        <v>0.6540024652280315</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6662127322400924</v>
+        <v>0.6663288934357714</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.673646873444155</v>
+        <v>0.6737770874034652</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6894007271014345</v>
+        <v>0.6895165108226735</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6982096049301865</v>
+        <v>0.6982964248119512</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7006184897797183</v>
+        <v>0.7007086029142318</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7009077463159799</v>
+        <v>0.700998216305552</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083150795591137</v>
+        <v>0.7083391806624656</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082773875328472</v>
+        <v>0.7082948641566189</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107287897692828</v>
+        <v>0.710711258872176</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7164001149838445</v>
+        <v>0.7163148338562815</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7165298695904965</v>
+        <v>0.7164401820754398</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7232718257851722</v>
+        <v>0.7231497237124586</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7193552645364905</v>
+        <v>0.7193031610823652</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7226418471511407</v>
+        <v>0.7225827040816968</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7222529794297221</v>
+        <v>0.7222034702249974</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7195154864471991</v>
+        <v>0.7194762268769452</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147348003335967</v>
+        <v>0.7147346321589179</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165548900548635</v>
+        <v>0.7165486736848439</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164293383081364</v>
+        <v>0.7164123085872766</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151152104682759</v>
+        <v>0.7150957768975879</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129280053430258</v>
+        <v>0.7129139228949717</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103969781633719</v>
+        <v>0.7103747846429895</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103908240864141</v>
+        <v>0.7103659724667956</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080738122479879</v>
+        <v>0.7080363435427048</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7052084266182437</v>
+        <v>0.7051441141974494</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7032690413308473</v>
+        <v>0.7037762881572767</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026629786824388</v>
+        <v>0.7030107254290447</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7017027609062341</v>
+        <v>0.7019348286769287</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7002810899218872</v>
+        <v>0.7004073059689779</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6991086218378579</v>
+        <v>0.6991787810277839</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6954849575913815</v>
+        <v>0.6951831305435092</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6928808227410557</v>
+        <v>0.6921698413472628</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6915002351127101</v>
+        <v>0.6905963727147795</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6866048350035869</v>
+        <v>0.6853527235701182</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6821924862351789</v>
+        <v>0.6805029094820679</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6792632113059652</v>
+        <v>0.6775065892573666</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6804465283849818</v>
+        <v>0.6779238794422301</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6846173155630952</v>
+        <v>0.6838006707255837</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6930005183188307</v>
+        <v>0.6951998902934522</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6867539875929403</v>
+        <v>0.6891767030878222</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7019348286769287</v>
+        <v>0.7019347145825646</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7004073059689779</v>
+        <v>0.7004071979564768</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6991787810277839</v>
+        <v>0.6991956488702056</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6951831305435092</v>
+        <v>0.6952159077281084</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6921698413472628</v>
+        <v>0.6921849128927567</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6905963727147795</v>
+        <v>0.6906016666962029</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6853527235701182</v>
+        <v>0.6853516143668086</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6805029094820679</v>
+        <v>0.6804932850476183</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6775065892573666</v>
+        <v>0.6774951880439737</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6779238794422301</v>
+        <v>0.6779067812470568</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6838006707255837</v>
+        <v>0.6837766216871555</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6951998902934522</v>
+        <v>0.6951469252919199</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6891767030878222</v>
+        <v>0.6889068696376264</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506575014720115</v>
+        <v>0.6506553782489692</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514385677636403</v>
+        <v>0.6514374656947757</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525172581954842</v>
+        <v>0.6525153556188321</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497467962603872</v>
+        <v>0.6497460257905295</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464478762839864</v>
+        <v>0.6464470431081176</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431595350836974</v>
+        <v>0.6431586127736142</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408437570249518</v>
+        <v>0.6408427776594491</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398284221793126</v>
+        <v>0.6398274400820944</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642492593409024</v>
+        <v>0.6424877946894247</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433279586116436</v>
+        <v>0.6433250618386765</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414204808603909</v>
+        <v>0.6414176049650149</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385442963267033</v>
+        <v>0.638541385706928</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405472445100197</v>
+        <v>0.6405387111084533</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406152835209794</v>
+        <v>0.6406071155877479</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400104711778315</v>
+        <v>0.6400062901509128</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423664907443662</v>
+        <v>0.6423629935948222</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451866470334728</v>
+        <v>0.6451799798430385</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471301408353397</v>
+        <v>0.6471215005472736</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467397811170315</v>
+        <v>0.6467325271038833</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468862861315005</v>
+        <v>0.6468820838833762</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457389741751876</v>
+        <v>0.64573187618346</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453286002823547</v>
+        <v>0.6453161710443251</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6463435307786891</v>
+        <v>0.646322420525371</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6442736943407457</v>
+        <v>0.644246176100268</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6436079519568845</v>
+        <v>0.6435729366558258</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6448767453854629</v>
+        <v>0.6448366805635001</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6455119641653232</v>
+        <v>0.6454697341770051</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6474753399337344</v>
+        <v>0.647426075445973</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6540024652280315</v>
+        <v>0.6539605126557765</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6663288934357714</v>
+        <v>0.6662698414991666</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6737770874034652</v>
+        <v>0.6737108901209321</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6895165108226735</v>
+        <v>0.6894576767396065</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6982964248119512</v>
+        <v>0.6982523128239089</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7007086029142318</v>
+        <v>0.7006628272928439</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.700998216305552</v>
+        <v>0.7009522755300719</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083391806624656</v>
+        <v>0.7083269674188265</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082948641566189</v>
+        <v>0.7082860225854779</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710711258872176</v>
+        <v>0.7107202125325374</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7163148338562815</v>
+        <v>0.7163581902484953</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7164401820754398</v>
+        <v>0.7164857670635091</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7231497237124586</v>
+        <v>0.72321176352133</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7193031610823652</v>
+        <v>0.7193296374805604</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7225827040816968</v>
+        <v>0.7226127531600018</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7222034702249974</v>
+        <v>0.722228612486424</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7194762268769452</v>
+        <v>0.7194961552229268</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147346321589179</v>
+        <v>0.7147347138549476</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165486736848439</v>
+        <v>0.7165518217084395</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164123085872766</v>
+        <v>0.7164209570464358</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7150957768975879</v>
+        <v>0.7151056538069089</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129139228949717</v>
+        <v>0.7129210929385217</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103747846429895</v>
+        <v>0.7103860926035159</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103659724667956</v>
+        <v>0.7103786339643415</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080363435427048</v>
+        <v>0.7080554212834742</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7051441141974494</v>
+        <v>0.705176795423477</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037762881572767</v>
+        <v>0.7038117854064103</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7030107254290447</v>
+        <v>0.7027144867509242</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7019347145825646</v>
+        <v>0.7017397591369487</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7004071979564768</v>
+        <v>0.700336311386772</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6991956488702056</v>
+        <v>0.6992885669874106</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6952159077281084</v>
+        <v>0.6954755163776849</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6921849128927567</v>
+        <v>0.6925521557800753</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6906016666962029</v>
+        <v>0.6909836429815642</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6853516143668086</v>
+        <v>0.686035905758948</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6804932850476183</v>
+        <v>0.6814785732299394</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6774951880439737</v>
+        <v>0.6784969796477672</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6779067812470568</v>
+        <v>0.6787524103591933</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6837766216871555</v>
+        <v>0.6840339438485646</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6951469252919199</v>
+        <v>0.6935621400360622</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6889068696376264</v>
+        <v>0.6874624636317143</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506553782489692</v>
+        <v>0.6506513405867738</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514374656947757</v>
+        <v>0.6514353676853433</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525153556188321</v>
+        <v>0.6525117360423816</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497460257905295</v>
+        <v>0.649744556135712</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464470431081176</v>
+        <v>0.6464454543900643</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431586127736142</v>
+        <v>0.6431568546253366</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408427776594491</v>
+        <v>0.6408409110812976</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398274400820944</v>
+        <v>0.6398255684744321</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424877946894247</v>
+        <v>0.6424786725267874</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433250618386765</v>
+        <v>0.6433195587875905</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414176049650149</v>
+        <v>0.6414121412705739</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.638541385706928</v>
+        <v>0.6385358557959899</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405387111084533</v>
+        <v>0.6405224951656222</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6406071155877479</v>
+        <v>0.6405915845733194</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400062901509128</v>
+        <v>0.6399983345880392</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423629935948222</v>
+        <v>0.6423563542232711</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451799798430385</v>
+        <v>0.6451673111288243</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471215005472736</v>
+        <v>0.6471050613991551</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467325271038833</v>
+        <v>0.6467187182425344</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468820838833762</v>
+        <v>0.6468740871498295</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.64573187618346</v>
+        <v>0.6457183728167487</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453161710443251</v>
+        <v>0.6452925395751592</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646322420525371</v>
+        <v>0.6462822596565888</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.644246176100268</v>
+        <v>0.6441938146539605</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6435729366558258</v>
+        <v>0.6435063083678147</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6448366805635001</v>
+        <v>0.6447604231426682</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6454697341770051</v>
+        <v>0.645389333912666</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.647426075445973</v>
+        <v>0.6473322875940648</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6539605126557765</v>
+        <v>0.6538807201055732</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6662698414991666</v>
+        <v>0.6661574717189389</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6737108901209321</v>
+        <v>0.6735849317975622</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6894576767396065</v>
+        <v>0.689345573239864</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6982523128239089</v>
+        <v>0.6981682355332868</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7006628272928439</v>
+        <v>0.7005755241634166</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7009522755300719</v>
+        <v>0.7008645653187355</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083269674188265</v>
+        <v>0.708303505006826</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082860225854779</v>
+        <v>0.7082689530142592</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107202125325374</v>
+        <v>0.7107370126274427</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7163581902484953</v>
+        <v>0.7164406775467609</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7164857670635091</v>
+        <v>0.7165725604365041</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.72321176352133</v>
+        <v>0.7233300031700021</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7193296374805604</v>
+        <v>0.7193800822442005</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7226127531600018</v>
+        <v>0.7226700305559691</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722228612486424</v>
+        <v>0.7222766059981311</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7194961552229268</v>
+        <v>0.7195342466278564</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147347138549476</v>
+        <v>0.7147348910106068</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165518217084395</v>
+        <v>0.7165578814646526</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164209570464358</v>
+        <v>0.7164374645235738</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151056538069089</v>
+        <v>0.7151244622333641</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129210929385217</v>
+        <v>0.7129346736901458</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103860926035159</v>
+        <v>0.7104074642065124</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103786339643415</v>
+        <v>0.7104025682920082</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080554212834742</v>
+        <v>0.7080915523818434</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.705176795423477</v>
+        <v>0.7052390568916644</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038117854064103</v>
+        <v>0.7033020836680222</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027144867509242</v>
+        <v>0.7024010218812455</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7017397591369487</v>
+        <v>0.7015212968252345</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.700336311386772</v>
+        <v>0.7002087518396848</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6992885669874106</v>
+        <v>0.6990723134004394</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6954755163776849</v>
+        <v>0.6955880845080429</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6925521557800753</v>
+        <v>0.6930614531416093</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6909836429815642</v>
+        <v>0.6916882696954196</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.686035905758948</v>
+        <v>0.6870449859039693</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6814785732299394</v>
+        <v>0.6828537932454836</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6784969796477672</v>
+        <v>0.6799088677641909</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6787524103591933</v>
+        <v>0.6808648906110433</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6840339438485646</v>
+        <v>0.6846110594067418</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6935621400360622</v>
+        <v>0.6918112187612804</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6874624636317143</v>
+        <v>0.685285977896716</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506513405867738</v>
+        <v>0.650653325780034</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514353676853433</v>
+        <v>0.6514363995786774</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525117360423816</v>
+        <v>0.6525135159231248</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649744556135712</v>
+        <v>0.6497452794528347</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464454543900643</v>
+        <v>0.6464462362169465</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431568546253366</v>
+        <v>0.6431577197437766</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408409110812976</v>
+        <v>0.6408418294997753</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398255684744321</v>
+        <v>0.6398264893386677</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424786725267874</v>
+        <v>0.6424831570531035</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433195587875905</v>
+        <v>0.6433222635419464</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414121412705739</v>
+        <v>0.6414148267310882</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385358557959899</v>
+        <v>0.6385385738429495</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405224951656222</v>
+        <v>0.6405304661158091</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405915845733194</v>
+        <v>0.640599220412754</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399983345880392</v>
+        <v>0.6400022468511462</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423563542232711</v>
+        <v>0.6423596167870058</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451673111288243</v>
+        <v>0.645173538290685</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471050613991551</v>
+        <v>0.6471131453530204</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467187182425344</v>
+        <v>0.6467255099432281</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468740871498295</v>
+        <v>0.6468780197861077</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457183728167487</v>
+        <v>0.6457250128737582</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452925395751592</v>
+        <v>0.6453041576385257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6462822596565888</v>
+        <v>0.6463020081503545</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6441938146539605</v>
+        <v>0.6442195641909325</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6435063083678147</v>
+        <v>0.6435390740793056</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6447604231426682</v>
+        <v>0.6447979275453017</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.645389333912666</v>
+        <v>0.6454288793732748</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6473322875940648</v>
+        <v>0.647378416979543</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6538807201055732</v>
+        <v>0.6539199536405215</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6661574717189389</v>
+        <v>0.6662127322400924</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6735849317975622</v>
+        <v>0.673646873444155</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.689345573239864</v>
+        <v>0.6894007271014345</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6981682355332868</v>
+        <v>0.6982096049301865</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7005755241634166</v>
+        <v>0.7006184897797183</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7008645653187355</v>
+        <v>0.7009077463159799</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708303505006826</v>
+        <v>0.7083150795591137</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082689530142592</v>
+        <v>0.7082773875328472</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107370126274427</v>
+        <v>0.7107287897692828</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7164406775467609</v>
+        <v>0.7164001149838445</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7165725604365041</v>
+        <v>0.7165298695904965</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7233300031700021</v>
+        <v>0.7232718257851722</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7193800822442005</v>
+        <v>0.7193552645364905</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7226700305559691</v>
+        <v>0.7226418471511407</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7222766059981311</v>
+        <v>0.7222529794297221</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7195342466278564</v>
+        <v>0.7195154864471991</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147348910106068</v>
+        <v>0.7147348003335967</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165578814646526</v>
+        <v>0.7165548900548635</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164374645235738</v>
+        <v>0.7164293383081364</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151244622333641</v>
+        <v>0.7151152104682759</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129346736901458</v>
+        <v>0.7129280053430258</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104074642065124</v>
+        <v>0.7103969781633719</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104025682920082</v>
+        <v>0.7103908240864141</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080915523818434</v>
+        <v>0.7080738122479879</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7052390568916644</v>
+        <v>0.7052084266182437</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7033020836680222</v>
+        <v>0.7038462046192984</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7024010218812455</v>
+        <v>0.7023367012050619</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7015212968252345</v>
+        <v>0.7014308324687306</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7002087518396848</v>
+        <v>0.7001344410182426</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6990723134004394</v>
+        <v>0.6992036784325613</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6955880845080429</v>
+        <v>0.6955191163892398</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6930614531416093</v>
+        <v>0.6926736364241795</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6916882696954196</v>
+        <v>0.6911059827330637</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6870449859039693</v>
+        <v>0.6863972505376994</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6828537932454836</v>
+        <v>0.6820319283112208</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6799088677641909</v>
+        <v>0.6790180959356003</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6808648906110433</v>
+        <v>0.6790882732373013</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6846110594067418</v>
+        <v>0.683786815005736</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6918112187612804</v>
+        <v>0.6916076664738984</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.685285977896716</v>
+        <v>0.685067347356124</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650653325780034</v>
+        <v>0.6506494194150719</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514363995786774</v>
+        <v>0.6514343683939436</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525135159231248</v>
+        <v>0.6525100131067147</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497452794528347</v>
+        <v>0.6497438547944971</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464462362169465</v>
+        <v>0.6464446964811931</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431577197437766</v>
+        <v>0.6431560161332206</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408418294997753</v>
+        <v>0.6408400210294017</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398264893386677</v>
+        <v>0.6398246761056157</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424831570531035</v>
+        <v>0.6424743336546437</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433222635419464</v>
+        <v>0.643316942965694</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414148267310882</v>
+        <v>0.6414095440160618</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385385738429495</v>
+        <v>0.6385332269509749</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405304661158091</v>
+        <v>0.6405147848292883</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640599220412754</v>
+        <v>0.6405841955123019</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6400022468511462</v>
+        <v>0.6399945470972612</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423596167870058</v>
+        <v>0.6423532002105308</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645173538290685</v>
+        <v>0.645161287844204</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6471131453530204</v>
+        <v>0.647097235713749</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467255099432281</v>
+        <v>0.6467121413270144</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468780197861077</v>
+        <v>0.6468702797089527</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457250128737582</v>
+        <v>0.6457119453121446</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6453041576385257</v>
+        <v>0.6452812976866844</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6463020081503545</v>
+        <v>0.6462631432170338</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6442195641909325</v>
+        <v>0.644168886322354</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6435390740793056</v>
+        <v>0.6434745872047738</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6447979275453017</v>
+        <v>0.6447241081489192</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6454288793732748</v>
+        <v>0.6453510360747894</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.647378416979543</v>
+        <v>0.647287615165556</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6539199536405215</v>
+        <v>0.6538427483233977</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6662127322400924</v>
+        <v>0.6661039719333011</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.673646873444155</v>
+        <v>0.6735249662860385</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6894007271014345</v>
+        <v>0.6892921319353109</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6982096049301865</v>
+        <v>0.6981281430340789</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7006184897797183</v>
+        <v>0.7005338682025134</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7009077463159799</v>
+        <v>0.7008226728799707</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7083150795591137</v>
+        <v>0.7082922322183487</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082773875328472</v>
+        <v>0.7082607131738872</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107287897692828</v>
+        <v>0.7107449015214968</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7164001149838445</v>
+        <v>0.716479943013812</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7165298695904965</v>
+        <v>0.716613905970207</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7232718257851722</v>
+        <v>0.7233863826668696</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7193552645364905</v>
+        <v>0.7194041281403121</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7226418471511407</v>
+        <v>0.7226973451738324</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7222529794297221</v>
+        <v>0.722299525091026</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7195154864471991</v>
+        <v>0.7195524603704018</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147348003335967</v>
+        <v>0.7147349853604539</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165548900548635</v>
+        <v>0.7165607985731424</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164293383081364</v>
+        <v>0.7164453471204899</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151152104682759</v>
+        <v>0.715133423486396</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129280053430258</v>
+        <v>0.7129411106275019</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7103969781633719</v>
+        <v>0.7104175720131896</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7103908240864141</v>
+        <v>0.7104138902608745</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7080738122479879</v>
+        <v>0.7081086751928556</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7052084266182437</v>
+        <v>0.7052687323823754</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038462046192984</v>
+        <v>0.7033341727566204</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7023367012050619</v>
+        <v>0.7024499160665774</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7014308324687306</v>
+        <v>0.7017116281940868</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7001344410182426</v>
+        <v>0.7005161211799527</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6992036784325613</v>
+        <v>0.6995086840752448</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6955191163892398</v>
+        <v>0.6962213363386972</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6926736364241795</v>
+        <v>0.6938358759355596</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6911059827330637</v>
+        <v>0.6925781181126633</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6863972505376994</v>
+        <v>0.6882179225620009</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6820319283112208</v>
+        <v>0.684383612242494</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6790180959356003</v>
+        <v>0.6816116547360822</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6790882732373013</v>
+        <v>0.6824811070323427</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.683786815005736</v>
+        <v>0.6860157777630067</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6916076664738984</v>
+        <v>0.6930512081721121</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.685067347356124</v>
+        <v>0.6907737158566579</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506494194150719</v>
+        <v>0.6506475592173321</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514343683939436</v>
+        <v>0.6514334001843485</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525100131067147</v>
+        <v>0.6525083444269008</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497438547944971</v>
+        <v>0.6497431744465166</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464446964811931</v>
+        <v>0.646443961412664</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431560161332206</v>
+        <v>0.6431552030598383</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408400210294017</v>
+        <v>0.6408391580527</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398246761056157</v>
+        <v>0.6398238109324061</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424743336546437</v>
+        <v>0.642470133456994</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643316942965694</v>
+        <v>0.6433144117641518</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414095440160618</v>
+        <v>0.641407030694921</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385332269509749</v>
+        <v>0.6385306829904577</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405147848292883</v>
+        <v>0.6405073225408163</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405841955123019</v>
+        <v>0.6405770414695122</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399945470972612</v>
+        <v>0.6399908785072633</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423532002105308</v>
+        <v>0.6423501494272925</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645161287844204</v>
+        <v>0.6451554585990155</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.647097235713749</v>
+        <v>0.6470896561374904</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467121413270144</v>
+        <v>0.6467057691840822</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468702797089527</v>
+        <v>0.6468665915891165</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457119453121446</v>
+        <v>0.6457057203315838</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452812976866844</v>
+        <v>0.645270414023012</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6462631432170338</v>
+        <v>0.6462446290044658</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.644168886322354</v>
+        <v>0.6441447406031762</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6434745872047738</v>
+        <v>0.6434438615407123</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6447241081489192</v>
+        <v>0.6446889270311403</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6453510360747894</v>
+        <v>0.6453139279441209</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.647287615165556</v>
+        <v>0.6472443320169941</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6538427483233977</v>
+        <v>0.6538059785748347</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6661039719333011</v>
+        <v>0.6660521503580272</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6735249662860385</v>
+        <v>0.6734668841768179</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6892921319353109</v>
+        <v>0.6892403250069179</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6981281430340789</v>
+        <v>0.6980892695337291</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7005338682025134</v>
+        <v>0.7004934633350961</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7008226728799707</v>
+        <v>0.7007820127671542</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082922322183487</v>
+        <v>0.7082812501595728</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082607131738872</v>
+        <v>0.70825266229377</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107449015214968</v>
+        <v>0.7107524753797614</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.716479943013812</v>
+        <v>0.7165179723964639</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.716613905970207</v>
+        <v>0.7166539684854085</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7233863826668696</v>
+        <v>0.7234410460177216</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7194041281403121</v>
+        <v>0.7194274374887388</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7226973451738324</v>
+        <v>0.7227238303028353</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722299525091026</v>
+        <v>0.7223217677091472</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7195524603704018</v>
+        <v>0.7195701509082449</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147349853604539</v>
+        <v>0.7147350829101479</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165607985731424</v>
+        <v>0.7165636439134978</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164453471204899</v>
+        <v>0.7164529968560738</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715133423486396</v>
+        <v>0.7151421077193038</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129411106275019</v>
+        <v>0.7129473279472731</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104175720131896</v>
+        <v>0.7104273213965909</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104138902608745</v>
+        <v>0.7104248120447441</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7081086751928556</v>
+        <v>0.7081252119522861</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7052687323823754</v>
+        <v>0.705297496475594</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7033341727566204</v>
+        <v>0.7033653482142355</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7024499160665774</v>
+        <v>0.702598771782845</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7017116281940868</v>
+        <v>0.7020127778197496</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7005161211799527</v>
+        <v>0.7009486667029029</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.6995086840752448</v>
+        <v>0.7000767675171438</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6962213363386972</v>
+        <v>0.6970231246637529</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6938358759355596</v>
+        <v>0.6948120156262666</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6925781181126633</v>
+        <v>0.693647813312925</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6882179225620009</v>
+        <v>0.6895724813600866</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.684383612242494</v>
+        <v>0.686099094145979</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6816116547360822</v>
+        <v>0.6835390128105125</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6824811070323427</v>
+        <v>0.684367502717401</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6860157777630067</v>
+        <v>0.6877685512448826</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6930512081721121</v>
+        <v>0.6948582181097536</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6907737158566579</v>
+        <v>0.6954814781986268</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7033653482142355</v>
+        <v>0.7039434541320589</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.702598771782845</v>
+        <v>0.7025770935485378</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7020127778197496</v>
+        <v>0.7018573749227859</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7009486667029029</v>
+        <v>0.7008903586234991</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7000767675171438</v>
+        <v>0.7002188938002885</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6970231246637529</v>
+        <v>0.6972129062227412</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6948120156262666</v>
+        <v>0.694762916969361</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.693647813312925</v>
+        <v>0.6934419756221358</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6895724813600866</v>
+        <v>0.6895707507726376</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.686099094145979</v>
+        <v>0.6861678842444705</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6835390128105125</v>
+        <v>0.6836079759238702</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.684367502717401</v>
+        <v>0.6835810279568655</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6877685512448826</v>
+        <v>0.687560540568763</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6948582181097536</v>
+        <v>0.6948277538925272</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6954814781986268</v>
+        <v>0.6938942173928795</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>0.6984143467016868</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506475592173321</v>
+        <v>0.6506457571363529</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514334001843485</v>
+        <v>0.6514324616294317</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525083444269008</v>
+        <v>0.652506727480388</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497431744465166</v>
+        <v>0.6497425141665776</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.646443961412664</v>
+        <v>0.646443248170378</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431552030598383</v>
+        <v>0.6431544142693439</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408391580527</v>
+        <v>0.6408383209368416</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398238109324061</v>
+        <v>0.6398229717326921</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642470133456994</v>
+        <v>0.6424660653929146</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433144117641518</v>
+        <v>0.6433119611450162</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.641407030694921</v>
+        <v>0.6414045973059108</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385306829904577</v>
+        <v>0.6385282198710203</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405073225408163</v>
+        <v>0.6405000965287094</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405770414695122</v>
+        <v>0.6405701114195421</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399908785072633</v>
+        <v>0.6399873233089897</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423501494272925</v>
+        <v>0.6423471968938658</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451554585990155</v>
+        <v>0.6451498141775762</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470896561374904</v>
+        <v>0.647082311261155</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6467057691840822</v>
+        <v>0.6466995924128844</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468665915891165</v>
+        <v>0.6468630172771768</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6457057203315838</v>
+        <v>0.6456996884667877</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645270414023012</v>
+        <v>0.6452598717564972</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6462446290044658</v>
+        <v>0.6462266890370338</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6441447406031762</v>
+        <v>0.6441213412798551</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6434438615407123</v>
+        <v>0.6434140853427576</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6446889270311403</v>
+        <v>0.6446548276504497</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6453139279441209</v>
+        <v>0.6452779551223505</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6472443320169941</v>
+        <v>0.6472023745822212</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6538059785748347</v>
+        <v>0.6537703548397652</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6660521503580272</v>
+        <v>0.6660019295272102</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6734668841768179</v>
+        <v>0.6734105984286723</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6892403250069179</v>
+        <v>0.6891900789388345</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6980892695337291</v>
+        <v>0.6980515605617174</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7004934633350961</v>
+        <v>0.700454254413154</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7007820127671542</v>
+        <v>0.700742531934625</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082812501595728</v>
+        <v>0.708270548283</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.70825266229377</v>
+        <v>0.7082447948004491</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107524753797614</v>
+        <v>0.7107597517739774</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7165179723964639</v>
+        <v>0.7165548229524719</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7166539684854085</v>
+        <v>0.7166928065074174</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7234410460177216</v>
+        <v>0.7234940701036667</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7194274374887388</v>
+        <v>0.7194500434490988</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7227238303028353</v>
+        <v>0.7227495229227152</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7223217677091472</v>
+        <v>0.7223433630878217</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7195701509082449</v>
+        <v>0.7195873401952781</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147350829101479</v>
+        <v>0.7147351832337424</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165636439134978</v>
+        <v>0.7165664199199236</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164529968560738</v>
+        <v>0.7164604238653</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151421077193038</v>
+        <v>0.7151505275999828</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129473279472731</v>
+        <v>0.7129533366570222</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104273213965909</v>
+        <v>0.7104367308258618</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104248120447441</v>
+        <v>0.7104353542035147</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7081252119522861</v>
+        <v>0.7081411918766329</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.705297496475594</v>
+        <v>0.7053253900024195</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7039434541320589</v>
+        <v>0.7033956475604495</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7025770935485378</v>
+        <v>0.7026243399141435</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7018573749227859</v>
+        <v>0.7019356973396437</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7008903586234991</v>
+        <v>0.7009574193993291</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7002188938002885</v>
+        <v>0.7001368760091103</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6972129062227412</v>
+        <v>0.6973086689059522</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.694762916969361</v>
+        <v>0.6951317624507078</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6934419756221358</v>
+        <v>0.693971200682413</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6895707507726376</v>
+        <v>0.6900629403626362</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6861678842444705</v>
+        <v>0.6867608202186246</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6836079759238702</v>
+        <v>0.6843086696026102</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6835810279568655</v>
+        <v>0.6849029357651308</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.687560540568763</v>
+        <v>0.6880206545531478</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6948277538925272</v>
+        <v>0.6944644654299585</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6938942173928795</v>
+        <v>0.6944840799507787</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.6984143467016868</v>
+        <v>0.6898920819192945</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7033956475604495</v>
+        <v>0.7039740086901037</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026243399141435</v>
+        <v>0.7026040205139568</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7019356973396437</v>
+        <v>0.7017890657812165</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7009574193993291</v>
+        <v>0.7009045695741495</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7001368760091103</v>
+        <v>0.7003054124519974</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6973086689059522</v>
+        <v>0.6975773347142405</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6951317624507078</v>
+        <v>0.6952188465591482</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.693971200682413</v>
+        <v>0.6939469821850771</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6900629403626362</v>
+        <v>0.6902694193847535</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6867608202186246</v>
+        <v>0.6870799474057456</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6843086696026102</v>
+        <v>0.6846547892306009</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6849029357651308</v>
+        <v>0.6845364825949932</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6880206545531478</v>
+        <v>0.6882608693231596</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6944644654299585</v>
+        <v>0.6951378157514463</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6944840799507787</v>
+        <v>0.6946048987942142</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.6898920819192945</v>
+        <v>0.6985253737976941</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506457571363529</v>
+        <v>0.6506440104906892</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514324616294317</v>
+        <v>0.6514315513880704</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652506727480388</v>
+        <v>0.6525051598985836</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497425141665776</v>
+        <v>0.6497418730828467</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.646443248170378</v>
+        <v>0.6464425557992046</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431544142693439</v>
+        <v>0.6431536486924032</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408383209368416</v>
+        <v>0.6408375085388672</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398229717326921</v>
+        <v>0.6398221573563566</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424660653929146</v>
+        <v>0.6424621233263086</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433119611450162</v>
+        <v>0.6433095873230628</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414045973059108</v>
+        <v>0.6414022400979821</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385282198710203</v>
+        <v>0.6385258338018853</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6405000965287094</v>
+        <v>0.640493095754193</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405701114195421</v>
+        <v>0.6405633950153184</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399873233089897</v>
+        <v>0.639983876328343</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423471968938658</v>
+        <v>0.6423443379453846</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451498141775762</v>
+        <v>0.6451443459379758</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.647082311261155</v>
+        <v>0.6470751903687502</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466995924128844</v>
+        <v>0.6466936021783668</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468630172771768</v>
+        <v>0.6468595515939113</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456996884667877</v>
+        <v>0.6456938408824386</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452598717564972</v>
+        <v>0.6452496550956832</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6462266890370338</v>
+        <v>0.6462092970378945</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6441213412798551</v>
+        <v>0.6440986543323957</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6434140853427576</v>
+        <v>0.6433852153667717</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6446548276504497</v>
+        <v>0.6446217610073633</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6452779551223505</v>
+        <v>0.6452430664663407</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6472023745822212</v>
+        <v>0.6471616830997464</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6537703548397652</v>
+        <v>0.6537358245159058</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6660019295272102</v>
+        <v>0.6659532366537393</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6734105984286723</v>
+        <v>0.6733560272634506</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6891900789388345</v>
+        <v>0.689141324539094</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6980515605617174</v>
+        <v>0.6980149648273299</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.700454254413154</v>
+        <v>0.7004161894594261</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.700742531934625</v>
+        <v>0.7007041803040188</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708270548283</v>
+        <v>0.7082601165054535</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082447948004491</v>
+        <v>0.7082371052694691</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107597517739774</v>
+        <v>0.7107667470358205</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7165548229524719</v>
+        <v>0.7165905484691777</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7166928065074174</v>
+        <v>0.71673047507234</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7234940701036667</v>
+        <v>0.7235455272994438</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7194500434490988</v>
+        <v>0.7194719772304659</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7227495229227152</v>
+        <v>0.722774457862038</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7223433630878217</v>
+        <v>0.7223643388192968</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7195873401952781</v>
+        <v>0.7196040489912269</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147351832337424</v>
+        <v>0.7147352859474692</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165664199199236</v>
+        <v>0.7165691289309866</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164604238653</v>
+        <v>0.7164676377051522</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151505275999828</v>
+        <v>0.7151586950343607</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129533366570222</v>
+        <v>0.7129591470436283</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104367308258618</v>
+        <v>0.7104458175370618</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104353542035147</v>
+        <v>0.71044553592811</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7081411918766329</v>
+        <v>0.7081566422921219</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7053253900024195</v>
+        <v>0.7053524514223586</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7039740086901037</v>
+        <v>0.703425106348437</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026040205139568</v>
+        <v>0.7026492585217541</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7017890657812165</v>
+        <v>0.7018638811139664</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7009045695741495</v>
+        <v>0.7009631271071741</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7003054124519974</v>
+        <v>0.7001871883404212</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6975773347142405</v>
+        <v>0.6975645916422837</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6952188465591482</v>
+        <v>0.6954266789403128</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6939469821850771</v>
+        <v>0.6942717156260185</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6902694193847535</v>
+        <v>0.6905188887412601</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6870799474057456</v>
+        <v>0.6873718529189865</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6846547892306009</v>
+        <v>0.6850185397122257</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6845364825949932</v>
+        <v>0.6854077772604741</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6882608693231596</v>
+        <v>0.6882767210036589</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6951378157514463</v>
+        <v>0.6941878995990149</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6946048987942142</v>
+        <v>0.6939182892598645</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.6985253737976941</v>
+        <v>0.6901910741856527</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.703425106348437</v>
+        <v>0.7040036969343033</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026492585217541</v>
+        <v>0.7026302476587124</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7018638811139664</v>
+        <v>0.7020052386037947</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7009631271071741</v>
+        <v>0.7012489395860393</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7001871883404212</v>
+        <v>0.7007378266849628</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6975645916422837</v>
+        <v>0.6983288486566356</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6954266789403128</v>
+        <v>0.6961014186962449</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6942717156260185</v>
+        <v>0.6949149471492362</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6905188887412601</v>
+        <v>0.6914730348643588</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6873718529189865</v>
+        <v>0.6885789795727799</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6850185397122257</v>
+        <v>0.6863553229902629</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6854077772604741</v>
+        <v>0.6862761444588596</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6882767210036589</v>
+        <v>0.6899073398587805</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6941878995990149</v>
+        <v>0.6968932068626807</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6939182892598645</v>
+        <v>0.697369789018795</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.6901910741856527</v>
+        <v>0.7044106459662133</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506440104906892</v>
+        <v>0.6506423167613431</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514315513880704</v>
+        <v>0.6514306681987652</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525051598985836</v>
+        <v>0.6525036394552874</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497418730828467</v>
+        <v>0.6497412503730735</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464425557992046</v>
+        <v>0.6464418833987705</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431536486924032</v>
+        <v>0.6431529053214077</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408375085388672</v>
+        <v>0.6408367197820499</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398221573563566</v>
+        <v>0.6398213667200632</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424621233263086</v>
+        <v>0.6424583014950755</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433095873230628</v>
+        <v>0.6433072867463369</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6414022400979821</v>
+        <v>0.6413999555510355</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385258338018853</v>
+        <v>0.6385235212254994</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640493095754193</v>
+        <v>0.640486309855117</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405633950153184</v>
+        <v>0.6405568825367761</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639983876328343</v>
+        <v>0.6399805327011239</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423443379453846</v>
+        <v>0.6423415682073437</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451443459379758</v>
+        <v>0.6451390457681591</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470751903687502</v>
+        <v>0.6470682833857442</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466936021783668</v>
+        <v>0.646687790169411</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468595515939113</v>
+        <v>0.6468561896691565</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456938408824386</v>
+        <v>0.645688169273283</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452496550956832</v>
+        <v>0.6452397492068633</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6462092970378945</v>
+        <v>0.6461924283074505</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6440986543323957</v>
+        <v>0.6440766477736406</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6433852153667717</v>
+        <v>0.6433572109497885</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6446217610073633</v>
+        <v>0.6445896810096796</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6452430664663407</v>
+        <v>0.64520921384908</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6471616830997464</v>
+        <v>0.6471222013334018</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6537358245159058</v>
+        <v>0.6537023381627974</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6659532366537393</v>
+        <v>0.6659060032825508</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6733560272634506</v>
+        <v>0.6733030937756073</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.689141324539094</v>
+        <v>0.6890939966278367</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6980149648273299</v>
+        <v>0.6979794339923225</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7004161894594261</v>
+        <v>0.7003792194445535</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7007041803040188</v>
+        <v>0.7006669105623139</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082601165054535</v>
+        <v>0.7082499451864872</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082371052694691</v>
+        <v>0.7082295884281251</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107667470358205</v>
+        <v>0.7107734763618188</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7165905484691777</v>
+        <v>0.7166251995216224</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.71673047507234</v>
+        <v>0.7167670259820245</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7235455272994438</v>
+        <v>0.7235954857974568</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7194719772304659</v>
+        <v>0.7194932682319172</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.722774457862038</v>
+        <v>0.7227986679512503</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7223643388192968</v>
+        <v>0.7223847209651899</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196040489912269</v>
+        <v>0.7196202969404057</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147352859474692</v>
+        <v>0.7147353907054184</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165691289309866</v>
+        <v>0.7165717731930019</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164676377051522</v>
+        <v>0.7164746473951378</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151586950343607</v>
+        <v>0.7151666212229315</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129591470436283</v>
+        <v>0.7129647687310918</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104458175370618</v>
+        <v>0.7104545976333971</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.71044553592811</v>
+        <v>0.7104553751514873</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7081566422921219</v>
+        <v>0.7081715887837725</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7053524514223586</v>
+        <v>0.7053787169906653</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040036969343033</v>
+        <v>0.7034537582873235</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026302476587124</v>
+        <v>0.7026735507939786</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7020052386037947</v>
+        <v>0.7020699246729651</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7012489395860393</v>
+        <v>0.7013014927397301</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7007378266849628</v>
+        <v>0.7006112647881363</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6983288486566356</v>
+        <v>0.6983041390803026</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6961014186962449</v>
+        <v>0.6962818260743847</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6949149471492362</v>
+        <v>0.6952011264956223</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6914730348643588</v>
+        <v>0.6916746812361165</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6885789795727799</v>
+        <v>0.6888019479010282</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6863553229902629</v>
+        <v>0.6866374114131365</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6862761444588596</v>
+        <v>0.6870336490011419</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6899073398587805</v>
+        <v>0.6898531239282849</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6968932068626807</v>
+        <v>0.6958816669010033</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.697369789018795</v>
+        <v>0.6969961701652539</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7044106459662133</v>
+        <v>0.6984292955601796</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7034537582873235</v>
+        <v>0.7040325545396302</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026735507939786</v>
+        <v>0.7026558007832715</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7020699246729651</v>
+        <v>0.7020641837395807</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7013014927397301</v>
+        <v>0.7013969153794973</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7006112647881363</v>
+        <v>0.7009509295337395</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6983041390803026</v>
+        <v>0.698799268406527</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6962818260743847</v>
+        <v>0.6966671931288418</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6952011264956223</v>
+        <v>0.6955372355770832</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6916746812361165</v>
+        <v>0.6922780021598358</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6888019479010282</v>
+        <v>0.6895864453388489</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6866374114131365</v>
+        <v>0.687495797599224</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6870336490011419</v>
+        <v>0.6873756968390012</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6898531239282849</v>
+        <v>0.6908338155571074</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6958816669010033</v>
+        <v>0.6976040563723496</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.6969961701652539</v>
+        <v>0.698402984288863</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.6984292955601796</v>
+        <v>0.7048843596901931</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506423167613431</v>
+        <v>0.6506390787162168</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514306681987652</v>
+        <v>0.6514289782940313</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525036394552874</v>
+        <v>0.65250073172906</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497412503730735</v>
+        <v>0.6497400570138401</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464418833987705</v>
+        <v>0.6464405951596026</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431529053214077</v>
+        <v>0.6431514814495359</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408367197820499</v>
+        <v>0.6408352091882278</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398213667200632</v>
+        <v>0.6398198526399581</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424583014950755</v>
+        <v>0.6424509971944619</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433072867463369</v>
+        <v>0.6433028921825593</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413999555510355</v>
+        <v>0.6413955914110329</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385235212254994</v>
+        <v>0.6385191033825265</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640486309855117</v>
+        <v>0.6404733443161943</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405568825367761</v>
+        <v>0.6405444333351888</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399805327011239</v>
+        <v>0.6399741374645727</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423415682073437</v>
+        <v>0.6423362801850525</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451390457681591</v>
+        <v>0.6451289196027943</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470682833857442</v>
+        <v>0.6470550737779643</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.646687790169411</v>
+        <v>0.6466766699774432</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468561896691565</v>
+        <v>0.6468497590257252</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645688169273283</v>
+        <v>0.6456773231786378</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452397492068633</v>
+        <v>0.6452208147768705</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6461924283074505</v>
+        <v>0.6461601690519088</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6440766477736406</v>
+        <v>0.6440345571547448</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6433572109497885</v>
+        <v>0.6433036479271854</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6445896810096796</v>
+        <v>0.6445283098650503</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.64520921384908</v>
+        <v>0.6451444380118692</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6471222013334018</v>
+        <v>0.6470466581216965</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6537023381627974</v>
+        <v>0.6536383140360313</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6659060032825508</v>
+        <v>0.6658156610154272</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6733030937756073</v>
+        <v>0.6732018544655841</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6890939966278367</v>
+        <v>0.6890033779238574</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6979794339923225</v>
+        <v>0.6979113871976885</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7003792194445535</v>
+        <v>0.7003083816432111</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7006669105623139</v>
+        <v>0.7005954402192365</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082499451864872</v>
+        <v>0.7082303474519536</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082295884281251</v>
+        <v>0.7082150524889301</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107734763618188</v>
+        <v>0.7107861928753185</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7166251995216224</v>
+        <v>0.7166914658649872</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7167670259820245</v>
+        <v>0.7168369672501663</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7235954857974568</v>
+        <v>0.7236911603129157</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7194932682319172</v>
+        <v>0.7195340312024714</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7227986679512503</v>
+        <v>0.7228450357405813</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7223847209651899</v>
+        <v>0.7224238017061879</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196202969404057</v>
+        <v>0.7196514837295421</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147353907054184</v>
+        <v>0.7147356051370145</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165717731930019</v>
+        <v>0.7165768760143101</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164746473951378</v>
+        <v>0.7164880879360942</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151666212229315</v>
+        <v>0.7151817914423796</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129647687310918</v>
+        <v>0.7129754814994321</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104545976333971</v>
+        <v>0.7104712972656895</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104553751514873</v>
+        <v>0.7104740921299975</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7081715887837725</v>
+        <v>0.7082000644290356</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7053787169906653</v>
+        <v>0.7054289954811657</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040325545396302</v>
+        <v>0.7035087679089238</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026558007832715</v>
+        <v>0.7027203440906549</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7020641837395807</v>
+        <v>0.7021720891139089</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7013969153794973</v>
+        <v>0.7016054569680149</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7009509295337395</v>
+        <v>0.7010257967058655</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.698799268406527</v>
+        <v>0.6990763925292234</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6966671931288418</v>
+        <v>0.6972688007619063</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6955372355770832</v>
+        <v>0.6963295489003496</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6922780021598358</v>
+        <v>0.6931800268161554</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6895864453388489</v>
+        <v>0.6907000779154968</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.687495797599224</v>
+        <v>0.6888151312342708</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6873756968390012</v>
+        <v>0.6891742134925379</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6908338155571074</v>
+        <v>0.6918477598064632</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6976040563723496</v>
+        <v>0.6977845663902504</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.698402984288863</v>
+        <v>0.7000558419375449</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7048843596901931</v>
+        <v>0.7035716177001951</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506390787162168</v>
+        <v>0.6506406735796476</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514289782940313</v>
+        <v>0.6514298108738211</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.65250073172906</v>
+        <v>0.6525021640561506</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497400570138401</v>
+        <v>0.6497406452611312</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464405951596026</v>
+        <v>0.6464412301196045</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431514814495359</v>
+        <v>0.6431521832060942</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408352091882278</v>
+        <v>0.6408359536511766</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398198526399581</v>
+        <v>0.6398205988024886</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424509971944619</v>
+        <v>0.6424545944830554</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433028921825593</v>
+        <v>0.6433050560784659</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413955914110329</v>
+        <v>0.6413977403584256</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385191033825265</v>
+        <v>0.6385212787998769</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404733443161943</v>
+        <v>0.6404797290949289</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405444333351888</v>
+        <v>0.6405505648441174</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399741374645727</v>
+        <v>0.6399772878501842</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423362801850525</v>
+        <v>0.6423388835733784</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451289196027943</v>
+        <v>0.645133906045977</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470550737779643</v>
+        <v>0.6470615808318591</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466766699774432</v>
+        <v>0.6466821485606283</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468497590257252</v>
+        <v>0.6468529269191312</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456773231786378</v>
+        <v>0.6456826658250271</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452208147768705</v>
+        <v>0.6452301401426567</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6461601690519088</v>
+        <v>0.6461760596068943</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6440345571547448</v>
+        <v>0.6440552914999353</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6433036479271854</v>
+        <v>0.6433300338206753</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6445283098650503</v>
+        <v>0.6445585442605977</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6451444380118692</v>
+        <v>0.6451763519413241</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6470466581216965</v>
+        <v>0.6470838763171568</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6536383140360313</v>
+        <v>0.6536698492684043</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6658156610154272</v>
+        <v>0.6658601649741573</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6732018544655841</v>
+        <v>0.6732517255758641</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6890033779238574</v>
+        <v>0.6890480337519931</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6979113871976885</v>
+        <v>0.6979449224626861</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7003083816432111</v>
+        <v>0.7003432980825981</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7005954402192365</v>
+        <v>0.7006306779759004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082303474519536</v>
+        <v>0.7082400251075507</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082150524889301</v>
+        <v>0.708222239156767</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107861928753185</v>
+        <v>0.7107799539079873</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7166914658649872</v>
+        <v>0.7166588237080378</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7168369672501663</v>
+        <v>0.716802508037086</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7236911603129157</v>
+        <v>0.7236440099043693</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195340312024714</v>
+        <v>0.7195139441711712</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7228450357405813</v>
+        <v>0.7228221841629477</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224238017061879</v>
+        <v>0.7224045341599562</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196514837295421</v>
+        <v>0.719636102644451</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147356051370145</v>
+        <v>0.7147354971956978</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165768760143101</v>
+        <v>0.7165743548634381</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164880879360942</v>
+        <v>0.7164814614544501</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151817914423796</v>
+        <v>0.7151743167123192</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129754814994321</v>
+        <v>0.7129702107328844</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104712972656895</v>
+        <v>0.7104630861759147</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104740921299975</v>
+        <v>0.7104648886491072</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082000644290356</v>
+        <v>0.7081860553306903</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054289954811657</v>
+        <v>0.7054042209119262</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7035087679089238</v>
+        <v>0.7040606152883879</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027203440906549</v>
+        <v>0.7026807045084684</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7021720891139089</v>
+        <v>0.7022913058028797</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7016054569680149</v>
+        <v>0.7017419352099312</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7010257967058655</v>
+        <v>0.7013807073368388</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6990763925292234</v>
+        <v>0.6994450914406786</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6972688007619063</v>
+        <v>0.6974423683388207</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6963295489003496</v>
+        <v>0.6964136286841894</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6931800268161554</v>
+        <v>0.6933747666599098</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6907000779154968</v>
+        <v>0.6909419538842672</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6888151312342708</v>
+        <v>0.6890355126572449</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6891742134925379</v>
+        <v>0.6889806496312738</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6918477598064632</v>
+        <v>0.6923842542082267</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6977845663902504</v>
+        <v>0.6992384383763413</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7000558419375449</v>
+        <v>0.7006854998736434</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7035716177001951</v>
+        <v>0.7080781633182158</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506406735796476</v>
+        <v>0.6506375300708587</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514298108738211</v>
+        <v>0.6514281694038124</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6525021640561506</v>
+        <v>0.6524993406153493</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497406452611312</v>
+        <v>0.6497394849380491</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464412301196045</v>
+        <v>0.6464399777607805</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431521832060942</v>
+        <v>0.6431507992044578</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408359536511766</v>
+        <v>0.6408344854884129</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398205988024886</v>
+        <v>0.6398191273224407</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424545944830554</v>
+        <v>0.6424475048305457</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6433050560784659</v>
+        <v>0.643300792106526</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413977403584256</v>
+        <v>0.6413935057827396</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385212787998769</v>
+        <v>0.6385169920157909</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404797290949289</v>
+        <v>0.6404671468981976</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405505648441174</v>
+        <v>0.6405384799065545</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399772878501842</v>
+        <v>0.639971077480469</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423388835733784</v>
+        <v>0.6423337544134435</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645133906045977</v>
+        <v>0.6451240796902908</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470615808318591</v>
+        <v>0.6470487538066629</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466821485606283</v>
+        <v>0.6466713474641402</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468529269191312</v>
+        <v>0.6468466819175542</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456826658250271</v>
+        <v>0.645672134397711</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452301401426567</v>
+        <v>0.6452117607450178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6461760596068943</v>
+        <v>0.646144736015507</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6440552914999353</v>
+        <v>0.6440144180039308</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6433300338206753</v>
+        <v>0.6432780192777712</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6445585442605977</v>
+        <v>0.6444989392524534</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6451763519413241</v>
+        <v>0.6451134317446394</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6470838763171568</v>
+        <v>0.6470104996406387</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6536698492684043</v>
+        <v>0.6536076911895319</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6658601649741573</v>
+        <v>0.6657724341549226</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6732517255758641</v>
+        <v>0.6731534161388255</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6890480337519931</v>
+        <v>0.6889599743812586</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6979449224626861</v>
+        <v>0.6978787875345487</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7003432980825981</v>
+        <v>0.7002744287788972</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7006306779759004</v>
+        <v>0.7005611572167961</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082400251075507</v>
+        <v>0.7082209037856434</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708222239156767</v>
+        <v>0.7082080236105111</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107799539079873</v>
+        <v>0.7107922055871276</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7166588237080378</v>
+        <v>0.7167231682641731</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.716802508037086</v>
+        <v>0.7168704470413499</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7236440099043693</v>
+        <v>0.7237369943513057</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195139441711712</v>
+        <v>0.7195535540247435</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7228221841629477</v>
+        <v>0.7228672503166875</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224045341599562</v>
+        <v>0.7224425456624755</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.719636102644451</v>
+        <v>0.7196664569085887</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147354971956978</v>
+        <v>0.7147357142756257</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165743548634381</v>
+        <v>0.7165793386355314</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164814614544501</v>
+        <v>0.7164945344582652</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151743167123192</v>
+        <v>0.7151890547892783</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129702107328844</v>
+        <v>0.7129805889612528</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104630861759147</v>
+        <v>0.7104792441184191</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104648886491072</v>
+        <v>0.7104830003194224</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7081860553306903</v>
+        <v>0.7082136372039505</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054042209119262</v>
+        <v>0.7054530712136227</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040606152883879</v>
+        <v>0.7035351847748142</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7026807045084684</v>
+        <v>0.702742886636655</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7022913058028797</v>
+        <v>0.7023823044057408</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7017419352099312</v>
+        <v>0.7019501818012657</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7013807073368388</v>
+        <v>0.7014528217671729</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.6994450914406786</v>
+        <v>0.699757200388481</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6974423683388207</v>
+        <v>0.6980825855995649</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6964136286841894</v>
+        <v>0.6972556369735405</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6933747666599098</v>
+        <v>0.6943317824951805</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6909419538842672</v>
+        <v>0.6921094659599015</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6890355126572449</v>
+        <v>0.6904194356185266</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6889806496312738</v>
+        <v>0.6909184746039121</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6923842542082267</v>
+        <v>0.693660461824243</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6992384383763413</v>
+        <v>0.6999028287050569</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7006854998736434</v>
+        <v>0.7033282348048673</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7080781633182158</v>
+        <v>0.7087041609476492</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506375300708587</v>
+        <v>0.6506360256633488</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514281694038124</v>
+        <v>0.6514273832067492</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524993406153493</v>
+        <v>0.6524979889617589</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497394849380491</v>
+        <v>0.649738928377951</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464399777607805</v>
+        <v>0.6464393772062913</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431507992044578</v>
+        <v>0.6431501356698576</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408344854884129</v>
+        <v>0.6408337816965325</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398191273224407</v>
+        <v>0.6398184219898762</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424475048305457</v>
+        <v>0.6424441128682713</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643300792106526</v>
+        <v>0.643298753069672</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413935057827396</v>
+        <v>0.6413914807171668</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385169920157909</v>
+        <v>0.6385149419134615</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404671468981976</v>
+        <v>0.6404611287182117</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405384799065545</v>
+        <v>0.6405326969179035</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639971077480469</v>
+        <v>0.6399681040637353</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423337544134435</v>
+        <v>0.6423313028423472</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451240796902908</v>
+        <v>0.6451193799501327</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470487538066629</v>
+        <v>0.6470426129762076</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466713474641402</v>
+        <v>0.646666174454587</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468466819175542</v>
+        <v>0.6468436917526146</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645672134397711</v>
+        <v>0.6456670929386015</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452117607450178</v>
+        <v>0.6452029663899245</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646144736015507</v>
+        <v>0.646129741039108</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6440144180039308</v>
+        <v>0.643994848821545</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6432780192777712</v>
+        <v>0.643253115796713</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444989392524534</v>
+        <v>0.6444703960142749</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6451134317446394</v>
+        <v>0.645083295070962</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6470104996406387</v>
+        <v>0.6469753563944955</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6536076911895319</v>
+        <v>0.6535779417950052</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6657724341549226</v>
+        <v>0.6657304303604077</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6731534161388255</v>
+        <v>0.6731063499093768</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6889599743812586</v>
+        <v>0.6889177713672915</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6978787875345487</v>
+        <v>0.6978470850272807</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7002744287788972</v>
+        <v>0.7002414003659978</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7005611572167961</v>
+        <v>0.7005277909971408</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082209037856434</v>
+        <v>0.7082116860388116</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082080236105111</v>
+        <v>0.7082011478581738</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107922055871276</v>
+        <v>0.7107980035591317</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7167231682641731</v>
+        <v>0.7167539707927009</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7168704470413499</v>
+        <v>0.7169029884174438</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7237369943513057</v>
+        <v>0.7237815662123354</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195535540247435</v>
+        <v>0.7195725359809422</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7228672503166875</v>
+        <v>0.7228888540216143</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224425456624755</v>
+        <v>0.722460786924488</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196664569085887</v>
+        <v>0.7196810380387995</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147357142756257</v>
+        <v>0.714735824382619</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165793386355314</v>
+        <v>0.7165817446382101</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164945344582652</v>
+        <v>0.7165008082332311</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151890547892783</v>
+        <v>0.7151961156049484</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129805889612528</v>
+        <v>0.7129855405681985</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104792441184191</v>
+        <v>0.7104869391322197</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104830003194224</v>
+        <v>0.710491627034036</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082136372039505</v>
+        <v>0.7082267935115744</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054530712136227</v>
+        <v>0.7054764769642279</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7035351847748142</v>
+        <v>0.7035609133482612</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.702742886636655</v>
+        <v>0.7027648859791649</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023823044057408</v>
+        <v>0.7023962062688064</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7019501818012657</v>
+        <v>0.7021158263183508</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7014528217671729</v>
+        <v>0.701687735915943</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.699757200388481</v>
+        <v>0.7000641513204777</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6980825855995649</v>
+        <v>0.6985963883280928</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6972556369735405</v>
+        <v>0.6978256672821881</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6943317824951805</v>
+        <v>0.6949921375702857</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6921094659599015</v>
+        <v>0.6928886004883842</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6904194356185266</v>
+        <v>0.6912714047326067</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6909184746039121</v>
+        <v>0.6917340546184045</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.693660461824243</v>
+        <v>0.6943164752739522</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.6999028287050569</v>
+        <v>0.7003764819546195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7033282348048673</v>
+        <v>0.7037942333186602</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7087041609476492</v>
+        <v>0.7087124887124302</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>0.7084038947381878</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506360256633488</v>
+        <v>0.6506375300708587</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514273832067492</v>
+        <v>0.6514281694038124</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524979889617589</v>
+        <v>0.6524993406153493</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649738928377951</v>
+        <v>0.6497394849380491</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464393772062913</v>
+        <v>0.6464399777607805</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431501356698576</v>
+        <v>0.6431507992044578</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408337816965325</v>
+        <v>0.6408344854884129</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398184219898762</v>
+        <v>0.6398191273224407</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424441128682713</v>
+        <v>0.6424475048305457</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643298753069672</v>
+        <v>0.643300792106526</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413914807171668</v>
+        <v>0.6413935057827396</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385149419134615</v>
+        <v>0.6385169920157909</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404611287182117</v>
+        <v>0.6404671468981976</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405326969179035</v>
+        <v>0.6405384799065545</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399681040637353</v>
+        <v>0.639971077480469</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423313028423472</v>
+        <v>0.6423337544134435</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451193799501327</v>
+        <v>0.6451240796902908</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470426129762076</v>
+        <v>0.6470487538066629</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.646666174454587</v>
+        <v>0.6466713474641402</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468436917526146</v>
+        <v>0.6468466819175542</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456670929386015</v>
+        <v>0.645672134397711</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452029663899245</v>
+        <v>0.6452117607450178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646129741039108</v>
+        <v>0.646144736015507</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643994848821545</v>
+        <v>0.6440144180039308</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.643253115796713</v>
+        <v>0.6432780192777712</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444703960142749</v>
+        <v>0.6444989392524534</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.645083295070962</v>
+        <v>0.6451134317446394</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6469753563944955</v>
+        <v>0.6470104996406387</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6535779417950052</v>
+        <v>0.6536076911895319</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6657304303604077</v>
+        <v>0.6657724341549226</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6731063499093768</v>
+        <v>0.6731534161388255</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6889177713672915</v>
+        <v>0.6889599743812586</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6978470850272807</v>
+        <v>0.6978787875345487</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7002414003659978</v>
+        <v>0.7002744287788972</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7005277909971408</v>
+        <v>0.7005611572167961</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082116860388116</v>
+        <v>0.7082209037856434</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082011478581738</v>
+        <v>0.7082080236105111</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107980035591317</v>
+        <v>0.7107922055871276</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7167539707927009</v>
+        <v>0.7167231682641731</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169029884174438</v>
+        <v>0.7168704470413499</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7237815662123354</v>
+        <v>0.7237369943513057</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195725359809422</v>
+        <v>0.7195535540247435</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7228888540216143</v>
+        <v>0.7228672503166875</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722460786924488</v>
+        <v>0.7224425456624755</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196810380387995</v>
+        <v>0.7196664569085887</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714735824382619</v>
+        <v>0.7147357142756257</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165817446382101</v>
+        <v>0.7165793386355314</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165008082332311</v>
+        <v>0.7164945344582652</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151961156049484</v>
+        <v>0.7151890547892783</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129855405681985</v>
+        <v>0.7129805889612528</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104869391322197</v>
+        <v>0.7104792441184191</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710491627034036</v>
+        <v>0.7104830003194224</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082267935115744</v>
+        <v>0.7082136372039505</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054764769642279</v>
+        <v>0.7054530712136227</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7035609133482612</v>
+        <v>0.7041144725984025</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027648859791649</v>
+        <v>0.7027286567063771</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023962062688064</v>
+        <v>0.7023237332540065</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7021158263183508</v>
+        <v>0.7021401773321635</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.701687735915943</v>
+        <v>0.701911566256165</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7000641513204777</v>
+        <v>0.7001647375026836</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6985963883280928</v>
+        <v>0.698655386979725</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6978256672821881</v>
+        <v>0.6977861965159152</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6949921375702857</v>
+        <v>0.6950291991515075</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6928886004883842</v>
+        <v>0.6929615223740209</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6912714047326067</v>
+        <v>0.6913109752532778</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6917340546184045</v>
+        <v>0.6913155595541196</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6943164752739522</v>
+        <v>0.6944938494731283</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7003764819546195</v>
+        <v>0.7011783071646771</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7037942333186602</v>
+        <v>0.7032335947726115</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7087124887124302</v>
+        <v>0.7104177049957563</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7084038947381878</v>
+        <v>0.7160462392198104</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506375300708587</v>
+        <v>0.6506345636249882</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514281694038124</v>
+        <v>0.6514266187615091</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524993406153493</v>
+        <v>0.6524966751130691</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497394849380491</v>
+        <v>0.6497383867126112</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464399777607805</v>
+        <v>0.6464387928176805</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431507992044578</v>
+        <v>0.6431494900878961</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408344854884129</v>
+        <v>0.6408330970036328</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398191273224407</v>
+        <v>0.639817735828798</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424475048305457</v>
+        <v>0.642440817040802</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643300792106526</v>
+        <v>0.6432967724504453</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413935057827396</v>
+        <v>0.6413895136155492</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385169920157909</v>
+        <v>0.6385129504485392</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404671468981976</v>
+        <v>0.6404552821160723</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405384799065545</v>
+        <v>0.6405270771594567</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639971077480469</v>
+        <v>0.6399652135939236</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423337544134435</v>
+        <v>0.6423289222529299</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451240796902908</v>
+        <v>0.645114814386232</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470487538066629</v>
+        <v>0.6470366437874209</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466713474641402</v>
+        <v>0.6466611447453758</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468466819175542</v>
+        <v>0.646840784902375</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645672134397711</v>
+        <v>0.6456621926230491</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452117607450178</v>
+        <v>0.6451944207119265</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646144736015507</v>
+        <v>0.6461151657510454</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6440144180039308</v>
+        <v>0.6439758257851209</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6432780192777712</v>
+        <v>0.6432289071912766</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444989392524534</v>
+        <v>0.6444426457550055</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6451134317446394</v>
+        <v>0.6450539920155859</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6470104996406387</v>
+        <v>0.6469411863506902</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6536076911895319</v>
+        <v>0.6535490290973811</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6657724341549226</v>
+        <v>0.6656895985963966</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6731534161388255</v>
+        <v>0.6730605984603732</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6889599743812586</v>
+        <v>0.6888767199277739</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6978787875345487</v>
+        <v>0.6978162432984004</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7002744287788972</v>
+        <v>0.7002092593581442</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7005611572167961</v>
+        <v>0.7004953055580608</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082209037856434</v>
+        <v>0.7082026864883192</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082080236105111</v>
+        <v>0.7081944207171409</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107922055871276</v>
+        <v>0.7108035975630385</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7167231682641731</v>
+        <v>0.7167839111183993</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7168704470413499</v>
+        <v>0.7169346301366488</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7237369943513057</v>
+        <v>0.7238249271640984</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195535540247435</v>
+        <v>0.7195909991494138</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7228672503166875</v>
+        <v>0.7229098715836206</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224425456624755</v>
+        <v>0.7224785452998665</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196664569085887</v>
+        <v>0.7196952421750272</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147357142756257</v>
+        <v>0.7147359352514793</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165793386355314</v>
+        <v>0.7165840958578695</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7164945344582652</v>
+        <v>0.7165069160939486</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151890547892783</v>
+        <v>0.7152029822532724</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129805889612528</v>
+        <v>0.7129903433252087</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104792441184191</v>
+        <v>0.7104943939493384</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104830003194224</v>
+        <v>0.7104999852503009</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082136372039505</v>
+        <v>0.7082395520321516</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054530712136227</v>
+        <v>0.7054992400377058</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041144725984025</v>
+        <v>0.7035859796752806</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027286567063771</v>
+        <v>0.7027863607178092</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023237332540065</v>
+        <v>0.7024098499802788</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7021401773321635</v>
+        <v>0.7023089282691704</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.701911566256165</v>
+        <v>0.7019502103136769</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7001647375026836</v>
+        <v>0.7003898437874417</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.698655386979725</v>
+        <v>0.6991259423865008</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6977861965159152</v>
+        <v>0.6983789117604933</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6950291991515075</v>
+        <v>0.6956661351435853</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6929615223740209</v>
+        <v>0.6936779267229958</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6913109752532778</v>
+        <v>0.6921336821582952</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6913155595541196</v>
+        <v>0.692569244903587</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6944938494731283</v>
+        <v>0.6950159955103378</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7011783071646771</v>
+        <v>0.7009294182873111</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7032335947726115</v>
+        <v>0.7043755614849146</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7104177049957563</v>
+        <v>0.709005148108642</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7160462392198104</v>
+        <v>0.7094956934166243</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506345636249882</v>
+        <v>0.6506360256633488</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514266187615091</v>
+        <v>0.6514273832067492</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524966751130691</v>
+        <v>0.6524979889617589</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497383867126112</v>
+        <v>0.649738928377951</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464387928176805</v>
+        <v>0.6464393772062913</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431494900878961</v>
+        <v>0.6431501356698576</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408330970036328</v>
+        <v>0.6408337816965325</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.639817735828798</v>
+        <v>0.6398184219898762</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642440817040802</v>
+        <v>0.6424441128682713</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432967724504453</v>
+        <v>0.643298753069672</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413895136155492</v>
+        <v>0.6413914807171668</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385129504485392</v>
+        <v>0.6385149419134615</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404552821160723</v>
+        <v>0.6404611287182117</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405270771594567</v>
+        <v>0.6405326969179035</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399652135939236</v>
+        <v>0.6399681040637353</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423289222529299</v>
+        <v>0.6423313028423472</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645114814386232</v>
+        <v>0.6451193799501327</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470366437874209</v>
+        <v>0.6470426129762076</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466611447453758</v>
+        <v>0.646666174454587</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646840784902375</v>
+        <v>0.6468436917526146</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456621926230491</v>
+        <v>0.6456670929386015</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451944207119265</v>
+        <v>0.6452029663899245</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6461151657510454</v>
+        <v>0.646129741039108</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439758257851209</v>
+        <v>0.643994848821545</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6432289071912766</v>
+        <v>0.643253115796713</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444426457550055</v>
+        <v>0.6444703960142749</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6450539920155859</v>
+        <v>0.645083295070962</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6469411863506902</v>
+        <v>0.6469753563944955</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6535490290973811</v>
+        <v>0.6535779417950052</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6656895985963966</v>
+        <v>0.6657304303604077</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6730605984603732</v>
+        <v>0.6731063499093768</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6888767199277739</v>
+        <v>0.6889177713672915</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6978162432984004</v>
+        <v>0.6978470850272807</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7002092593581442</v>
+        <v>0.7002414003659978</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7004953055580608</v>
+        <v>0.7005277909971408</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082026864883192</v>
+        <v>0.7082116860388116</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081944207171409</v>
+        <v>0.7082011478581738</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108035975630385</v>
+        <v>0.7107980035591317</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7167839111183993</v>
+        <v>0.7167539707927009</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169346301366488</v>
+        <v>0.7169029884174438</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7238249271640984</v>
+        <v>0.7237815662123354</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195909991494138</v>
+        <v>0.7195725359809422</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229098715836206</v>
+        <v>0.7228888540216143</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224785452998665</v>
+        <v>0.722460786924488</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196952421750272</v>
+        <v>0.7196810380387995</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147359352514793</v>
+        <v>0.714735824382619</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165840958578695</v>
+        <v>0.7165817446382101</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165069160939486</v>
+        <v>0.7165008082332311</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152029822532724</v>
+        <v>0.7151961156049484</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129903433252087</v>
+        <v>0.7129855405681985</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104943939493384</v>
+        <v>0.7104869391322197</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7104999852503009</v>
+        <v>0.710491627034036</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082395520321516</v>
+        <v>0.7082267935115744</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054992400377058</v>
+        <v>0.7054764769642279</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7035859796752806</v>
+        <v>0.7041403283051029</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027863607178092</v>
+        <v>0.7027517490526087</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024098499802788</v>
+        <v>0.702339457449063</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7023089282691704</v>
+        <v>0.7023373708634935</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7019502103136769</v>
+        <v>0.7021689368978568</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7003898437874417</v>
+        <v>0.7004988819945881</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6991259423865008</v>
+        <v>0.6992132581440411</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6983789117604933</v>
+        <v>0.6984249814866423</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6956661351435853</v>
+        <v>0.6957865881335688</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6936779267229958</v>
+        <v>0.6938775991773498</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6921336821582952</v>
+        <v>0.6923403515971727</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.692569244903587</v>
+        <v>0.6923714742937291</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6950159955103378</v>
+        <v>0.6954529559013941</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7009294182873111</v>
+        <v>0.7020465680376566</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7043755614849146</v>
+        <v>0.7043148866524551</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.709005148108642</v>
+        <v>0.7113292334373307</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7094956934166243</v>
+        <v>0.7165402739665685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506360256633488</v>
+        <v>0.6506331421908592</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514273832067492</v>
+        <v>0.6514258751780884</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524979889617589</v>
+        <v>0.6524953975053428</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649738928377951</v>
+        <v>0.6497378593536871</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464393772062913</v>
+        <v>0.6464382239523547</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431501356698576</v>
+        <v>0.6431488617410347</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408337816965325</v>
+        <v>0.6408324306439267</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398184219898762</v>
+        <v>0.6398170680692241</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424441128682713</v>
+        <v>0.6424376133196185</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643298753069672</v>
+        <v>0.6432948477752173</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413914807171668</v>
+        <v>0.6413876020256343</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385149419134615</v>
+        <v>0.6385110151420273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404611287182117</v>
+        <v>0.6404495998617322</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405326969179035</v>
+        <v>0.6405216138220885</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399681040637353</v>
+        <v>0.6399624026495996</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423313028423472</v>
+        <v>0.6423266096096932</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451193799501327</v>
+        <v>0.6451103773393355</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470426129762076</v>
+        <v>0.6470308391533364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.646666174454587</v>
+        <v>0.6466562524711523</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468436917526146</v>
+        <v>0.6468379579371746</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456670929386015</v>
+        <v>0.645657427613059</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6452029663899245</v>
+        <v>0.645186113323212</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646129741039108</v>
+        <v>0.6461009927917981</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643994848821545</v>
+        <v>0.6439573263795549</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.643253115796713</v>
+        <v>0.6432053648297514</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444703960142749</v>
+        <v>0.6444156559552542</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.645083295070962</v>
+        <v>0.6450254885551494</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6469753563944955</v>
+        <v>0.6469079497581218</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6535779417950052</v>
+        <v>0.6535209183704658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6657304303604077</v>
+        <v>0.6656498906198398</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6731063499093768</v>
+        <v>0.6730161076143478</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6889177713672915</v>
+        <v>0.6888367737247999</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6978470850272807</v>
+        <v>0.6977862279023144</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7002414003659978</v>
+        <v>0.7001779706510667</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7005277909971408</v>
+        <v>0.7004636667418334</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7082116860388116</v>
+        <v>0.7081938977409348</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7082011478581738</v>
+        <v>0.708187837818498</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7107980035591317</v>
+        <v>0.7108089976843217</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7167539707927009</v>
+        <v>0.7168130248416094</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169029884174438</v>
+        <v>0.7169654088599844</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7237815662123354</v>
+        <v>0.7238671257439939</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7195725359809422</v>
+        <v>0.7196089644280017</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7228888540216143</v>
+        <v>0.7229303264211252</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722460786924488</v>
+        <v>0.7224958395774704</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7196810380387995</v>
+        <v>0.7197090836192309</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714735824382619</v>
+        <v>0.7147360466959137</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165817446382101</v>
+        <v>0.716586394057583</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165008082332311</v>
+        <v>0.7165128645186141</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7151961156049484</v>
+        <v>0.7152096626433031</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129855405681985</v>
+        <v>0.7129950038249309</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7104869391322197</v>
+        <v>0.7105016195123973</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710491627034036</v>
+        <v>0.7105080871668624</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082267935115744</v>
+        <v>0.7082519303551186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7054764769642279</v>
+        <v>0.7055213862901426</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041403283051029</v>
+        <v>0.7036104085329684</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027517490526087</v>
+        <v>0.7028073286610819</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.702339457449063</v>
+        <v>0.7024232410356757</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7023373708634935</v>
+        <v>0.7024886577062611</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7021689368978568</v>
+        <v>0.7021925412456396</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7004988819945881</v>
+        <v>0.7006855696542575</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6992132581440411</v>
+        <v>0.6996109466150768</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6984249814866423</v>
+        <v>0.6988853203701277</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6957865881335688</v>
+        <v>0.6962827758999895</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6938775991773498</v>
+        <v>0.6943948369513119</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6923403515971727</v>
+        <v>0.692913077887488</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6923714742937291</v>
+        <v>0.6933177817702544</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6954529559013941</v>
+        <v>0.6956294467031124</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7020465680376566</v>
+        <v>0.7013875337490231</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7043148866524551</v>
+        <v>0.7048155485341665</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7113292334373307</v>
+        <v>0.7091561326238334</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7165402739665685</v>
+        <v>0.7096160025256699</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506331421908592</v>
+        <v>0.6506317596927212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514258751780884</v>
+        <v>0.651425151614363</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524953975053428</v>
+        <v>0.6524941546597208</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497378593536871</v>
+        <v>0.6497373457433255</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464382239523547</v>
+        <v>0.6464376700012517</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431488617410347</v>
+        <v>0.643148249949397</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408324306439267</v>
+        <v>0.640831781891959</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398170680692241</v>
+        <v>0.6398164179817967</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424376133196185</v>
+        <v>0.6424344978981159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432948477752173</v>
+        <v>0.6432929767080016</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413876020256343</v>
+        <v>0.6413857436315055</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385110151420273</v>
+        <v>0.6385091336526597</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404495998617322</v>
+        <v>0.6404440751255069</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405216138220885</v>
+        <v>0.6405163004698997</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399624026495996</v>
+        <v>0.6399596679948614</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423266096096932</v>
+        <v>0.6423243620476164</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451103773393355</v>
+        <v>0.6451060634637251</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470308391533364</v>
+        <v>0.6470251923713</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466562524711523</v>
+        <v>0.64665149208193</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468379579371746</v>
+        <v>0.646835207612801</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645657427613059</v>
+        <v>0.6456527923878236</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645186113323212</v>
+        <v>0.6451780344059105</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6461009927917981</v>
+        <v>0.6460872057453009</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439573263795549</v>
+        <v>0.6439393293087694</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6432053648297514</v>
+        <v>0.6431824616293464</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444156559552542</v>
+        <v>0.6443893958458458</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6450254885551494</v>
+        <v>0.6449977524879463</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6469079497581218</v>
+        <v>0.6468756089949305</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6535209183704658</v>
+        <v>0.6534935767791749</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6656498906198398</v>
+        <v>0.6656112607922532</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6730161076143478</v>
+        <v>0.6729728261218082</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6888367737247999</v>
+        <v>0.6887978888649219</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977862279023144</v>
+        <v>0.6977570061993423</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7001779706510667</v>
+        <v>0.7001475009577537</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7004636667418334</v>
+        <v>0.700432842119735</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081938977409348</v>
+        <v>0.7081853127173648</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708187837818498</v>
+        <v>0.7081813949361213</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108089976843217</v>
+        <v>0.7108142133747872</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7168130248416094</v>
+        <v>0.7168413456347238</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169654088599844</v>
+        <v>0.7169953592906912</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7238671257439939</v>
+        <v>0.7239082079375454</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196089644280017</v>
+        <v>0.7196264516115651</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229303264211252</v>
+        <v>0.7229502407278141</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224958395774704</v>
+        <v>0.7225126875914543</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197090836192309</v>
+        <v>0.7197225759663837</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147360466959137</v>
+        <v>0.7147361585479006</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716586394057583</v>
+        <v>0.7165886409310154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165128645186141</v>
+        <v>0.7165186596533408</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152096626433031</v>
+        <v>0.7152161642598077</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129950038249309</v>
+        <v>0.712999528277519</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105016195123973</v>
+        <v>0.7105086261157283</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105080871668624</v>
+        <v>0.7105159442614877</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082519303551186</v>
+        <v>0.7082639450569606</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055213862901426</v>
+        <v>0.7055429402227642</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7036104085329684</v>
+        <v>0.7036342235037893</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028073286610819</v>
+        <v>0.7028278068642112</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024232410356757</v>
+        <v>0.7024363848959009</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7024886577062611</v>
+        <v>0.7027398026754028</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7021925412456396</v>
+        <v>0.7025108452520095</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7006855696542575</v>
+        <v>0.7010664728616484</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.6996109466150768</v>
+        <v>0.7001194215486624</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6988853203701277</v>
+        <v>0.6994342071309737</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6962827758999895</v>
+        <v>0.6969707144583847</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6943948369513119</v>
+        <v>0.695214909198308</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.692913077887488</v>
+        <v>0.6938266834830649</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6933177817702544</v>
+        <v>0.6942392764291128</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6956294467031124</v>
+        <v>0.6964850518669754</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7013875337490231</v>
+        <v>0.7021927360961534</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7048155485341665</v>
+        <v>0.7057680085724247</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7091561326238334</v>
+        <v>0.7101168982691964</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7096160025256699</v>
+        <v>0.7118068855181607</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506317596927212</v>
+        <v>0.6506304145524804</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651425151614363</v>
+        <v>0.6514244472729129</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524941546597208</v>
+        <v>0.6524929451767129</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497373457433255</v>
+        <v>0.6497368453522192</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464376700012517</v>
+        <v>0.6464371303866859</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643148249949397</v>
+        <v>0.6431476540683354</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640831781891959</v>
+        <v>0.640831150059989</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398164179817967</v>
+        <v>0.6398157848751406</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424344978981159</v>
+        <v>0.6424314671765348</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432929767080016</v>
+        <v>0.6432911570410135</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413857436315055</v>
+        <v>0.6413839362442413</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385091336526597</v>
+        <v>0.6385073037674689</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404440751255069</v>
+        <v>0.640438701450755</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405163004698997</v>
+        <v>0.6405111310150099</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399596679948614</v>
+        <v>0.6399570065669354</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423243620476164</v>
+        <v>0.6423221768603652</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451060634637251</v>
+        <v>0.6451018677058191</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470251923713</v>
+        <v>0.6470196970973041</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.64665149208193</v>
+        <v>0.6466468583222018</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646835207612801</v>
+        <v>0.6468325308581391</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456527923878236</v>
+        <v>0.6456482817224954</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451780344059105</v>
+        <v>0.6451701746735787</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460872057453009</v>
+        <v>0.6460737890757703</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439393293087694</v>
+        <v>0.6439218144144304</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6431824616293464</v>
+        <v>0.6431601719530293</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6443893958458458</v>
+        <v>0.6443638362918949</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6449977524879463</v>
+        <v>0.6449707533139499</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6468756089949305</v>
+        <v>0.6468441284282505</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6534935767791749</v>
+        <v>0.6534669732528164</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6656112607922532</v>
+        <v>0.6655736659067707</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6729728261218082</v>
+        <v>0.672930705466621</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6887978888649219</v>
+        <v>0.6887600237406432</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977570061993423</v>
+        <v>0.6977285472394221</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7001475009577537</v>
+        <v>0.7001178186930546</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.700432842119735</v>
+        <v>0.7004028008850283</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081853127173648</v>
+        <v>0.7081769246370573</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081813949361213</v>
+        <v>0.7081750879833161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108142133747872</v>
+        <v>0.710819253500464</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7168413456347238</v>
+        <v>0.7168689053706021</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169953592906912</v>
+        <v>0.7170245143027025</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7239082079375454</v>
+        <v>0.7239482173433985</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196264516115651</v>
+        <v>0.7196434794634904</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229502407278141</v>
+        <v>0.7229696355512365</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225126875914543</v>
+        <v>0.7225291062806216</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197225759663837</v>
+        <v>0.7197357321471083</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147361585479006</v>
+        <v>0.7147362706559409</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165886409310154</v>
+        <v>0.7165908381053656</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165186596533408</v>
+        <v>0.7165243073331177</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152161642598077</v>
+        <v>0.7152224941913745</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.712999528277519</v>
+        <v>0.7130039225378946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105086261157283</v>
+        <v>0.7105154234522852</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105159442614877</v>
+        <v>0.7105235673431094</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082639450569606</v>
+        <v>0.7082756117725395</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055429402227642</v>
+        <v>0.7055639250686081</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7036342235037893</v>
+        <v>0.7036574470448833</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028278068642112</v>
+        <v>0.7028478116652349</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024363848959009</v>
+        <v>0.7024492869733376</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7027398026754028</v>
+        <v>0.7029741465484226</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7025108452520095</v>
+        <v>0.7028066939938208</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7010664728616484</v>
+        <v>0.7014136636981677</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7001194215486624</v>
+        <v>0.7005704467226066</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6994342071309737</v>
+        <v>0.6998933584887903</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6969707144583847</v>
+        <v>0.6975259420835321</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.695214909198308</v>
+        <v>0.6958471055262767</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6938266834830649</v>
+        <v>0.694504267818423</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6942392764291128</v>
+        <v>0.6948740304062649</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6964850518669754</v>
+        <v>0.696941765164354</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7021927360961534</v>
+        <v>0.7024549687155278</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7057680085724247</v>
+        <v>0.7058825354790234</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7101168982691964</v>
+        <v>0.7097883500277902</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7118068855181607</v>
+        <v>0.7103022007358228</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506304145524804</v>
+        <v>0.6506291052761825</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514244472729129</v>
+        <v>0.651423761398096</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524929451767129</v>
+        <v>0.6524917677309461</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497368453522192</v>
+        <v>0.6497363576778096</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464371303866859</v>
+        <v>0.6464366045603589</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431476540683354</v>
+        <v>0.6431470734861821</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640831150059989</v>
+        <v>0.6408305344955765</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398157848751406</v>
+        <v>0.6398151680934274</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424314671765348</v>
+        <v>0.6424285177481043</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432911570410135</v>
+        <v>0.6432893866860008</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413839362442413</v>
+        <v>0.6413821777933328</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385073037674689</v>
+        <v>0.6385055233931227</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640438701450755</v>
+        <v>0.6404334727287659</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405111310150099</v>
+        <v>0.6405060996943674</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399570065669354</v>
+        <v>0.6399544154647582</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423221768603652</v>
+        <v>0.6423200514894658</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451018677058191</v>
+        <v>0.6450977852845061</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470196970973041</v>
+        <v>0.6470143473223482</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466468583222018</v>
+        <v>0.6466423462116919</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468325308581391</v>
+        <v>0.646829924763794</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456482817224954</v>
+        <v>0.6456438906686416</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451701746735787</v>
+        <v>0.6451625253357619</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460737890757703</v>
+        <v>0.6460607280695349</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439218144144304</v>
+        <v>0.643904762601077</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6431601719530293</v>
+        <v>0.6431384715144859</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6443638362918949</v>
+        <v>0.6443389496859568</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6449707533139499</v>
+        <v>0.6449444621241713</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6468441284282505</v>
+        <v>0.6468134742848721</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6534669732528164</v>
+        <v>0.6534410783684071</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6655736659067707</v>
+        <v>0.6655370650287594</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.672930705466621</v>
+        <v>0.6728896996866753</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6887600237406432</v>
+        <v>0.6887231388840411</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977285472394221</v>
+        <v>0.6977008216546445</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7001178186930546</v>
+        <v>0.700088893866909</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7004028008850283</v>
+        <v>0.7003735137537155</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081769246370573</v>
+        <v>0.7081687270037518</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081750879833161</v>
+        <v>0.7081689130092416</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710819253500464</v>
+        <v>0.7108241263852879</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7168689053706021</v>
+        <v>0.716895734240887</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7170245143027025</v>
+        <v>0.717052905059169</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7239482173433985</v>
+        <v>0.7239871953257233</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196434794634904</v>
+        <v>0.7196600657817398</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229696355512365</v>
+        <v>0.7229885308654602</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225291062806216</v>
+        <v>0.7225451117434467</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197357321471083</v>
+        <v>0.7197485644673072</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147362706559409</v>
+        <v>0.7147363828834883</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165908381053656</v>
+        <v>0.7165929871442059</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165243073331177</v>
+        <v>0.716529813101206</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152224941913745</v>
+        <v>0.7152286591563168</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130039225378946</v>
+        <v>0.713008192130714</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105154234522852</v>
+        <v>0.710522020656571</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105235673431094</v>
+        <v>0.7105309665994571</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082756117725395</v>
+        <v>0.7082869452605195</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055639250686081</v>
+        <v>0.7055843628727001</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7036574470448833</v>
+        <v>0.7036801005527582</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028478116652349</v>
+        <v>0.7028673587193391</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024492869733376</v>
+        <v>0.7024619526201924</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7029741465484226</v>
+        <v>0.7031889613697464</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7028066939938208</v>
+        <v>0.7030743658920235</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7014136636981677</v>
+        <v>0.7017202081928795</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7005704467226066</v>
+        <v>0.7009634069481929</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6998933584887903</v>
+        <v>0.7002826938411688</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6975259420835321</v>
+        <v>0.6979936722937853</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6958471055262767</v>
+        <v>0.6963689862678258</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.694504267818423</v>
+        <v>0.6950546110636238</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6948740304062649</v>
+        <v>0.6953720392319331</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.696941765164354</v>
+        <v>0.6972485405414686</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7024549687155278</v>
+        <v>0.7025639236602197</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7058825354790234</v>
+        <v>0.7058411477958481</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7097883500277902</v>
+        <v>0.7093766040516738</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7103022007358228</v>
+        <v>0.7091243224131577</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506291052761825</v>
+        <v>0.6506331421908592</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651423761398096</v>
+        <v>0.6514258751780884</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524917677309461</v>
+        <v>0.6524953975053428</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497363576778096</v>
+        <v>0.6497378593536871</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464366045603589</v>
+        <v>0.6464382239523547</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431470734861821</v>
+        <v>0.6431488617410347</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408305344955765</v>
+        <v>0.6408324306439267</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398151680934274</v>
+        <v>0.6398170680692241</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424285177481043</v>
+        <v>0.6424376133196185</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432893866860008</v>
+        <v>0.6432948477752173</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413821777933328</v>
+        <v>0.6413876020256343</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385055233931227</v>
+        <v>0.6385110151420273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404334727287659</v>
+        <v>0.6404495998617322</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405060996943674</v>
+        <v>0.6405216138220885</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399544154647582</v>
+        <v>0.6399624026495996</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423200514894658</v>
+        <v>0.6423266096096932</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450977852845061</v>
+        <v>0.6451103773393355</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470143473223482</v>
+        <v>0.6470308391533364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466423462116919</v>
+        <v>0.6466562524711523</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646829924763794</v>
+        <v>0.6468379579371746</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456438906686416</v>
+        <v>0.645657427613059</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451625253357619</v>
+        <v>0.645186113323212</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460607280695349</v>
+        <v>0.6461009927917981</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643904762601077</v>
+        <v>0.6439573263795549</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6431384715144859</v>
+        <v>0.6432053648297514</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6443389496859568</v>
+        <v>0.6444156559552542</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6449444621241713</v>
+        <v>0.6450254885551494</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6468134742848721</v>
+        <v>0.6469079497581218</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6534410783684071</v>
+        <v>0.6535209183704658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6655370650287594</v>
+        <v>0.6656498906198398</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6728896996866753</v>
+        <v>0.6730161076143478</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6887231388840411</v>
+        <v>0.6888367737247999</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977008216546445</v>
+        <v>0.6977862279023144</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.700088893866909</v>
+        <v>0.7001779706510667</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7003735137537155</v>
+        <v>0.7004636667418334</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081687270037518</v>
+        <v>0.7081938977409348</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081689130092416</v>
+        <v>0.708187837818498</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108241263852879</v>
+        <v>0.7108089976843217</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.716895734240887</v>
+        <v>0.7168130248416094</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.717052905059169</v>
+        <v>0.7169654088599844</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7239871953257233</v>
+        <v>0.7238671257439939</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196600657817398</v>
+        <v>0.7196089644280017</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229885308654602</v>
+        <v>0.7229303264211252</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225451117434467</v>
+        <v>0.7224958395774704</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197485644673072</v>
+        <v>0.7197090836192309</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147363828834883</v>
+        <v>0.7147360466959137</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165929871442059</v>
+        <v>0.716586394057583</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716529813101206</v>
+        <v>0.7165128645186141</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152286591563168</v>
+        <v>0.7152096626433031</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.713008192130714</v>
+        <v>0.7129950038249309</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710522020656571</v>
+        <v>0.7105016195123973</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105309665994571</v>
+        <v>0.7105080871668624</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082869452605195</v>
+        <v>0.7082519303551186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055843628727001</v>
+        <v>0.7055213862901426</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7036801005527582</v>
+        <v>0.7041900305870703</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028673587193391</v>
+        <v>0.7027962686784517</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024619526201924</v>
+        <v>0.7023699676875426</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031889613697464</v>
+        <v>0.7026129882619758</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7030743658920235</v>
+        <v>0.7028814955939346</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7017202081928795</v>
+        <v>0.7014431799487413</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7009634069481929</v>
+        <v>0.7003662037935038</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7002826938411688</v>
+        <v>0.6998075835638591</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6979936722937853</v>
+        <v>0.6974984799116895</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6963689862678258</v>
+        <v>0.6958783186171537</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6950546110636238</v>
+        <v>0.6945735428255351</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6953720392319331</v>
+        <v>0.6946854512232983</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6972485405414686</v>
+        <v>0.6976543948878018</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7025639236602197</v>
+        <v>0.7041258937263921</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7058411477958481</v>
+        <v>0.7067789613414894</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7093766040516738</v>
+        <v>0.7136316293130355</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7091243224131577</v>
+        <v>0.7188694383217605</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>0.7195677968801257</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506331421908592</v>
+        <v>0.6506278304484789</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514258751780884</v>
+        <v>0.6514230932733474</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524953975053428</v>
+        <v>0.6524906210663228</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497378593536871</v>
+        <v>0.6497358822426237</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464382239523547</v>
+        <v>0.6464360920015184</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431488617410347</v>
+        <v>0.6431465076221713</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408324306439267</v>
+        <v>0.6408299345793477</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398170680692241</v>
+        <v>0.6398145670141236</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424376133196185</v>
+        <v>0.6424256463862843</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432948477752173</v>
+        <v>0.6432876636662653</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413876020256343</v>
+        <v>0.641380466318787</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385110151420273</v>
+        <v>0.6385037905479493</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404495998617322</v>
+        <v>0.6404283831756459</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405216138220885</v>
+        <v>0.6405012010483826</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399624026495996</v>
+        <v>0.6399518919384455</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423266096096932</v>
+        <v>0.6423179835143518</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451103773393355</v>
+        <v>0.64509381167304</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470308391533364</v>
+        <v>0.6470091373506428</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466562524711523</v>
+        <v>0.6466379510275921</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468379579371746</v>
+        <v>0.6468273865715963</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645657427613059</v>
+        <v>0.645639614536222</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645186113323212</v>
+        <v>0.645155078065353</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6461009927917981</v>
+        <v>0.646048008781412</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439573263795549</v>
+        <v>0.6438881557670749</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6432053648297514</v>
+        <v>0.6431173372904679</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6444156559552542</v>
+        <v>0.6443147098494337</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6450254885551494</v>
+        <v>0.6449188514985151</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6469079497581218</v>
+        <v>0.646783614531837</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6535209183704658</v>
+        <v>0.6534158642431056</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6656498906198398</v>
+        <v>0.6655014193487749</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6730161076143478</v>
+        <v>0.6728497652084415</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6888367737247999</v>
+        <v>0.6886871968314542</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977862279023144</v>
+        <v>0.6976738015598514</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7001779706510667</v>
+        <v>0.7000606979854662</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7004636667418334</v>
+        <v>0.7003449528724167</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081938977409348</v>
+        <v>0.7081607135917513</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708187837818498</v>
+        <v>0.7081628661951842</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108089976843217</v>
+        <v>0.7108288398510002</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7168130248416094</v>
+        <v>0.7169218608651287</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169654088599844</v>
+        <v>0.717080561121922</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7238671257439939</v>
+        <v>0.7240251811551235</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196089644280017</v>
+        <v>0.7196762274599071</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229303264211252</v>
+        <v>0.723006945638299</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7224958395774704</v>
+        <v>0.7225607192891266</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197090836192309</v>
+        <v>0.7197610846450277</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147360466959137</v>
+        <v>0.7147364951075359</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716586394057583</v>
+        <v>0.7165950895502149</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165128645186141</v>
+        <v>0.7165351822271063</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152096626433031</v>
+        <v>0.715234665526564</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7129950038249309</v>
+        <v>0.7130123422732665</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105016195123973</v>
+        <v>0.7105284263439624</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105080871668624</v>
+        <v>0.7105381516407041</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082519303551186</v>
+        <v>0.7082979594634484</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055213862901426</v>
+        <v>0.7056042745662897</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041900305870703</v>
+        <v>0.7037022044237071</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7027962686784517</v>
+        <v>0.70288646303152</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023699676875426</v>
+        <v>0.7024743871187982</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7026129882619758</v>
+        <v>0.7031897545143252</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7028814955939346</v>
+        <v>0.7033894849195992</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7014431799487413</v>
+        <v>0.7021440999235868</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7003662037935038</v>
+        <v>0.7013903178703345</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.6998075835638591</v>
+        <v>0.7007641557182192</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6974984799116895</v>
+        <v>0.6985144611529857</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6958783186171537</v>
+        <v>0.6967536931603593</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6945735428255351</v>
+        <v>0.6953359333329596</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6946854512232983</v>
+        <v>0.6957196464162986</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6976543948878018</v>
+        <v>0.6974173454871824</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7041258937263921</v>
+        <v>0.7023907281882196</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7067789613414894</v>
+        <v>0.7053036369545483</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7136316293130355</v>
+        <v>0.7082838677213177</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7188694383217605</v>
+        <v>0.7070176344147128</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7195677968801257</v>
+        <v>0.6954676344147127</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506278304484789</v>
+        <v>0.6506317596927212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514230932733474</v>
+        <v>0.651425151614363</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524906210663228</v>
+        <v>0.6524941546597208</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497358822426237</v>
+        <v>0.6497373457433255</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464360920015184</v>
+        <v>0.6464376700012517</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431465076221713</v>
+        <v>0.643148249949397</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408299345793477</v>
+        <v>0.640831781891959</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398145670141236</v>
+        <v>0.6398164179817967</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424256463862843</v>
+        <v>0.6424344978981159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432876636662653</v>
+        <v>0.6432929767080016</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.641380466318787</v>
+        <v>0.6413857436315055</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385037905479493</v>
+        <v>0.6385091336526597</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404283831756459</v>
+        <v>0.6404440751255069</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405012010483826</v>
+        <v>0.6405163004698997</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399518919384455</v>
+        <v>0.6399596679948614</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423179835143518</v>
+        <v>0.6423243620476164</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.64509381167304</v>
+        <v>0.6451060634637251</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470091373506428</v>
+        <v>0.6470251923713</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466379510275921</v>
+        <v>0.64665149208193</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468273865715963</v>
+        <v>0.646835207612801</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645639614536222</v>
+        <v>0.6456527923878236</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645155078065353</v>
+        <v>0.6451780344059105</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.646048008781412</v>
+        <v>0.6460872057453009</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6438881557670749</v>
+        <v>0.6439393293087694</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6431173372904679</v>
+        <v>0.6431824616293464</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6443147098494337</v>
+        <v>0.6443893958458458</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6449188514985151</v>
+        <v>0.6449977524879463</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.646783614531837</v>
+        <v>0.6468756089949305</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6534158642431056</v>
+        <v>0.6534935767791749</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6655014193487749</v>
+        <v>0.6656112607922532</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6728497652084415</v>
+        <v>0.6729728261218082</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6886871968314542</v>
+        <v>0.6887978888649219</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6976738015598514</v>
+        <v>0.6977570061993423</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7000606979854662</v>
+        <v>0.7001475009577537</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7003449528724167</v>
+        <v>0.700432842119735</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081607135917513</v>
+        <v>0.7081853127173648</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081628661951842</v>
+        <v>0.7081813949361213</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108288398510002</v>
+        <v>0.7108142133747872</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7169218608651287</v>
+        <v>0.7168413456347238</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.717080561121922</v>
+        <v>0.7169953592906912</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7240251811551235</v>
+        <v>0.7239082079375454</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196762274599071</v>
+        <v>0.7196264516115651</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.723006945638299</v>
+        <v>0.7229502407278141</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225607192891266</v>
+        <v>0.7225126875914543</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197610846450277</v>
+        <v>0.7197225759663837</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147364951075359</v>
+        <v>0.7147361585479006</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165950895502149</v>
+        <v>0.7165886409310154</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165351822271063</v>
+        <v>0.7165186596533408</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715234665526564</v>
+        <v>0.7152161642598077</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130123422732665</v>
+        <v>0.712999528277519</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105284263439624</v>
+        <v>0.7105086261157283</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105381516407041</v>
+        <v>0.7105159442614877</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082979594634484</v>
+        <v>0.7082639450569606</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056042745662897</v>
+        <v>0.7055429402227642</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037022044237071</v>
+        <v>0.7042139278053381</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.70288646303152</v>
+        <v>0.7028177342412885</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024743871187982</v>
+        <v>0.7023847695901424</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031897545143252</v>
+        <v>0.7026182076690484</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7033894849195992</v>
+        <v>0.7030705726605275</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7021440999235868</v>
+        <v>0.7017358925081676</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7013903178703345</v>
+        <v>0.7006760823197304</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7007641557182192</v>
+        <v>0.7002166480767342</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6985144611529857</v>
+        <v>0.698018078280878</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6967536931603593</v>
+        <v>0.6964642461974644</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6953359333329596</v>
+        <v>0.6952104689839552</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6957196464162986</v>
+        <v>0.6953001243542135</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6974173454871824</v>
+        <v>0.6981445560571244</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7023907281882196</v>
+        <v>0.7043337028433767</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7053036369545483</v>
+        <v>0.7069102620714722</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7082838677213177</v>
+        <v>0.7131924341191862</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7070176344147128</v>
+        <v>0.7170677405229074</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.6954676344147127</v>
+        <v>0.71316700705758</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506317596927212</v>
+        <v>0.6506265887275247</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651425151614363</v>
+        <v>0.6514224422186886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524941546597208</v>
+        <v>0.6524895039915533</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497373457433255</v>
+        <v>0.6497354185927324</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464376700012517</v>
+        <v>0.6464355922152545</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643148249949397</v>
+        <v>0.6431459559245156</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640831781891959</v>
+        <v>0.6408293497229316</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398164179817967</v>
+        <v>0.6398139810459065</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424344978981159</v>
+        <v>0.642422850033005</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432929767080016</v>
+        <v>0.6432859861093152</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413857436315055</v>
+        <v>0.6413787999638528</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385091336526597</v>
+        <v>0.6385021033545939</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404440751255069</v>
+        <v>0.6404234273110234</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405163004698997</v>
+        <v>0.6404964299012311</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399596679948614</v>
+        <v>0.6399494333795763</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423243620476164</v>
+        <v>0.6423159706432034</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451060634637251</v>
+        <v>0.6450899425823622</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470251923713</v>
+        <v>0.647004061779491</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.64665149208193</v>
+        <v>0.6466336682881569</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646835207612801</v>
+        <v>0.646824913664915</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456527923878236</v>
+        <v>0.645635448876961</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451780344059105</v>
+        <v>0.6451478249684921</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460872057453009</v>
+        <v>0.6460356179852272</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439393293087694</v>
+        <v>0.643871976740878</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6431824616293464</v>
+        <v>0.6430967474398689</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6443893958458458</v>
+        <v>0.6442910919415029</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6449977524879463</v>
+        <v>0.6448938954113852</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6468756089949305</v>
+        <v>0.6467545187660865</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6534935767791749</v>
+        <v>0.6533913044349499</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6656112607922532</v>
+        <v>0.665466692046761</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6729728261218082</v>
+        <v>0.6728108606941953</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6887978888649219</v>
+        <v>0.6886521619982734</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977570061993423</v>
+        <v>0.6976474604606007</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7001475009577537</v>
+        <v>0.7000332039594248</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.700432842119735</v>
+        <v>0.7003170917327914</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081853127173648</v>
+        <v>0.7081528784328843</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081813949361213</v>
+        <v>0.7081569438507325</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108142133747872</v>
+        <v>0.710833401253633</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7168413456347238</v>
+        <v>0.7169473123915413</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7169953592906912</v>
+        <v>0.7171075105526671</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7239082079375454</v>
+        <v>0.7240622121390482</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196264516115651</v>
+        <v>0.7196919805437194</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229502407278141</v>
+        <v>0.7230248978935805</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225126875914543</v>
+        <v>0.7225759434849899</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197225759663837</v>
+        <v>0.7197733038447809</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147361585479006</v>
+        <v>0.7147366072173471</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165886409310154</v>
+        <v>0.7165971467678068</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165186596533408</v>
+        <v>0.7165404197232143</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152161642598077</v>
+        <v>0.7152405193497268</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.712999528277519</v>
+        <v>0.7130163778964975</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105086261157283</v>
+        <v>0.7105346486467849</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105159442614877</v>
+        <v>0.7105451315395077</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082639450569606</v>
+        <v>0.7083086675629948</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055429402227642</v>
+        <v>0.7056236800356451</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042139278053381</v>
+        <v>0.7037237781102633</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028177342412885</v>
+        <v>0.7029051389876313</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023847695901424</v>
+        <v>0.7024865956736135</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7026182076690484</v>
+        <v>0.7031906334007276</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7030705726605275</v>
+        <v>0.703540369677299</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7017358925081676</v>
+        <v>0.7023830670699369</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7006760823197304</v>
+        <v>0.7016110995564884</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7002166480767342</v>
+        <v>0.7009597407424454</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.698018078280878</v>
+        <v>0.6986773460553048</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6964642461974644</v>
+        <v>0.6968216193808384</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6952104689839552</v>
+        <v>0.6952716917912067</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6953001243542135</v>
+        <v>0.6954227168211491</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6981445560571244</v>
+        <v>0.6973312500869588</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7043337028433767</v>
+        <v>0.7019465719159135</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7069102620714722</v>
+        <v>0.7044678107173135</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7131924341191862</v>
+        <v>0.7069015789192139</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7170677405229074</v>
+        <v>0.7046891023155779</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.71316700705758</v>
+        <v>0.6931391023155778</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506265887275247</v>
+        <v>0.6506304145524804</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514224422186886</v>
+        <v>0.6514244472729129</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524895039915533</v>
+        <v>0.6524929451767129</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497354185927324</v>
+        <v>0.6497368453522192</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464355922152545</v>
+        <v>0.6464371303866859</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431459559245156</v>
+        <v>0.6431476540683354</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408293497229316</v>
+        <v>0.640831150059989</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398139810459065</v>
+        <v>0.6398157848751406</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642422850033005</v>
+        <v>0.6424314671765348</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432859861093152</v>
+        <v>0.6432911570410135</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413787999638528</v>
+        <v>0.6413839362442413</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385021033545939</v>
+        <v>0.6385073037674689</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404234273110234</v>
+        <v>0.640438701450755</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404964299012311</v>
+        <v>0.6405111310150099</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399494333795763</v>
+        <v>0.6399570065669354</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423159706432034</v>
+        <v>0.6423221768603652</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450899425823622</v>
+        <v>0.6451018677058191</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.647004061779491</v>
+        <v>0.6470196970973041</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466336682881569</v>
+        <v>0.6466468583222018</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646824913664915</v>
+        <v>0.6468325308581391</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645635448876961</v>
+        <v>0.6456482817224954</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451478249684921</v>
+        <v>0.6451701746735787</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460356179852272</v>
+        <v>0.6460737890757703</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643871976740878</v>
+        <v>0.6439218144144304</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430967474398689</v>
+        <v>0.6431601719530293</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6442910919415029</v>
+        <v>0.6443638362918949</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448938954113852</v>
+        <v>0.6449707533139499</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6467545187660865</v>
+        <v>0.6468441284282505</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6533913044349499</v>
+        <v>0.6534669732528164</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.665466692046761</v>
+        <v>0.6655736659067707</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6728108606941953</v>
+        <v>0.672930705466621</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6886521619982734</v>
+        <v>0.6887600237406432</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6976474604606007</v>
+        <v>0.6977285472394221</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7000332039594248</v>
+        <v>0.7001178186930546</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7003170917327914</v>
+        <v>0.7004028008850283</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081528784328843</v>
+        <v>0.7081769246370573</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081569438507325</v>
+        <v>0.7081750879833161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710833401253633</v>
+        <v>0.710819253500464</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7169473123915413</v>
+        <v>0.7168689053706021</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7171075105526671</v>
+        <v>0.7170245143027025</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7240622121390482</v>
+        <v>0.7239482173433985</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196919805437194</v>
+        <v>0.7196434794634904</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7230248978935805</v>
+        <v>0.7229696355512365</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225759434849899</v>
+        <v>0.7225291062806216</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197733038447809</v>
+        <v>0.7197357321471083</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147366072173471</v>
+        <v>0.7147362706559409</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165971467678068</v>
+        <v>0.7165908381053656</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165404197232143</v>
+        <v>0.7165243073331177</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152405193497268</v>
+        <v>0.7152224941913745</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130163778964975</v>
+        <v>0.7130039225378946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105346486467849</v>
+        <v>0.7105154234522852</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105451315395077</v>
+        <v>0.7105235673431094</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083086675629948</v>
+        <v>0.7082756117725395</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056236800356451</v>
+        <v>0.7055639250686081</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037237781102633</v>
+        <v>0.7042372207693928</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029051389876313</v>
+        <v>0.7028386944366511</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024865956736135</v>
+        <v>0.7023992796264562</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031906334007276</v>
+        <v>0.7026234069008591</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.703540369677299</v>
+        <v>0.7033948952550702</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7023830670699369</v>
+        <v>0.7021824106027867</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7016110995564884</v>
+        <v>0.7011621516724162</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7009597407424454</v>
+        <v>0.7008448809008829</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6986773460553048</v>
+        <v>0.6987821595759001</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6968216193808384</v>
+        <v>0.6973137455115075</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6952716917912067</v>
+        <v>0.6961432613920072</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6954227168211491</v>
+        <v>0.6962534670065306</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6973312500869588</v>
+        <v>0.699033482832527</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7019465719159135</v>
+        <v>0.7051109672127094</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7044678107173135</v>
+        <v>0.7077561183889534</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7069015789192139</v>
+        <v>0.7138481735784996</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7046891023155779</v>
+        <v>0.7175251476235673</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.6931391023155778</v>
+        <v>0.7151839920673044</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506304145524804</v>
+        <v>0.6506253788402678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514244472729129</v>
+        <v>0.6514218075884215</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524929451767129</v>
+        <v>0.6524884153760298</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497368453522192</v>
+        <v>0.6497349662963221</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464371303866859</v>
+        <v>0.6464351047309194</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431476540683354</v>
+        <v>0.6431454178686243</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640831150059989</v>
+        <v>0.640828779367047</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398157848751406</v>
+        <v>0.6398134096267358</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424314671765348</v>
+        <v>0.6424201257878174</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432911570410135</v>
+        <v>0.6432843522400911</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413839362442413</v>
+        <v>0.6413771769683158</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385073037674689</v>
+        <v>0.6385004600332475</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640438701450755</v>
+        <v>0.640418599938407</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6405111310150099</v>
+        <v>0.640491781342665</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399570065669354</v>
+        <v>0.6399470373122161</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423221768603652</v>
+        <v>0.6423140107045082</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6451018677058191</v>
+        <v>0.6450861739457165</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6470196970973041</v>
+        <v>0.6469991154806989</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466468583222018</v>
+        <v>0.6466294937375356</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468325308581391</v>
+        <v>0.6468225035597053</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456482817224954</v>
+        <v>0.6456313894689846</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451701746735787</v>
+        <v>0.6451407585567805</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460737890757703</v>
+        <v>0.6460235431281022</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6439218144144304</v>
+        <v>0.6438562092221271</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6431601719530293</v>
+        <v>0.6430766812289302</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6443638362918949</v>
+        <v>0.6442680723749116</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6449707533139499</v>
+        <v>0.6448695691443636</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6468441284282505</v>
+        <v>0.6467261581123822</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6534669732528164</v>
+        <v>0.6533673738511543</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6655736659067707</v>
+        <v>0.6654328481665047</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.672930705466621</v>
+        <v>0.6727729469007868</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6887600237406432</v>
+        <v>0.6886180005629715</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6977285472394221</v>
+        <v>0.6976217731678744</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7001178186930546</v>
+        <v>0.7000063860189925</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7004028008850283</v>
+        <v>0.7002899050919711</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081769246370573</v>
+        <v>0.708145215804131</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081750879833161</v>
+        <v>0.7081511424098914</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710819253500464</v>
+        <v>0.7108378175169106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7168689053706021</v>
+        <v>0.7169721145901264</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7170245143027025</v>
+        <v>0.7171337800066269</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7239482173433985</v>
+        <v>0.7240983237426052</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196434794634904</v>
+        <v>0.7197073402833705</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7229696355512365</v>
+        <v>0.7230424047688674</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225291062806216</v>
+        <v>0.7225907982005597</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197357321471083</v>
+        <v>0.7197852327095119</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147362706559409</v>
+        <v>0.7147367191133103</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165908381053656</v>
+        <v>0.7165991601856548</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165243073331177</v>
+        <v>0.71654553036028</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152224941913745</v>
+        <v>0.7152462263694939</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130039225378946</v>
+        <v>0.7130203036643362</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105154234522852</v>
+        <v>0.7105406952474377</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105235673431094</v>
+        <v>0.7105519148677892</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7082756117725395</v>
+        <v>0.7083190820307872</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7055639250686081</v>
+        <v>0.7056425981858635</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042372207693928</v>
+        <v>0.7037448401739788</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028386944366511</v>
+        <v>0.7029234003838816</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7023992796264562</v>
+        <v>0.7024985834046984</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7026234069008591</v>
+        <v>0.7031915911978887</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7033948952550702</v>
+        <v>0.7038187683413706</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7021824106027867</v>
+        <v>0.7027564490107222</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7011621516724162</v>
+        <v>0.701988462271931</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7008448809008829</v>
+        <v>0.7013532831729243</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6987821595759001</v>
+        <v>0.699048560158705</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6973137455115075</v>
+        <v>0.6971501208085771</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6961432613920072</v>
+        <v>0.6955212366721334</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6962534670065306</v>
+        <v>0.6957759283172598</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.699033482832527</v>
+        <v>0.697522386343927</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7051109672127094</v>
+        <v>0.7018697314500633</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7077561183889534</v>
+        <v>0.7041442807170237</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7138481735784996</v>
+        <v>0.7062361532497635</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7175251476235673</v>
+        <v>0.7037332490896404</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7151839920673044</v>
+        <v>0.6920975193433073</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506253788402678</v>
+        <v>0.6506241995780968</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514218075884215</v>
+        <v>0.6514211887689964</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524884153760298</v>
+        <v>0.6524873541460119</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497349662963221</v>
+        <v>0.6497345249423665</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464351047309194</v>
+        <v>0.6464346291006617</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431454178686243</v>
+        <v>0.6431448929554502</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640828779367047</v>
+        <v>0.6408282229797277</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398134096267358</v>
+        <v>0.6398128522220665</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424201257878174</v>
+        <v>0.6424174708978678</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432843522400911</v>
+        <v>0.6432827603747119</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413771769683158</v>
+        <v>0.6413755956623057</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385004600332475</v>
+        <v>0.6384988588953929</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640418599938407</v>
+        <v>0.6404138961270471</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640491781342665</v>
+        <v>0.6404872507112067</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399470373122161</v>
+        <v>0.6399447013846125</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423140107045082</v>
+        <v>0.6423121016392749</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450861739457165</v>
+        <v>0.6450825019044427</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469991154806989</v>
+        <v>0.6469942935833819</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466294937375356</v>
+        <v>0.6466254233317318</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468225035597053</v>
+        <v>0.6468201538962224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456313894689846</v>
+        <v>0.6456274323026113</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451407585567805</v>
+        <v>0.6451338717216037</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460235431281022</v>
+        <v>0.6460117722881842</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6438562092221271</v>
+        <v>0.6438408377271603</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430766812289302</v>
+        <v>0.6430571189620491</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6442680723749116</v>
+        <v>0.6442456287380387</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448695691443636</v>
+        <v>0.6448458492053524</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6467261581123822</v>
+        <v>0.6466985051287802</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6533673738511543</v>
+        <v>0.6533440486633126</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6654328481665047</v>
+        <v>0.6653998544994566</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6727729469007868</v>
+        <v>0.6727359865489583</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6886180005629715</v>
+        <v>0.688584680359589</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6976217731678744</v>
+        <v>0.6975967157189621</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7000063860189925</v>
+        <v>0.6999802196349135</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7002899050919711</v>
+        <v>0.7002633688985245</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708145215804131</v>
+        <v>0.7081377202158823</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081511424098914</v>
+        <v>0.7081454584271775</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108378175169106</v>
+        <v>0.7108420951628645</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7169721145901264</v>
+        <v>0.7169962919388305</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7171337800066269</v>
+        <v>0.7171593948192809</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7240983237426052</v>
+        <v>0.7241335497005865</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197073402833705</v>
+        <v>0.7197223211820408</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7230424047688674</v>
+        <v>0.723059482569019</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225907982005597</v>
+        <v>0.7226052966485377</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197852327095119</v>
+        <v>0.7197968813904064</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147367191133103</v>
+        <v>0.714736830705907</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165991601856548</v>
+        <v>0.7166011311391088</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.71654553036028</v>
+        <v>0.7165505186817653</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152462263694939</v>
+        <v>0.7152517920445068</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130203036643362</v>
+        <v>0.7130241239914792</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105406952474377</v>
+        <v>0.710546573408849</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105519148677892</v>
+        <v>0.7105585097305506</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083190820307872</v>
+        <v>0.7083292146752562</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056425981858635</v>
+        <v>0.705661047000107</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037448401739788</v>
+        <v>0.7037654083347981</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029234003838816</v>
+        <v>0.7029412604548461</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024985834046984</v>
+        <v>0.7025103553424636</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031915911978887</v>
+        <v>0.7031926215691549</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7038187683413706</v>
+        <v>0.7042976291744729</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7027564490107222</v>
+        <v>0.7033630694220023</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.701988462271931</v>
+        <v>0.7026484894597225</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7013532831729243</v>
+        <v>0.702120597532879</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.699048560158705</v>
+        <v>0.6997673340264207</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6971501208085771</v>
+        <v>0.6978937872843309</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6955212366721334</v>
+        <v>0.6962523198527796</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6957759283172598</v>
+        <v>0.6965640627146639</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.697522386343927</v>
+        <v>0.698212017019715</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7018697314500633</v>
+        <v>0.7024243562949681</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7041442807170237</v>
+        <v>0.7046519840080978</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7062361532497635</v>
+        <v>0.7066516940751681</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7037332490896404</v>
+        <v>0.7045213300002104</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.6920975193433073</v>
+        <v>0.6966357243510051</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506241995780968</v>
+        <v>0.650623049792815</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514211887689964</v>
+        <v>0.6514205851770357</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524873541460119</v>
+        <v>0.6524863192810965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497345249423665</v>
+        <v>0.649734094139395</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464346291006617</v>
+        <v>0.6464341648980662</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431448929554502</v>
+        <v>0.6431443807099571</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408282229797277</v>
+        <v>0.6408276800546797</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398128522220665</v>
+        <v>0.6398123083231884</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424174708978678</v>
+        <v>0.6424148827486327</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432827603747119</v>
+        <v>0.6432812089146989</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413755956623057</v>
+        <v>0.6413740544605775</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384988588953929</v>
+        <v>0.6384972983380304</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404138961270471</v>
+        <v>0.6404093111951724</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404872507112067</v>
+        <v>0.6404828335786029</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399447013846125</v>
+        <v>0.6399424233615105</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423121016392749</v>
+        <v>0.6423102414938445</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450825019044427</v>
+        <v>0.6450789227948452</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469942935833819</v>
+        <v>0.6469895914580449</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466254233317318</v>
+        <v>0.6466214532256001</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468201538962224</v>
+        <v>0.6468178624313556</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456274323026113</v>
+        <v>0.6456235735672022</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451338717216037</v>
+        <v>0.6451271577103801</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460117722881842</v>
+        <v>0.6460002941355191</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6438408377271603</v>
+        <v>0.6438258475385623</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430571189620491</v>
+        <v>0.6430380419177006</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6442456287380387</v>
+        <v>0.6442237397226881</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448458492053524</v>
+        <v>0.6448227132536319</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6466985051287802</v>
+        <v>0.6466715337190192</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6533440486633126</v>
+        <v>0.6533213062289012</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6653998544994566</v>
+        <v>0.6653676794771137</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6727359865489583</v>
+        <v>0.6726999442022983</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.688584680359589</v>
+        <v>0.6885521707779658</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6975967157189621</v>
+        <v>0.6975722653040052</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6999802196349135</v>
+        <v>0.6999546814450734</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7002633688985245</v>
+        <v>0.7002374602235144</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081377202158823</v>
+        <v>0.7081303864008028</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081454584271775</v>
+        <v>0.7081398885737189</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108420951628645</v>
+        <v>0.7108462403399268</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7169962919388305</v>
+        <v>0.7170198677033319</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7171593948192809</v>
+        <v>0.7171843790867836</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7241335497005865</v>
+        <v>0.7241679221214423</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197223211820408</v>
+        <v>0.7197369370409229</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.723059482569019</v>
+        <v>0.7230761468159315</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226052966485377</v>
+        <v>0.7226194514229582</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197968813904064</v>
+        <v>0.7198082595747006</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714736830705907</v>
+        <v>0.7147369419147811</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166011311391088</v>
+        <v>0.7166030609125131</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165505186817653</v>
+        <v>0.7165553890171925</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152517920445068</v>
+        <v>0.7152572215658441</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130241239914792</v>
+        <v>0.7130278430597795</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710546573408849</v>
+        <v>0.7105522900025081</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105585097305506</v>
+        <v>0.7105649237970089</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083292146752562</v>
+        <v>0.7083390766848403</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.705661047000107</v>
+        <v>0.7056790435946383</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037654083347981</v>
+        <v>0.7037854995172645</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029412604548461</v>
+        <v>0.7029587319000646</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025103553424636</v>
+        <v>0.7025219164235283</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031926215691549</v>
+        <v>0.7031937186340711</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7042976291744729</v>
+        <v>0.7047479486374102</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7033630694220023</v>
+        <v>0.7039449633791038</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7026484894597225</v>
+        <v>0.7033075703197202</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.702120597532879</v>
+        <v>0.7029309399217827</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.6997673340264207</v>
+        <v>0.7006492802845221</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6978937872843309</v>
+        <v>0.6989277389275761</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6962523198527796</v>
+        <v>0.6974121724505631</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6965640627146639</v>
+        <v>0.6977744329765615</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.698212017019715</v>
+        <v>0.6994714040960873</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7024243562949681</v>
+        <v>0.7038116602869391</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7046519840080978</v>
+        <v>0.7063490971870763</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7066516940751681</v>
+        <v>0.7086669462676065</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7045213300002104</v>
+        <v>0.7077282828224296</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.6966357243510051</v>
+        <v>0.7048351622462513</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650623049792815</v>
+        <v>0.650621928392912</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514205851770357</v>
+        <v>0.6514199962575036</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524863192810965</v>
+        <v>0.6524853098109462</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649734094139395</v>
+        <v>0.649733673514346</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464341648980662</v>
+        <v>0.6464337117168889</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431443807099571</v>
+        <v>0.6431438806796949</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408276800546797</v>
+        <v>0.6408271501097516</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398123083231884</v>
+        <v>0.6398117774456878</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424148827486327</v>
+        <v>0.6424123588553374</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432812089146989</v>
+        <v>0.6432796963416297</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413740544605775</v>
+        <v>0.6413725518572193</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384972983380304</v>
+        <v>0.6384957768383315</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404093111951724</v>
+        <v>0.6404048406944766</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404828335786029</v>
+        <v>0.6404785257354275</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399424233615105</v>
+        <v>0.6399402011170297</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423102414938445</v>
+        <v>0.6423084284132452</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450789227948452</v>
+        <v>0.6450754331360424</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469895914580449</v>
+        <v>0.6469850047018294</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466214532256001</v>
+        <v>0.6466175797607829</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468178624313556</v>
+        <v>0.6468156270315137</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456235735672022</v>
+        <v>0.6456198096389724</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451271577103801</v>
+        <v>0.6451206101045668</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460002941355191</v>
+        <v>0.6459890978957961</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6438258475385623</v>
+        <v>0.643811224658398</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430380419177006</v>
+        <v>0.6430194322890428</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6442237397226881</v>
+        <v>0.644202385057131</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448227132536319</v>
+        <v>0.6448001400303347</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6466715337190192</v>
+        <v>0.6466452190512406</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6533213062289012</v>
+        <v>0.6532991250185505</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6653676794771137</v>
+        <v>0.6653362930712399</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6726999442022983</v>
+        <v>0.6726647861550212</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6885521707779658</v>
+        <v>0.6885204426710803</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6975722653040052</v>
+        <v>0.6975484001977396</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6999546814450734</v>
+        <v>0.6999297491862232</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7002374602235144</v>
+        <v>0.7002121571962459</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081303864008028</v>
+        <v>0.7081232093032708</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081398885737189</v>
+        <v>0.7081344296333831</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108462403399268</v>
+        <v>0.710850258848736</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7170198677033319</v>
+        <v>0.7170428640110018</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7171843790867836</v>
+        <v>0.7172087557405943</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7241679221214423</v>
+        <v>0.7242014715838661</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197369370409229</v>
+        <v>0.7197512010010407</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7230761468159315</v>
+        <v>0.7230924122947742</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226194514229582</v>
+        <v>0.7226332745347334</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198082595747006</v>
+        <v>0.7198193765116445</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147369419147811</v>
+        <v>0.7147370526678968</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166030609125131</v>
+        <v>0.7166049507414229</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165553890171925</v>
+        <v>0.7165601454945643</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152572215658441</v>
+        <v>0.7152625198732327</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130278430597795</v>
+        <v>0.713031464833359</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105522900025081</v>
+        <v>0.7105578515342915</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105649237970089</v>
+        <v>0.7105711643292847</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083390766848403</v>
+        <v>0.7083486786678767</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056790435946383</v>
+        <v>0.7056966042699975</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7037854995172645</v>
+        <v>0.703805129893792</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029587319000646</v>
+        <v>0.7029758269092823</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025219164235283</v>
+        <v>0.7025332714875314</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031937186340711</v>
+        <v>0.7031948769333943</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7047479486374102</v>
+        <v>0.7051445400363685</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7039449633791038</v>
+        <v>0.7044584751823906</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7033075703197202</v>
+        <v>0.7038881150476963</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7029309399217827</v>
+        <v>0.7035682256885805</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7006492802845221</v>
+        <v>0.7014151211092226</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6989277389275761</v>
+        <v>0.6998249616702392</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6974121724505631</v>
+        <v>0.6984187735864498</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6977744329765615</v>
+        <v>0.6988191847417203</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.6994714040960873</v>
+        <v>0.7005494581665509</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7038116602869391</v>
+        <v>0.7049663175543652</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7063490971870763</v>
+        <v>0.7077301595371457</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7086669462676065</v>
+        <v>0.7102656725889249</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7077282828224296</v>
+        <v>0.7101262375342221</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7048351622462513</v>
+        <v>0.7097792721772731</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650621928392912</v>
+        <v>0.6506265887275247</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514199962575036</v>
+        <v>0.6514224422186886</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524853098109462</v>
+        <v>0.6524895039915533</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649733673514346</v>
+        <v>0.6497354185927324</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464337117168889</v>
+        <v>0.6464355922152545</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431438806796949</v>
+        <v>0.6431459559245156</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408271501097516</v>
+        <v>0.6408293497229316</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398117774456878</v>
+        <v>0.6398139810459065</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424123588553374</v>
+        <v>0.642422850033005</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432796963416297</v>
+        <v>0.6432859861093152</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413725518572193</v>
+        <v>0.6413787999638528</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384957768383315</v>
+        <v>0.6385021033545939</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404048406944766</v>
+        <v>0.6404234273110234</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404785257354275</v>
+        <v>0.6404964299012311</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399402011170297</v>
+        <v>0.6399494333795763</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423084284132452</v>
+        <v>0.6423159706432034</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450754331360424</v>
+        <v>0.6450899425823622</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469850047018294</v>
+        <v>0.647004061779491</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466175797607829</v>
+        <v>0.6466336682881569</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468156270315137</v>
+        <v>0.646824913664915</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456198096389724</v>
+        <v>0.645635448876961</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451206101045668</v>
+        <v>0.6451478249684921</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459890978957961</v>
+        <v>0.6460356179852272</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643811224658398</v>
+        <v>0.643871976740878</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430194322890428</v>
+        <v>0.6430967474398689</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.644202385057131</v>
+        <v>0.6442910919415029</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448001400303347</v>
+        <v>0.6448938954113852</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6466452190512406</v>
+        <v>0.6467545187660865</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6532991250185505</v>
+        <v>0.6533913044349499</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6653362930712399</v>
+        <v>0.665466692046761</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6726647861550212</v>
+        <v>0.6728108606941953</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6885204426710803</v>
+        <v>0.6886521619982734</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6975484001977396</v>
+        <v>0.6976474604606007</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6999297491862232</v>
+        <v>0.7000332039594248</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7002121571962459</v>
+        <v>0.7003170917327914</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081232093032708</v>
+        <v>0.7081528784328843</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081344296333831</v>
+        <v>0.7081569438507325</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710850258848736</v>
+        <v>0.710833401253633</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7170428640110018</v>
+        <v>0.7169473123915413</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7172087557405943</v>
+        <v>0.7171075105526671</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7242014715838661</v>
+        <v>0.7240622121390482</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197512010010407</v>
+        <v>0.7196919805437194</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7230924122947742</v>
+        <v>0.7230248978935805</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226332745347334</v>
+        <v>0.7225759434849899</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198193765116445</v>
+        <v>0.7197733038447809</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147370526678968</v>
+        <v>0.7147366072173471</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166049507414229</v>
+        <v>0.7165971467678068</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165601454945643</v>
+        <v>0.7165404197232143</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152625198732327</v>
+        <v>0.7152405193497268</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.713031464833359</v>
+        <v>0.7130163778964975</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105578515342915</v>
+        <v>0.7105346486467849</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105711643292847</v>
+        <v>0.7105451315395077</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083486786678767</v>
+        <v>0.7083086675629948</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056966042699975</v>
+        <v>0.7056236800356451</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.703805129893792</v>
+        <v>0.7043036921486727</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029758269092823</v>
+        <v>0.7028987103828236</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025332714875314</v>
+        <v>0.7024411324366427</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031948769333943</v>
+        <v>0.7026388498226328</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7051445400363685</v>
+        <v>0.7043974406280366</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7044584751823906</v>
+        <v>0.7039529857755159</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7038881150476963</v>
+        <v>0.703199051119395</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7035682256885805</v>
+        <v>0.703260529815227</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7014151211092226</v>
+        <v>0.7015651486813064</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.6998249616702392</v>
+        <v>0.7005007643091208</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6984187735864498</v>
+        <v>0.699569752670975</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6988191847417203</v>
+        <v>0.6998124768084465</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7005494581665509</v>
+        <v>0.7025342533044934</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7049663175543652</v>
+        <v>0.7086118403429162</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7077301595371457</v>
+        <v>0.7117334932874455</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7102656725889249</v>
+        <v>0.717924381793408</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7101262375342221</v>
+        <v>0.7223113457666863</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7097792721772731</v>
+        <v>0.7238609275841367</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>0.7271450963102948</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506265887275247</v>
+        <v>0.6506208343401081</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514224422186886</v>
+        <v>0.6514194214820057</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524895039915533</v>
+        <v>0.652484324812257</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497354185927324</v>
+        <v>0.6497332627115002</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464355922152545</v>
+        <v>0.6464332691698804</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431459559245156</v>
+        <v>0.6431433924334748</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408293497229316</v>
+        <v>0.6408266326855154</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398139810459065</v>
+        <v>0.639811259128015</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642422850033005</v>
+        <v>0.6424098968550098</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432859861093152</v>
+        <v>0.643278221212192</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413787999638528</v>
+        <v>0.6413710864207525</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385021033545939</v>
+        <v>0.6384942929486922</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404234273110234</v>
+        <v>0.6404004803957519</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404964299012311</v>
+        <v>0.6404743231777381</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399494333795763</v>
+        <v>0.6399380326280568</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423159706432034</v>
+        <v>0.6423066606350432</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450899425823622</v>
+        <v>0.645072029618714</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.647004061779491</v>
+        <v>0.6469805291248278</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466336682881569</v>
+        <v>0.6466137994545187</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646824913664915</v>
+        <v>0.6468134456660315</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645635448876961</v>
+        <v>0.6456161370696882</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451478249684921</v>
+        <v>0.6451142227992767</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460356179852272</v>
+        <v>0.6459781733167241</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643871976740878</v>
+        <v>0.6437969557648306</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430967474398689</v>
+        <v>0.6430012731288068</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6442910919415029</v>
+        <v>0.6441815454439557</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448938954113852</v>
+        <v>0.6447781092938842</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6467545187660865</v>
+        <v>0.6466195374825146</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6533913044349499</v>
+        <v>0.6532774845485918</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.665466692046761</v>
+        <v>0.6653056667012656</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6728108606941953</v>
+        <v>0.672630480327829</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6886521619982734</v>
+        <v>0.6884894682689121</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6976474604606007</v>
+        <v>0.6975250996960125</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7000332039594248</v>
+        <v>0.6999054016304191</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7003170917327914</v>
+        <v>0.7001874389443429</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081528784328843</v>
+        <v>0.7081161840693608</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081569438507325</v>
+        <v>0.7081290784989561</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710833401253633</v>
+        <v>0.7108541561658663</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7169473123915413</v>
+        <v>0.7170653019195289</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7171075105526671</v>
+        <v>0.7172325466167933</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7240622121390482</v>
+        <v>0.7242342272265951</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7196919805437194</v>
+        <v>0.7197651255821248</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7230248978935805</v>
+        <v>0.7231082930970003</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225759434849899</v>
+        <v>0.7226467774447933</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197733038447809</v>
+        <v>0.7198302410367592</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147366072173471</v>
+        <v>0.7147371629007784</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165971467678068</v>
+        <v>0.7166068018147238</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165404197232143</v>
+        <v>0.7165647920519314</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152405193497268</v>
+        <v>0.7152676916700934</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130163778964975</v>
+        <v>0.7130349930725629</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105346486467849</v>
+        <v>0.7105632641682864</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105451315395077</v>
+        <v>0.7105772382088694</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083086675629948</v>
+        <v>0.7083580306894708</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056236800356451</v>
+        <v>0.7057137445586275</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043036921486727</v>
+        <v>0.7038243149252077</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7028987103828236</v>
+        <v>0.7029925571864053</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024411324366427</v>
+        <v>0.7025444252747732</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7026388498226328</v>
+        <v>0.7031960913970321</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7043974406280366</v>
+        <v>0.7051328828159626</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7039529857755159</v>
+        <v>0.7048387336611934</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.703199051119395</v>
+        <v>0.7043786581310558</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.703260529815227</v>
+        <v>0.7041461068654041</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7015651486813064</v>
+        <v>0.7022500360717547</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7005007643091208</v>
+        <v>0.7008398479645894</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.699569752670975</v>
+        <v>0.6995802130043077</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.6998124768084465</v>
+        <v>0.7000595547856905</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7025342533044934</v>
+        <v>0.7018863949370195</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7086118403429162</v>
+        <v>0.7065022328562883</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7117334932874455</v>
+        <v>0.7099226710712816</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.717924381793408</v>
+        <v>0.7130527170138602</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7223113457666863</v>
+        <v>0.7143604916599213</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7238609275841367</v>
+        <v>0.7176728907749705</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7271450963102948</v>
+        <v>0.7298772657749706</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506208343401081</v>
+        <v>0.6506253788402678</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514194214820057</v>
+        <v>0.6514218075884215</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652484324812257</v>
+        <v>0.6524884153760298</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497332627115002</v>
+        <v>0.6497349662963221</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464332691698804</v>
+        <v>0.6464351047309194</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431433924334748</v>
+        <v>0.6431454178686243</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408266326855154</v>
+        <v>0.640828779367047</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.639811259128015</v>
+        <v>0.6398134096267358</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424098968550098</v>
+        <v>0.6424201257878174</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643278221212192</v>
+        <v>0.6432843522400911</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413710864207525</v>
+        <v>0.6413771769683158</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384942929486922</v>
+        <v>0.6385004600332475</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6404004803957519</v>
+        <v>0.640418599938407</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404743231777381</v>
+        <v>0.640491781342665</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399380326280568</v>
+        <v>0.6399470373122161</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423066606350432</v>
+        <v>0.6423140107045082</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645072029618714</v>
+        <v>0.6450861739457165</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469805291248278</v>
+        <v>0.6469991154806989</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466137994545187</v>
+        <v>0.6466294937375356</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468134456660315</v>
+        <v>0.6468225035597053</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456161370696882</v>
+        <v>0.6456313894689846</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451142227992767</v>
+        <v>0.6451407585567805</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459781733167241</v>
+        <v>0.6460235431281022</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437969557648306</v>
+        <v>0.6438562092221271</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430012731288068</v>
+        <v>0.6430766812289302</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6441815454439557</v>
+        <v>0.6442680723749116</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6447781092938842</v>
+        <v>0.6448695691443636</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6466195374825146</v>
+        <v>0.6467261581123822</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6532774845485918</v>
+        <v>0.6533673738511543</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6653056667012656</v>
+        <v>0.6654328481665047</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.672630480327829</v>
+        <v>0.6727729469007868</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6884894682689121</v>
+        <v>0.6886180005629715</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6975250996960125</v>
+        <v>0.6976217731678744</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6999054016304191</v>
+        <v>0.7000063860189925</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7001874389443429</v>
+        <v>0.7002899050919711</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081161840693608</v>
+        <v>0.708145215804131</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081290784989561</v>
+        <v>0.7081511424098914</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108541561658663</v>
+        <v>0.7108378175169106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7170653019195289</v>
+        <v>0.7169721145901264</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7172325466167933</v>
+        <v>0.7171337800066269</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7242342272265951</v>
+        <v>0.7240983237426052</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197651255821248</v>
+        <v>0.7197073402833705</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231082930970003</v>
+        <v>0.7230424047688674</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226467774447933</v>
+        <v>0.7225907982005597</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198302410367592</v>
+        <v>0.7197852327095119</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147371629007784</v>
+        <v>0.7147367191133103</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166068018147238</v>
+        <v>0.7165991601856548</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165647920519314</v>
+        <v>0.71654553036028</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152676916700934</v>
+        <v>0.7152462263694939</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130349930725629</v>
+        <v>0.7130203036643362</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105632641682864</v>
+        <v>0.7105406952474377</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105772382088694</v>
+        <v>0.7105519148677892</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083580306894708</v>
+        <v>0.7083190820307872</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7057137445586275</v>
+        <v>0.7056425981858635</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038243149252077</v>
+        <v>0.7043247809991284</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029925571864053</v>
+        <v>0.7029178131411862</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025444252747732</v>
+        <v>0.7024545479850576</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031960913970321</v>
+        <v>0.7026439364380423</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7051328828159626</v>
+        <v>0.7043897669579773</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7048387336611934</v>
+        <v>0.7045095224365455</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7043786581310558</v>
+        <v>0.7038646452037314</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7041461068654041</v>
+        <v>0.7039751237261279</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7022500360717547</v>
+        <v>0.7025070724149892</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7008398479645894</v>
+        <v>0.7016202113182598</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.6995802130043077</v>
+        <v>0.7006711818145762</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7000595547856905</v>
+        <v>0.7009568228690137</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7018863949370195</v>
+        <v>0.7036697399010856</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7065022328562883</v>
+        <v>0.7097450259037713</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7099226710712816</v>
+        <v>0.713041762809282</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7130527170138602</v>
+        <v>0.7192680139319575</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7143604916599213</v>
+        <v>0.7238022343714321</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7176728907749705</v>
+        <v>0.7258558009798601</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7298772657749706</v>
+        <v>0.7322593441758504</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506253788402678</v>
+        <v>0.6506197666461484</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514218075884215</v>
+        <v>0.65141886034721</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524884153760298</v>
+        <v>0.6524833634059429</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497349662963221</v>
+        <v>0.6497328613914868</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464351047309194</v>
+        <v>0.6464328368876913</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431454178686243</v>
+        <v>0.643142915560138</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640828779367047</v>
+        <v>0.6408261273439445</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398134096267358</v>
+        <v>0.6398107529301531</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424201257878174</v>
+        <v>0.6424074944991084</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432843522400911</v>
+        <v>0.6432767821535973</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413771769683158</v>
+        <v>0.6413696567895913</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6385004600332475</v>
+        <v>0.6384928452921457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640418599938407</v>
+        <v>0.6403962262755699</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640491781342665</v>
+        <v>0.6404702220946972</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399470373122161</v>
+        <v>0.6399359159681138</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423140107045082</v>
+        <v>0.6423049364836483</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450861739457165</v>
+        <v>0.6450687090946678</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469991154806989</v>
+        <v>0.646976160737377</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466294937375356</v>
+        <v>0.6466101089892407</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468225035597053</v>
+        <v>0.6468113164010426</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456313894689846</v>
+        <v>0.6456125525761756</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451407585567805</v>
+        <v>0.6451079899843675</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6460235431281022</v>
+        <v>0.645967510636819</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6438562092221271</v>
+        <v>0.6437830281718335</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6430766812289302</v>
+        <v>0.6429835482981213</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6442680723749116</v>
+        <v>0.644161202502328</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6448695691443636</v>
+        <v>0.6447566017599949</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6467261581123822</v>
+        <v>0.6465944664886957</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6533673738511543</v>
+        <v>0.653256365318444</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6654328481665047</v>
+        <v>0.6652757731482755</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6727729469007868</v>
+        <v>0.6725969961711857</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6886180005629715</v>
+        <v>0.6884592210983014</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6976217731678744</v>
+        <v>0.6975023440566899</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.7000063860189925</v>
+        <v>0.6998816185258013</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7002899050919711</v>
+        <v>0.7001632855378186</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708145215804131</v>
+        <v>0.7081093060373508</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081511424098914</v>
+        <v>0.7081238321683825</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108378175169106</v>
+        <v>0.7108579374656742</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7169721145901264</v>
+        <v>0.7170872014806472</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7171337800066269</v>
+        <v>0.7172557725205222</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7240983237426052</v>
+        <v>0.724266216831978</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197073402833705</v>
+        <v>0.7197787227187825</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7230424047688674</v>
+        <v>0.7231238026603947</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7225907982005597</v>
+        <v>0.7226599710950101</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7197852327095119</v>
+        <v>0.7198408615945162</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147367191133103</v>
+        <v>0.7147372725558222</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7165991601856548</v>
+        <v>0.7166086152766573</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.71654553036028</v>
+        <v>0.7165693324481718</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152462263694939</v>
+        <v>0.7152727414375168</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130203036643362</v>
+        <v>0.7130384313468575</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105406952474377</v>
+        <v>0.7105685337487844</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105519148677892</v>
+        <v>0.7105831519610666</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083190820307872</v>
+        <v>0.7083671423056054</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7056425981858635</v>
+        <v>0.7057304792692288</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043247809991284</v>
+        <v>0.7038430693987598</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7029178131411862</v>
+        <v>0.703008933972231</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7024545479850576</v>
+        <v>0.7025553824245647</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7026439364380423</v>
+        <v>0.7031973573146459</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7043897669579773</v>
+        <v>0.7051215840361338</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7045095224365455</v>
+        <v>0.7053104698670027</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7038646452037314</v>
+        <v>0.7049715190509012</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7039751237261279</v>
+        <v>0.7048420764565138</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7025070724149892</v>
+        <v>0.703209170886602</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7016202113182598</v>
+        <v>0.7019814194193397</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7006711818145762</v>
+        <v>0.7008907525033767</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7009568228690137</v>
+        <v>0.7014735837133665</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7036697399010856</v>
+        <v>0.7034210077184895</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7097450259037713</v>
+        <v>0.708268224188892</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.713041762809282</v>
+        <v>0.712383435559759</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7192680139319575</v>
+        <v>0.7161202967190253</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7238022343714321</v>
+        <v>0.7188030447721906</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7258558009798601</v>
+        <v>0.725042510837937</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7322593441758504</v>
+        <v>0.7372468858379371</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506197666461484</v>
+        <v>0.6506187243698274</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.65141886034721</v>
+        <v>0.6514183123733785</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524833634059429</v>
+        <v>0.6524824247545201</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497328613914868</v>
+        <v>0.6497324692303574</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464328368876913</v>
+        <v>0.6464324145178506</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643142915560138</v>
+        <v>0.6431424496674063</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408261273439445</v>
+        <v>0.6408256336671846</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398107529301531</v>
+        <v>0.6398102584323782</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424074944991084</v>
+        <v>0.6424051496466797</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432767821535973</v>
+        <v>0.6432753778593265</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413696567895913</v>
+        <v>0.6413682616678301</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384928452921457</v>
+        <v>0.6384914325581069</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403962262755699</v>
+        <v>0.6403920745039205</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404702220946972</v>
+        <v>0.640466218857076</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399359159681138</v>
+        <v>0.6399338493016572</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423049364836483</v>
+        <v>0.6423032543650337</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450687090946678</v>
+        <v>0.6450654685671573</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.646976160737377</v>
+        <v>0.6469718957382495</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466101089892407</v>
+        <v>0.646606505202908</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468113164010426</v>
+        <v>0.6468092373937853</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456125525761756</v>
+        <v>0.6456090530305673</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6451079899843675</v>
+        <v>0.645101906126881</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.645967510636819</v>
+        <v>0.6459571005564004</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437830281718335</v>
+        <v>0.6437694297917496</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6429835482981213</v>
+        <v>0.642966242418942</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.644161202502328</v>
+        <v>0.6441413387143036</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6447566017599949</v>
+        <v>0.6447355990458594</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6465944664886957</v>
+        <v>0.6465699845991737</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.653256365318444</v>
+        <v>0.6532357487524363</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6652757731482755</v>
+        <v>0.6652465864750425</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6725969961711857</v>
+        <v>0.6725643045754</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6884592210983014</v>
+        <v>0.6884296759083245</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6975023440566899</v>
+        <v>0.6974801144446077</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6998816185258013</v>
+        <v>0.6998583805413728</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7001632855378186</v>
+        <v>0.7001396779368358</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081093060373508</v>
+        <v>0.7081025707287179</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081238321683825</v>
+        <v>0.7081186877410806</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108579374656742</v>
+        <v>0.7108616076404274</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7170872014806472</v>
+        <v>0.7171085817993721</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7172557725205222</v>
+        <v>0.7172784532859416</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724266216831978</v>
+        <v>0.7242974669038005</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197787227187825</v>
+        <v>0.7197920037941786</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231238026603947</v>
+        <v>0.7231389538063895</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226599710950101</v>
+        <v>0.7226728659370707</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198408615945162</v>
+        <v>0.7198512462595565</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147372725558222</v>
+        <v>0.7147373815816723</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166086152766573</v>
+        <v>0.7166103922287554</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165693324481718</v>
+        <v>0.7165737702730477</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152727414375168</v>
+        <v>0.7152776734472599</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130384313468575</v>
+        <v>0.7130417830467626</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105685337487844</v>
+        <v>0.7105736658206109</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105831519610666</v>
+        <v>0.7105889117775845</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083671423056054</v>
+        <v>0.7083760225947254</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7057304792692288</v>
+        <v>0.7057468225281038</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038430693987598</v>
+        <v>0.7038614074637649</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.703008933972231</v>
+        <v>0.7030249680660154</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025553824245647</v>
+        <v>0.7025661474741938</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7031973573146459</v>
+        <v>0.703198670308673</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7051215840361338</v>
+        <v>0.7051106288020238</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7053104698670027</v>
+        <v>0.7057694724452831</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7049715190509012</v>
+        <v>0.7055331712609925</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7048420764565138</v>
+        <v>0.7054870157214969</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.703209170886602</v>
+        <v>0.7040682537548133</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7019814194193397</v>
+        <v>0.702964563585061</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7008907525033767</v>
+        <v>0.7020039050406142</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7014735837133665</v>
+        <v>0.7026580802877164</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7034210077184895</v>
+        <v>0.7046854338696498</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.708268224188892</v>
+        <v>0.7096745961569033</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.712383435559759</v>
+        <v>0.7142268470155524</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7161202967190253</v>
+        <v>0.7183068446691507</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7188030447721906</v>
+        <v>0.7217214647458127</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.725042510837937</v>
+        <v>0.7290722006316492</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7372468858379371</v>
+        <v>0.7618237653311197</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506187243698274</v>
+        <v>0.65061770661422</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514183123733785</v>
+        <v>0.6514177771030022</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524824247545201</v>
+        <v>0.6524815080596758</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497324692303574</v>
+        <v>0.649732085918722</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464324145178506</v>
+        <v>0.6464320017238154</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431424496674063</v>
+        <v>0.6431419943808129</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408256336671846</v>
+        <v>0.6408251512564056</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398102584323782</v>
+        <v>0.6398097752341043</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424051496466797</v>
+        <v>0.6424028602580018</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432753778593265</v>
+        <v>0.6432740070851812</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413682616678301</v>
+        <v>0.6413668998213314</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384914325581069</v>
+        <v>0.6384900534984228</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403920745039205</v>
+        <v>0.6403880214327332</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640466218857076</v>
+        <v>0.6404623100065697</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399338493016572</v>
+        <v>0.6399318308787771</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423032543650337</v>
+        <v>0.6423016127618353</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450654685671573</v>
+        <v>0.6450623051818924</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469718957382495</v>
+        <v>0.6469677305036698</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.646606505202908</v>
+        <v>0.6466029850800062</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468092373937853</v>
+        <v>0.6468072068873052</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456090530305673</v>
+        <v>0.6456056354512376</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645101906126881</v>
+        <v>0.6450959659547234</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459571005564004</v>
+        <v>0.6459469342106225</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437694297917496</v>
+        <v>0.6437561491004596</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.642966242418942</v>
+        <v>0.6429493408297998</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6441413387143036</v>
+        <v>0.6441219373748629</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6447355990458594</v>
+        <v>0.6447150836181861</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6465699845991737</v>
+        <v>0.6465460713361286</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6532357487524363</v>
+        <v>0.6532156171457069</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6652465864750425</v>
+        <v>0.6652180819516197</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6725643045754</v>
+        <v>0.6725323777869602</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6884296759083245</v>
+        <v>0.6884008086007493</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6974801144446077</v>
+        <v>0.6974583928802447</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6998583805413728</v>
+        <v>0.6998356692154661</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7001396779368358</v>
+        <v>0.7001165979428792</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7081025707287179</v>
+        <v>0.7080959738396022</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081186877410806</v>
+        <v>0.7081136424143435</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108616076404274</v>
+        <v>0.7108651713188721</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7171085817993721</v>
+        <v>0.7171294610891081</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7172784532859416</v>
+        <v>0.7173006078320632</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7242974669038005</v>
+        <v>0.724328002739829</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7197920037941786</v>
+        <v>0.7198049796714233</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231389538063895</v>
+        <v>0.7231537587748647</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226728659370707</v>
+        <v>0.7226854719594593</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198512462595565</v>
+        <v>0.7198614027565547</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147373815816723</v>
+        <v>0.7147374899326564</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166103922287554</v>
+        <v>0.7166121337316878</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165737702730477</v>
+        <v>0.7165781089565921</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152776734472599</v>
+        <v>0.7152824917738382</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130417830467626</v>
+        <v>0.7130450513949016</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105736658206109</v>
+        <v>0.7105786656479323</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105889117775845</v>
+        <v>0.7105945235374431</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083760225947254</v>
+        <v>0.7083846801870152</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7057468225281038</v>
+        <v>0.7057627878177184</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038614074637649</v>
+        <v>0.7038793426650658</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7030249680660154</v>
+        <v>0.7030406698459317</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025661474741938</v>
+        <v>0.7025767248584147</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.703198670308673</v>
+        <v>0.7032000263095517</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7051106288020238</v>
+        <v>0.7051000029865317</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7057694724452831</v>
+        <v>0.7062170602368206</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7055331712609925</v>
+        <v>0.7060920976432605</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7054870157214969</v>
+        <v>0.7061332479305433</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7040682537548133</v>
+        <v>0.7049403201028916</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.702964563585061</v>
+        <v>0.7039855753624197</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7020039050406142</v>
+        <v>0.7031683961648099</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7026580802877164</v>
+        <v>0.7039094616625194</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7046854338696498</v>
+        <v>0.7060352789629715</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7096745961569033</v>
+        <v>0.71119622288611</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7142268470155524</v>
+        <v>0.716264961708296</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7183068446691507</v>
+        <v>0.7207560219904657</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7217214647458127</v>
+        <v>0.7249843680040617</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7290722006316492</v>
+        <v>0.7335307339367481</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7618237653311197</v>
+        <v>0.7646827470237985</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.65061770661422</v>
+        <v>0.6506167125241098</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514177771030022</v>
+        <v>0.651417254099528</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524815080596758</v>
+        <v>0.6524806125600037</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649732085918722</v>
+        <v>0.6497317111609412</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464320017238154</v>
+        <v>0.6464315981840825</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431419943808129</v>
+        <v>0.6431415493427042</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408251512564056</v>
+        <v>0.6408246797307339</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398097752341043</v>
+        <v>0.6398093029528058</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424028602580018</v>
+        <v>0.6424006243886717</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432740070851812</v>
+        <v>0.6432726686456128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413668998213314</v>
+        <v>0.6413655700740903</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384900534984228</v>
+        <v>0.638488706923698</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403880214327332</v>
+        <v>0.6403840635852037</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404623100065697</v>
+        <v>0.6404584922458578</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399318308787771</v>
+        <v>0.6399298590302632</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423016127618353</v>
+        <v>0.6423000102288032</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450623051818924</v>
+        <v>0.6450592162186761</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469677305036698</v>
+        <v>0.6469636615770896</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6466029850800062</v>
+        <v>0.6465995457431649</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468072068873052</v>
+        <v>0.6468052232055232</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456056354512376</v>
+        <v>0.6456022969943607</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450959659547234</v>
+        <v>0.6450901644414831</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459469342106225</v>
+        <v>0.6459370031443693</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437561491004596</v>
+        <v>0.6437431751049547</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6429493408297998</v>
+        <v>0.6429328295445951</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6441219373748629</v>
+        <v>0.644102982545373</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6447150836181861</v>
+        <v>0.6446950387447836</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6465460713361286</v>
+        <v>0.6465227071579305</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6532156171457069</v>
+        <v>0.6531959536138512</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6652180819516197</v>
+        <v>0.6651902359860467</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6725323777869602</v>
+        <v>0.6725011893306281</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6884008086007493</v>
+        <v>0.6883725961651725</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6974583928802447</v>
+        <v>0.6974371621918334</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6998356692154661</v>
+        <v>0.6998134669076198</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7001165979428792</v>
+        <v>0.7000940281530821</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080959738396022</v>
+        <v>0.7080895112327152</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081136424143435</v>
+        <v>0.70810869347983</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108651713188721</v>
+        <v>0.7108686328833766</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7171294610891081</v>
+        <v>0.7171498567229587</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7173006078320632</v>
+        <v>0.7173222542147857</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724328002739829</v>
+        <v>0.7243578484994809</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198049796714233</v>
+        <v>0.7198176607228473</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231537587748647</v>
+        <v>0.7231682292566246</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226854719594593</v>
+        <v>0.7226977987126866</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198614027565547</v>
+        <v>0.719871338478828</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147374899326564</v>
+        <v>0.7147375975682733</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166121337316878</v>
+        <v>0.7166138408070226</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165781089565921</v>
+        <v>0.716582351777879</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152824917738382</v>
+        <v>0.7152872003057903</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130450513949016</v>
+        <v>0.7130482394562451</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105786656479323</v>
+        <v>0.7105835382316712</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7105945235374431</v>
+        <v>0.710599992826333</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7083846801870152</v>
+        <v>0.708393123291558</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7057627878177184</v>
+        <v>0.705778388012703</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038793426650658</v>
+        <v>0.7038968879744444</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7030406698459317</v>
+        <v>0.7030560492884869</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025767248584147</v>
+        <v>0.7025871189093913</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032000263095517</v>
+        <v>0.7032014215329545</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7051000029865317</v>
+        <v>0.7050896931835777</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7062170602368206</v>
+        <v>0.7066405866311077</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7060920976432605</v>
+        <v>0.7066031070637886</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7061332479305433</v>
+        <v>0.7067045290071228</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7049403201028916</v>
+        <v>0.7056785202271514</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7039855753624197</v>
+        <v>0.7048016100051903</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7031683961648099</v>
+        <v>0.7040772753138674</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7039094616625194</v>
+        <v>0.7048590485911895</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7060352789629715</v>
+        <v>0.7070199724506445</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.71119622288611</v>
+        <v>0.7122189871008566</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.716264961708296</v>
+        <v>0.7174386154194239</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7207560219904657</v>
+        <v>0.7219777868341042</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7249843680040617</v>
+        <v>0.7263015625813106</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7335307339367481</v>
+        <v>0.7345510609356788</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7646827470237985</v>
+        <v>0.7603582519699968</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506167125241098</v>
+        <v>0.6506157412835911</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651417254099528</v>
+        <v>0.6514167429461726</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524806125600037</v>
+        <v>0.6524797375288968</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497317111609412</v>
+        <v>0.6497313446743735</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464315981840825</v>
+        <v>0.6464312035913585</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431415493427042</v>
+        <v>0.6431411142113082</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408246797307339</v>
+        <v>0.6408242187262534</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398093029528058</v>
+        <v>0.6398088412230128</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6424006243886717</v>
+        <v>0.6423984401841035</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432726686456128</v>
+        <v>0.6432713614103078</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413655700740903</v>
+        <v>0.6413642713048535</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.638488706923698</v>
+        <v>0.6384873916998801</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403840635852037</v>
+        <v>0.640380197645865</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404584922458578</v>
+        <v>0.6404547624293508</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399298590302632</v>
+        <v>0.6399279321630069</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6423000102288032</v>
+        <v>0.6422984453885686</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450592162186761</v>
+        <v>0.6450561990836305</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469636615770896</v>
+        <v>0.6469596856596609</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465995457431649</v>
+        <v>0.6465961844453446</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468052232055232</v>
+        <v>0.6468032847486394</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6456022969943607</v>
+        <v>0.6455990349460479</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450901644414831</v>
+        <v>0.6450844967922962</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459370031443693</v>
+        <v>0.6459272992888689</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437431751049547</v>
+        <v>0.6437304973131206</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6429328295445951</v>
+        <v>0.642916695214202</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.644102982545373</v>
+        <v>0.6440844590102053</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6446950387447836</v>
+        <v>0.6446754484494135</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6465227071579305</v>
+        <v>0.6464998734063595</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6531959536138512</v>
+        <v>0.6531767420460157</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6651902359860467</v>
+        <v>0.6651630260597639</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6725011893306281</v>
+        <v>0.6724707139368264</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6883725961651725</v>
+        <v>0.6883450166184777</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6974371621918334</v>
+        <v>0.6974164059706387</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6998134669076198</v>
+        <v>0.6997917567536013</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7000940281530821</v>
+        <v>0.7000719519174784</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080895112327152</v>
+        <v>0.7080831789296633</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.70810869347983</v>
+        <v>0.7081038383201508</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108686328833766</v>
+        <v>0.7108719964857739</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7171498567229587</v>
+        <v>0.717169785281541</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7173222542147857</v>
+        <v>0.7173434096754294</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7243578484994809</v>
+        <v>0.724387027267001</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198176607228473</v>
+        <v>0.7198300568573281</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231682292566246</v>
+        <v>0.7231823764237341</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7226977987126866</v>
+        <v>0.722709855332899</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.719871338478828</v>
+        <v>0.7198810605057822</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147375975682733</v>
+        <v>0.714737704452727</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166138408070226</v>
+        <v>0.7166155144389091</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716582351777879</v>
+        <v>0.7165865018732231</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152872003057903</v>
+        <v>0.7152918027561769</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130482394562451</v>
+        <v>0.7130513501476141</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105835382316712</v>
+        <v>0.7105882883256489</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710599992826333</v>
+        <v>0.7106053249545671</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.708393123291558</v>
+        <v>0.7084013597215566</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.705778388012703</v>
+        <v>0.7057936354134786</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7038968879744444</v>
+        <v>0.7039140558201353</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7030560492884869</v>
+        <v>0.7030711159869393</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025871189093913</v>
+        <v>0.7025973338570212</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032014215329545</v>
+        <v>0.7032028524588507</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050896931835777</v>
+        <v>0.7050796866646157</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7066405866311077</v>
+        <v>0.7069165220675281</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7066031070637886</v>
+        <v>0.7069346811362869</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7067045290071228</v>
+        <v>0.707067049303067</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7056785202271514</v>
+        <v>0.7061616523926417</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7048016100051903</v>
+        <v>0.7053514360529931</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7040772753138674</v>
+        <v>0.7046825429924151</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7048590485911895</v>
+        <v>0.7054660592339568</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7070199724506445</v>
+        <v>0.7076171686225143</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7122189871008566</v>
+        <v>0.7127784943799621</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7174386154194239</v>
+        <v>0.7180073118572852</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7219777868341042</v>
+        <v>0.7224853826222781</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7263015625813106</v>
+        <v>0.7266693432213565</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7345510609356788</v>
+        <v>0.7342195621506998</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7603582519699968</v>
+        <v>0.7551771162218619</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506157412835911</v>
+        <v>0.6506147921138375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514167429461726</v>
+        <v>0.6514162432448172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524797375288968</v>
+        <v>0.6524788822725821</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497313446743735</v>
+        <v>0.6497309861886695</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464312035913585</v>
+        <v>0.6464308176517851</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431411142113082</v>
+        <v>0.6431406886598634</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408242187262534</v>
+        <v>0.6408237678950736</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398088412230128</v>
+        <v>0.6398083896953718</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423984401841035</v>
+        <v>0.6423963058744021</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432713614103078</v>
+        <v>0.6432700843010097</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413642713048535</v>
+        <v>0.6413630024439694</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384873916998801</v>
+        <v>0.638486106745078</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640380197645865</v>
+        <v>0.6403764204513389</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404547624293508</v>
+        <v>0.6404511175545655</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399279321630069</v>
+        <v>0.639926048755715</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422984453885686</v>
+        <v>0.6422969169277093</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450561990836305</v>
+        <v>0.6450532513019516</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469596856596609</v>
+        <v>0.6469557996013523</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465961844453446</v>
+        <v>0.6465928985625466</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468032847486394</v>
+        <v>0.6468013899888463</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455990349460479</v>
+        <v>0.645595846715017</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450844967922962</v>
+        <v>0.6450789584306762</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459272992888689</v>
+        <v>0.645917814939891</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437304973131206</v>
+        <v>0.6437181057055565</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.642916695214202</v>
+        <v>0.6429009250906581</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6440844590102053</v>
+        <v>0.6440663522362619</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6446754484494135</v>
+        <v>0.6446562974696544</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6464998734063595</v>
+        <v>0.6464775522573494</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6531767420460157</v>
+        <v>0.6531579670611691</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6651630260597639</v>
+        <v>0.665136430667369</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6724707139368264</v>
+        <v>0.6724409274739157</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6883450166184777</v>
+        <v>0.688318048948279</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6974164059706387</v>
+        <v>0.6973961085291673</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6997917567536013</v>
+        <v>0.6997705226233404</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7000719519174784</v>
+        <v>0.7000503532989617</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080831789296633</v>
+        <v>0.7080769731036706</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7081038383201508</v>
+        <v>0.7080990744055575</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108719964857739</v>
+        <v>0.7108752660620172</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.717169785281541</v>
+        <v>0.7171892625975769</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7173434096754294</v>
+        <v>0.7173640906860408</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724387027267001</v>
+        <v>0.7244155611104848</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198300568573281</v>
+        <v>0.7198421775458153</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231823764237341</v>
+        <v>0.7231962109578689</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722709855332899</v>
+        <v>0.7227216505639878</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198810605057822</v>
+        <v>0.7198905756192749</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714737704452727</v>
+        <v>0.7147378105545055</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166155144389091</v>
+        <v>0.7166171555756815</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165865018732231</v>
+        <v>0.7165905622438511</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152918027561769</v>
+        <v>0.7152963026723782</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130513501476141</v>
+        <v>0.7130543862465069</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105882883256489</v>
+        <v>0.7105929204515614</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106053249545671</v>
+        <v>0.7106105249737341</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084013597215566</v>
+        <v>0.7084093969177725</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7057936354134786</v>
+        <v>0.7058085417776947</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7039140558201353</v>
+        <v>0.7039308581145663</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7030711159869393</v>
+        <v>0.7030858791687788</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7025973338570212</v>
+        <v>0.7026073738295893</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032028524588507</v>
+        <v>0.7032043158122382</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050796866646157</v>
+        <v>0.7050699713381491</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7069165220675281</v>
+        <v>0.7068902277348647</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7069346811362869</v>
+        <v>0.7071485180671533</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.707067049303067</v>
+        <v>0.7072924538165479</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7061616523926417</v>
+        <v>0.7064332222728124</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7053514360529931</v>
+        <v>0.7057552725230385</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7046825429924151</v>
+        <v>0.7051055561256223</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7054660592339568</v>
+        <v>0.7058515418814558</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7076171686225143</v>
+        <v>0.7079510133332559</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7127784943799621</v>
+        <v>0.713011166424534</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7180073118572852</v>
+        <v>0.7181108878906999</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7224853826222781</v>
+        <v>0.7224618628772086</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7266693432213565</v>
+        <v>0.7263372474526626</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7342195621506998</v>
+        <v>0.7329624499063152</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7551771162218619</v>
+        <v>0.7496505470642912</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>0.7388374220642914</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506147921138375</v>
+        <v>0.6506138642710176</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514162432448172</v>
+        <v>0.6514157546149737</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524788822725821</v>
+        <v>0.652478046128286</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497309861886695</v>
+        <v>0.6497306354451127</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464308176517851</v>
+        <v>0.6464304400842138</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431406886598634</v>
+        <v>0.6431402723758053</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408237678950736</v>
+        <v>0.6408233269044581</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398083896953718</v>
+        <v>0.6398079480357671</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423963058744021</v>
+        <v>0.6423942197695846</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432700843010097</v>
+        <v>0.643268836288557</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413630024439694</v>
+        <v>0.6413617624704557</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.638486106745078</v>
+        <v>0.638484851026598</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403764204513389</v>
+        <v>0.6403727289817183</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404511175545655</v>
+        <v>0.6404475547540833</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639926048755715</v>
+        <v>0.6399242073549087</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422969169277093</v>
+        <v>0.6422954235930822</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450532513019516</v>
+        <v>0.6450503705111583</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469557996013523</v>
+        <v>0.6469520003926595</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465928985625466</v>
+        <v>0.6465896855870066</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6468013899888463</v>
+        <v>0.6467995374663273</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.645595846715017</v>
+        <v>0.6455927298257509</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450789584306762</v>
+        <v>0.645073544986231</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.645917814939891</v>
+        <v>0.6459085427374023</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437181057055565</v>
+        <v>0.6437059907092779</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6429009250906581</v>
+        <v>0.6428855069937397</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6440663522362619</v>
+        <v>0.6440486483351868</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6446562974696544</v>
+        <v>0.6446375712175492</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6464775522573494</v>
+        <v>0.646455726674982</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6531579670611691</v>
+        <v>0.6531396139673036</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.665136430667369</v>
+        <v>0.6651104292603761</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6724409274739157</v>
+        <v>0.6724118068849714</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.688318048948279</v>
+        <v>0.6882916730600533</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6973961085291673</v>
+        <v>0.697376254862085</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6997705226233404</v>
+        <v>0.6997497490815598</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7000503532989617</v>
+        <v>0.7000292170357558</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080769731036706</v>
+        <v>0.7080708900726747</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080990744055575</v>
+        <v>0.70809439929073</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108752660620172</v>
+        <v>0.710878445345749</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7171892625975769</v>
+        <v>0.717208303797515</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7173640906860408</v>
+        <v>0.7173843129917147</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7244155611104848</v>
+        <v>0.724443471137066</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198421775458153</v>
+        <v>0.7198540318451927</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7231962109578689</v>
+        <v>0.7232097430768372</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227216505639878</v>
+        <v>0.7227331927783043</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198905756192749</v>
+        <v>0.7198998903189744</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147378105545055</v>
+        <v>0.7147379158459948</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166171555756815</v>
+        <v>0.7166187651313869</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165905622438511</v>
+        <v>0.7165945357630842</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7152963026723782</v>
+        <v>0.7153007034452387</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130543862465069</v>
+        <v>0.7130573503993026</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105929204515614</v>
+        <v>0.7105974389128851</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106105249737341</v>
+        <v>0.7106155976921655</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084093969177725</v>
+        <v>0.7084172419703271</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058085417776947</v>
+        <v>0.7058231183496378</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7039308581145663</v>
+        <v>0.703947306280449</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7030858791687788</v>
+        <v>0.7031003477123134</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026073738295893</v>
+        <v>0.7026172428546971</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032043158122382</v>
+        <v>0.7032058085454018</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050699713381491</v>
+        <v>0.7050605357120132</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7068902277348647</v>
+        <v>0.7068645422087618</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7071485180671533</v>
+        <v>0.7073631787639127</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7072924538165479</v>
+        <v>0.7075187243617213</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7064332222728124</v>
+        <v>0.7067000297360425</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7057552725230385</v>
+        <v>0.7060996210646151</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7051055561256223</v>
+        <v>0.7054868393978833</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7058515418814558</v>
+        <v>0.7062089105792064</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7079510133332559</v>
+        <v>0.7082682605237127</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.713011166424534</v>
+        <v>0.7132402184356244</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7181108878906999</v>
+        <v>0.7182274402806119</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7224618628772086</v>
+        <v>0.7224688937576987</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7263372474526626</v>
+        <v>0.7260781792686055</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7329624499063152</v>
+        <v>0.7319398179808525</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7496505470642912</v>
+        <v>0.7455953927933465</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7388374220642914</v>
+        <v>0.7347822677933467</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506138642710176</v>
+        <v>0.6506129570443528</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514157546149737</v>
+        <v>0.6514152766928201</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652478046128286</v>
+        <v>0.6524772284625224</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497306354451127</v>
+        <v>0.6497302921960014</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464304400842138</v>
+        <v>0.6464300706195278</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431402723758053</v>
+        <v>0.6431398650600039</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408233269044581</v>
+        <v>0.6408228954360091</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398079480357671</v>
+        <v>0.6398075159245018</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423942197695846</v>
+        <v>0.6423921802551216</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643268836288557</v>
+        <v>0.643267616390121</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413617624704557</v>
+        <v>0.6413605504092623</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.638484851026598</v>
+        <v>0.6384836235581802</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403727289817183</v>
+        <v>0.640369120352527</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404475547540833</v>
+        <v>0.6404440712880437</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399242073549087</v>
+        <v>0.639922406571189</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422954235930822</v>
+        <v>0.6422939641884077</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450503705111583</v>
+        <v>0.6450475544547964</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469520003926595</v>
+        <v>0.6469482851568616</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465896855870066</v>
+        <v>0.6465865431208345</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467995374663273</v>
+        <v>0.6467977257855202</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455927298257509</v>
+        <v>0.6455896819121101</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645073544986231</v>
+        <v>0.6450682522832002</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6459085427374023</v>
+        <v>0.6458994756465699</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6437059907092779</v>
+        <v>0.6436941431731495</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6428855069937397</v>
+        <v>0.6428704292797418</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6440486483351868</v>
+        <v>0.6440313340280563</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6446375712175492</v>
+        <v>0.6446192557428219</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.646455726674982</v>
+        <v>0.6464343803684885</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6531396139673036</v>
+        <v>0.6531216687233353</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6651104292603761</v>
+        <v>0.6650850021946744</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6724118068849714</v>
+        <v>0.6723833301287269</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6882916730600533</v>
+        <v>0.6882658697276816</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.697376254862085</v>
+        <v>0.6973568306096405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6997497490815598</v>
+        <v>0.6997294213509013</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7000292170357558</v>
+        <v>0.7000085285062192</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080708900726747</v>
+        <v>0.7080649262927795</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.70809439929073</v>
+        <v>0.7080898106116708</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710878445345749</v>
+        <v>0.7108815378808726</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.717208303797515</v>
+        <v>0.7172269233404058</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7173843129917147</v>
+        <v>0.7174040916501594</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724443471137066</v>
+        <v>0.7244707775445511</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198540318451927</v>
+        <v>0.7198656284206004</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232097430768372</v>
+        <v>0.7232229825594041</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227331927783043</v>
+        <v>0.7227444899960839</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7198998903189744</v>
+        <v>0.7199090108367854</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147379158459948</v>
+        <v>0.7147380203031322</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166187651313869</v>
+        <v>0.7166203439872451</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165945357630842</v>
+        <v>0.7165984251830702</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153007034452387</v>
+        <v>0.7153050083176147</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130573503993026</v>
+        <v>0.7130602451288934</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7105974389128851</v>
+        <v>0.7106018478078007</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106155976921655</v>
+        <v>0.7106205476893128</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084172419703271</v>
+        <v>0.7084249016389979</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058231183496378</v>
+        <v>0.7058373758877621</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.703947306280449</v>
+        <v>0.703963411275327</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031003477123134</v>
+        <v>0.7031145301624127</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026172428546971</v>
+        <v>0.7026269448604222</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032058085454018</v>
+        <v>0.7032073278215626</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050605357120132</v>
+        <v>0.7050513688582152</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7068645422087618</v>
+        <v>0.7068394452634409</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7073631787639127</v>
+        <v>0.7077126080269094</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7075187243617213</v>
+        <v>0.7078958546495697</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7067000297360425</v>
+        <v>0.7071480507432235</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7060996210646151</v>
+        <v>0.706643824220882</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7054868393978833</v>
+        <v>0.7060876402328573</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7062089105792064</v>
+        <v>0.7068129260109309</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7082682605237127</v>
+        <v>0.7088635044251645</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7132402184356244</v>
+        <v>0.7138014132542596</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7182274402806119</v>
+        <v>0.7187497728602925</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7224688937576987</v>
+        <v>0.7229818079520869</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7260781792686055</v>
+        <v>0.7265027212584021</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7319398179808525</v>
+        <v>0.7319852560997244</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7455953927933465</v>
+        <v>0.7439904633618464</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7347822677933467</v>
+        <v>0.723543692180921</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506129570443528</v>
+        <v>0.6506120697543011</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514152766928201</v>
+        <v>0.651414809130298</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524772284625224</v>
+        <v>0.652476428669494</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497302921960014</v>
+        <v>0.6497299562040697</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464300706195278</v>
+        <v>0.6464297090000048</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431398650600039</v>
+        <v>0.6431394664260508</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408228954360091</v>
+        <v>0.6408224731849043</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398075159245018</v>
+        <v>0.6398070930555267</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423921802551216</v>
+        <v>0.642390185787774</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643267616390121</v>
+        <v>0.6432664236666298</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413605504092623</v>
+        <v>0.6413593653287186</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384836235581802</v>
+        <v>0.6384824233974183</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640369120352527</v>
+        <v>0.640365591807215</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404440712880437</v>
+        <v>0.6404406645371333</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639922406571189</v>
+        <v>0.6399206450757429</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422939641884077</v>
+        <v>0.642292537571082</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450475544547964</v>
+        <v>0.645044800976561</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469482851568616</v>
+        <v>0.646944651142786</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465865431208345</v>
+        <v>0.6465834688700681</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467977257855202</v>
+        <v>0.6467959536116236</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455896819121101</v>
+        <v>0.6455867007113627</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450682522832002</v>
+        <v>0.6450630763297474</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458994756465699</v>
+        <v>0.6458906069400063</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436941431731495</v>
+        <v>0.6436825543449256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6428704292797418</v>
+        <v>0.6428556808122914</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6440313340280563</v>
+        <v>0.6440143966123625</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6446192557428219</v>
+        <v>0.6446013376984718</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6464343803684885</v>
+        <v>0.6464134977520296</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6531216687233353</v>
+        <v>0.6531041179035058</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6650850021946744</v>
+        <v>0.6650601306814047</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6723833301287269</v>
+        <v>0.6723554761243572</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6882658697276816</v>
+        <v>0.6882406205471453</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6973568306096405</v>
+        <v>0.6973378220234105</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6997294213509013</v>
+        <v>0.699709525277366</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.7000085285062192</v>
+        <v>0.6999882736958104</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080649262927795</v>
+        <v>0.70805907835204</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080898106116708</v>
+        <v>0.7080853060826995</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108815378808726</v>
+        <v>0.7108845470332167</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7172269233404058</v>
+        <v>0.7172451350542437</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7174040916501594</v>
+        <v>0.7174234410687137</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7244707775445511</v>
+        <v>0.7244974996697716</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198656284206004</v>
+        <v>0.7198769755663341</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232229825594041</v>
+        <v>0.723235938768543</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227444899960839</v>
+        <v>0.7227555499036721</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199090108367854</v>
+        <v>0.7199179431504042</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147380203031322</v>
+        <v>0.714738123905086</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166203439872451</v>
+        <v>0.7166218929930382</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7165984251830702</v>
+        <v>0.7166022331410917</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153050083176147</v>
+        <v>0.7153092203923668</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130602451288934</v>
+        <v>0.7130630728417899</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106018478078007</v>
+        <v>0.7106061510412147</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106205476893128</v>
+        <v>0.7106253793291216</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084249016389979</v>
+        <v>0.7084323823721281</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058373758877621</v>
+        <v>0.7058513246904787</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.703963411275327</v>
+        <v>0.7039791836146887</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031145301624127</v>
+        <v>0.7031284347454518</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026269448604222</v>
+        <v>0.7026364836766748</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032073278215626</v>
+        <v>0.7032088709998027</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050513688582152</v>
+        <v>0.7050424603801355</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7068394452634409</v>
+        <v>0.706814917532538</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7077126080269094</v>
+        <v>0.7080865362956916</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7078958546495697</v>
+        <v>0.7082985069970282</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7071480507432235</v>
+        <v>0.7076360217189144</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.706643824220882</v>
+        <v>0.7072258459524465</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7060876402328573</v>
+        <v>0.7067283503922278</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7068129260109309</v>
+        <v>0.7074648139709395</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7088635044251645</v>
+        <v>0.7095150293806372</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7138014132542596</v>
+        <v>0.7144314201727078</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7187497728602925</v>
+        <v>0.7193571346564913</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7229818079520869</v>
+        <v>0.7236009034879093</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7265027212584021</v>
+        <v>0.7270729379131273</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7319852560997244</v>
+        <v>0.7322815115195083</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7439904633618464</v>
+        <v>0.7431148868734168</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.723543692180921</v>
+        <v>0.7268776787876667</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506120697543011</v>
+        <v>0.6506112017508594</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651414809130298</v>
+        <v>0.6514143515942685</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652476428669494</v>
+        <v>0.6524756461695941</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497299562040697</v>
+        <v>0.6497296272419453</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464297090000048</v>
+        <v>0.646429354978723</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431394664260508</v>
+        <v>0.6431390761995913</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408224731849043</v>
+        <v>0.6408220598591813</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398070930555267</v>
+        <v>0.6398066791357224</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642390185787774</v>
+        <v>0.6423882348917</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432664236666298</v>
+        <v>0.6432652572203583</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413593653287186</v>
+        <v>0.6413582063381477</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384824233974183</v>
+        <v>0.6384812496433486</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640365591807215</v>
+        <v>0.6403621407101473</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404406645371333</v>
+        <v>0.6404373319960314</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399206450757429</v>
+        <v>0.6399189215970801</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.642292537571082</v>
+        <v>0.6422911426492023</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645044800976561</v>
+        <v>0.6450421080148028</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.646944651142786</v>
+        <v>0.6469410957180368</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465834688700681</v>
+        <v>0.6465804606391062</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467959536116236</v>
+        <v>0.6467942196673268</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455867007113627</v>
+        <v>0.6455837840586002</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450630763297474</v>
+        <v>0.6450580133079519</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458906069400063</v>
+        <v>0.6458819301811669</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436825543449256</v>
+        <v>0.6436712158497675</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6428556808122914</v>
+        <v>0.6428412509350454</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6440143966123625</v>
+        <v>0.6439978239311146</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6446013376984718</v>
+        <v>0.6445838043085687</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6464134977520296</v>
+        <v>0.6463930639070466</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6531041179035058</v>
+        <v>0.6530869486640875</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6650601306814047</v>
+        <v>0.665035796740997</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6723554761243572</v>
+        <v>0.6723282246998221</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6882406205471453</v>
+        <v>0.6882159078931493</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6973378220234105</v>
+        <v>0.6973192159341981</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.699709525277366</v>
+        <v>0.6996900472979022</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6999882736958104</v>
+        <v>0.69996843916607</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.70805907835204</v>
+        <v>0.7080533429645675</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080853060826995</v>
+        <v>0.7080808834935528</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108845470332167</v>
+        <v>0.7108874760013595</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7172451350542437</v>
+        <v>0.7172629521699635</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7174234410687137</v>
+        <v>0.7174423750390011</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7244974996697716</v>
+        <v>0.724523656033884</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198769755663341</v>
+        <v>0.7198880812254229</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.723235938768543</v>
+        <v>0.7232486206732305</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227555499036721</v>
+        <v>0.7227663798706356</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199179431504042</v>
+        <v>0.7199266929960662</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714738123905086</v>
+        <v>0.714738226633967</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166218929930382</v>
+        <v>0.7166234129684372</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166022331410917</v>
+        <v>0.7166059621654888</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153092203923668</v>
+        <v>0.7153133426398381</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130630728417899</v>
+        <v>0.713065835834744</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106061510412147</v>
+        <v>0.7106103523359496</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106253793291216</v>
+        <v>0.7106300967724846</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084323823721281</v>
+        <v>0.7084396903242596</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058513246904787</v>
+        <v>0.7058649746203317</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7039791836146887</v>
+        <v>0.7039946333937368</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031284347454518</v>
+        <v>0.7031420693835015</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026364836766748</v>
+        <v>0.7026458630367121</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032088709998027</v>
+        <v>0.7032104356211561</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050424603801355</v>
+        <v>0.705033800381918</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.706814917532538</v>
+        <v>0.706790940465287</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7080865362956916</v>
+        <v>0.7084423148217931</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7082985069970282</v>
+        <v>0.7086891598509066</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7076360217189144</v>
+        <v>0.7081235261894228</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7072258459524465</v>
+        <v>0.7078476945402001</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7067283503922278</v>
+        <v>0.7074445617839091</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7074648139709395</v>
+        <v>0.7082315405555755</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7095150293806372</v>
+        <v>0.7103233881162778</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7144314201727078</v>
+        <v>0.7152755766491354</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7193571346564913</v>
+        <v>0.7202498215580044</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7236009034879093</v>
+        <v>0.7246557070978392</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7270729379131273</v>
+        <v>0.7281953811454629</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7322815115195083</v>
+        <v>0.7332981323070719</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7431148868734168</v>
+        <v>0.743432869858475</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7268776787876667</v>
+        <v>0.730834850239703</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506112017508594</v>
+        <v>0.6506103524119764</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514143515942685</v>
+        <v>0.6514139037657211</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524756461695941</v>
+        <v>0.6524748804080081</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497296272419453</v>
+        <v>0.6497293050916397</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.646429354978723</v>
+        <v>0.6464290083190002</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431390761995913</v>
+        <v>0.643138694117697</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408220598591813</v>
+        <v>0.640821655179068</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398066791357224</v>
+        <v>0.6398062738842233</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423882348917</v>
+        <v>0.6423863261548197</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432652572203583</v>
+        <v>0.6432641161926806</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413582063381477</v>
+        <v>0.6413570725856377</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384812496433486</v>
+        <v>0.6384801014341998</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403621407101473</v>
+        <v>0.6403587645400471</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404373319960314</v>
+        <v>0.640434071267278</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399189215970801</v>
+        <v>0.6399172349179736</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422911426492023</v>
+        <v>0.642289778378787</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450421080148028</v>
+        <v>0.645039473597395</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469410957180368</v>
+        <v>0.6469376163626611</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465804606391062</v>
+        <v>0.6465775163254985</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467942196673268</v>
+        <v>0.646792522729752</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455837840586002</v>
+        <v>0.6455809298815123</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450580133079519</v>
+        <v>0.6450530595644463</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458819301811669</v>
+        <v>0.6458734392088086</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436712158497675</v>
+        <v>0.6436601196701378</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6428412509350454</v>
+        <v>0.6428271294461293</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6439978239311146</v>
+        <v>0.6439816043439076</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6445838043085687</v>
+        <v>0.644566643338082</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6463930639070466</v>
+        <v>0.6463730645469965</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6530869486640875</v>
+        <v>0.6530701487122259</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.665035796740997</v>
+        <v>0.6650119831601375</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6723282246998221</v>
+        <v>0.672301556543502</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6882159078931493</v>
+        <v>0.6881917148784533</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6973192159341981</v>
+        <v>0.6973009997219253</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6996900472979022</v>
+        <v>0.699670974409989</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.69996843916607</v>
+        <v>0.6999490120254721</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080533429645675</v>
+        <v>0.7080477169649309</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080808834935528</v>
+        <v>0.7080765407065852</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108874760013595</v>
+        <v>0.7108903278266847</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7172629521699635</v>
+        <v>0.7172803873532654</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7174423750390011</v>
+        <v>0.7174609067693982</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724523656033884</v>
+        <v>0.7245492643848499</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7198880812254229</v>
+        <v>0.719898953007983</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232486206732305</v>
+        <v>0.7232610368688908</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227663798706356</v>
+        <v>0.7227769869658368</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199266929960662</v>
+        <v>0.7199352658805388</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714738226633967</v>
+        <v>0.714738328474565</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166234129684372</v>
+        <v>0.7166249047042641</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166059621654888</v>
+        <v>0.7166096146812162</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153133426398381</v>
+        <v>0.7153173779048605</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.713065835834744</v>
+        <v>0.7130685363009241</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106103523359496</v>
+        <v>0.7106144552431708</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106300967724846</v>
+        <v>0.7106347039888451</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084396903242596</v>
+        <v>0.7084468313725846</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058649746203317</v>
+        <v>0.7058783351266746</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7039946333937368</v>
+        <v>0.7040097703079026</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031420693835015</v>
+        <v>0.7031554417078003</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026458630367121</v>
+        <v>0.7026550865787853</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032104356211561</v>
+        <v>0.7032120193957671</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.705033800381918</v>
+        <v>0.7050253794398791</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.706790940465287</v>
+        <v>0.706767496285273</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7084423148217931</v>
+        <v>0.7087811321582813</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7086891598509066</v>
+        <v>0.7090397803537001</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7081235261894228</v>
+        <v>0.7085477190716527</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7078476945402001</v>
+        <v>0.7083263925573228</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7074445617839091</v>
+        <v>0.7079889264664335</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7082315405555755</v>
+        <v>0.708816646416504</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7103233881162778</v>
+        <v>0.7109262838285452</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7152755766491354</v>
+        <v>0.7158494533278632</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7202498215580044</v>
+        <v>0.7207588207418882</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7246557070978392</v>
+        <v>0.7250768936098204</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7281953811454629</v>
+        <v>0.7284488138686254</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7332981323070719</v>
+        <v>0.7331566652888624</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.743432869858475</v>
+        <v>0.7421931069736389</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.730834850239703</v>
+        <v>0.7306965014495234</v>
       </c>
     </row>
   </sheetData>
